--- a/vet_skills_refined.xlsx
+++ b/vet_skills_refined.xlsx
@@ -759,7 +759,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Configures IKE and site-to-site IPSec tunnels, securing network connections between locations.</t>
+          <t>Configures IKE and site-to-site IPSec tunnels for secure network connections between locations.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>keep:0, "IKE/IPSec Configuration":3</t>
+          <t>keep:1, "IKE/IPSec Configuration":2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Procedure Initiation</t>
+          <t>Initiative Problem</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Initiates standard protocols to resolve issues promptly across stable and evolving work situations.</t>
+          <t>Initiates standard procedures to resolve issues promptly across stable and evolving work situations.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>standard operating procedures; troubleshooting; adaptive response; process initiation; problem solving</t>
+          <t>standard operating procedures; initiative; adaptive response; process initiation; problem solving</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -963,16 +963,16 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Response' (respond) but evidence describes 'Initiates' procedures; action does not match</t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>keep:0, "Problem Response Initiation":3</t>
+          <t>keep:0, "Problem Response Initiation":1, "Standard Procedure Initiation":1, "Problem Response Initiative":1</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -989,24 +989,24 @@
         </is>
       </c>
       <c r="Z3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>generic FS capability "Initiative Problem" is implicit in other skills</t>
+        </is>
+      </c>
       <c r="AE3" t="b">
         <v>1</v>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Response' (respond) but evidence describes 'Initiates' procedures; action does not match</t>
-        </is>
-      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1123,12 +1123,12 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>keep:2, "Router Audit Configuration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>keep:0, "Security Procedure Confirmation":2, "Work Brief Confirmation":1</t>
+          <t>keep:0, "Security Procedure Confirmation":3</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Industry Regulation</t>
+          <t>Reading Industry Regulations</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Gathers, interprets and analyses current industry regulations from multiple sources to ensure compliance.</t>
+          <t>Collects and interprets current industry regulations from multiple sources to ensure compliance.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>regulatory compliance; policy interpretation; industry standards; legal research; governance frameworks</t>
+          <t>regulatory compliance; policy interpretation; industry standards; legal research; reading</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1436,19 +1436,15 @@
         </is>
       </c>
       <c r="S6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>keep:0, "Industry Regulation Interpretation/Regulation Interpretation":2, "Industry Regulation Analysis":1</t>
+          <t>keep:0, "Industry Regulation Interpretation":1, "reading industry rules":1, "Regulation Analysis":1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1465,7 +1461,7 @@
         </is>
       </c>
       <c r="Z6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -1476,13 +1472,9 @@
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Skill name 'Industry Regulation' is a noun and does not describe the gathering, interpreting, analysing actions in the evidence</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1581,7 +1573,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>formal planning processes; risk assessment; threat analysis; vulnerability assessment; risk management framework</t>
+          <t>risk assessment; threat analysis; vulnerability assessment; formal planning processes; risk management framework</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1737,7 +1729,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>VPN; network security; encryption; configuration; secure</t>
+          <t>VPN; network security; encryption; remote access; configuration</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1755,12 +1747,12 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>keep:2, "VPN Configuration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1893,7 +1885,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>system configuration; compliance; policy management; access control; documentation</t>
+          <t>system configuration; documentation; policy management; access control; audit trail</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1911,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1920,7 +1912,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "System Settings Documentation":1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -2022,7 +2014,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Asset Security</t>
+          <t>Security Monitoring</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2053,7 +2045,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>cybersecurity; asset monitoring; SIEM; intrusion detection; asset security monitoring</t>
+          <t>cybersecurity; asset monitoring; SIEM; intrusion detection; security monitoring</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2080,7 +2072,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>keep:1, "Asset Security Monitoring":2</t>
+          <t>keep:1, "Security Monitoring/Asset Security Monitoring":2</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -2100,17 +2092,17 @@
         <v>1</v>
       </c>
       <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Network Router Auditing (LLM verified, sim=0.83)</t>
+        </is>
+      </c>
       <c r="AC10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FS implicit in PCs — covered by: 1.6 Create and apply audit rules for network router and run </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
@@ -2187,7 +2179,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Identifies and manages work‑related risks independently.</t>
+          <t>Identifies and manages work‑related risks in personal security procedures independently.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2343,7 +2335,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Identifies purposes, functions, and key features of specialist systems for informed selection.</t>
+          <t>Identifies purposes, functions and key features of specialist systems to inform selection.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2369,7 +2361,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>system analysis; functional specification; feature identification; technology; function</t>
+          <t>function; technology; functional specification; feature identification; specialist systems</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2387,12 +2379,12 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.95</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>keep:2, "System Function Identification":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2490,12 +2482,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Remote Access Troubleshooting</t>
+          <t>Remote Server Troubleshooting</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tests remote access server.</t>
+          <t>Tests remote access server to rectify any faults.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2543,12 +2535,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>keep:0, "Remote Access Troubleshooting/Remote Server Troubleshooting":3</t>
+          <t>keep:0, "Remote Server Troubleshooting/Remote Access Troubleshooting":2, "Remote Access Fault Rectification":1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2650,7 +2642,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>VPN User Authentication</t>
+          <t>Site-to-site VPN Authentication</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2681,7 +2673,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>IPsec; SSL/TLS; RADIUS; MFA; user authentication</t>
+          <t>authentication; RADIUS; MFA; site-to-site; IPsec</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2696,15 +2688,19 @@
         </is>
       </c>
       <c r="S14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>keep:2, "Site-to-site VPN Authentication":1</t>
+          <t>keep:1, "Site-to-site VPN Authentication":2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2724,9 +2720,13 @@
         <v>1</v>
       </c>
       <c r="AA14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Secure VPN Configuration (LLM verified, sim=0.73)</t>
+        </is>
+      </c>
       <c r="AC14" t="b">
         <v>0</v>
       </c>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tests network for vulnerabilities following work briefs and organizational policies.</t>
+          <t>Tests network for vulnerabilities according to work brief and organisational policies and procedures.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>penetration testing; network security assessment; vulnerability scanning; risk assessment; security policies</t>
+          <t>penetration testing; network security assessment; vulnerability scanning; risk assessment; network testing</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Z15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -2892,13 +2892,9 @@
         </is>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>Skill name 'Network Vulnerability' does not describe the action 'Test' shown in the evidence; it is a noun rather than an action verb</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2971,7 +2967,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Prepares technical reports using prescribed templates to meet organisational documentation standards.</t>
+          <t>Prepares technical documentation using prescribed templates to meet organisational documentation standards.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2997,7 +2993,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>technical documentation; report formatting; organizational standards; template compliance; writing</t>
+          <t>technical documentation; report formatting; organizational standards; word processing tools; template compliance</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3024,7 +3020,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>keep:0, "Documentation Writing/Technical Documentation Writing":2, "Documentation Preparation":1</t>
+          <t>keep:0, "Documentation Writing/Workplace Documentation Writing":2, "Documentation Preparation":1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -3041,7 +3037,7 @@
         </is>
       </c>
       <c r="Z16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="b">
         <v>1</v>
@@ -3131,7 +3127,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sources required network hardware, software and tools, then confirms each component is serviceable before deployment.</t>
+          <t>Sources required network configuration hardware, software and tools and confirms each component is serviceable before deployment.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3157,7 +3153,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>network hardware sourcing; tool procurement; component verification; serviceability confirmation; network configuration hardware</t>
+          <t>network hardware sourcing; network configuration hardware; component verification; serviceability check; tool procurement</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3167,54 +3163,22 @@
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Network Component Procurement</t>
-        </is>
-      </c>
-      <c r="S17" t="b">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Sources required network hardware, software and tools, then verifies each component is serviceable before deployment.</t>
-        </is>
-      </c>
-      <c r="X17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>network hardware sourcing, software acquisition, tool procurement, component verification, serviceability confirmation</t>
-        </is>
-      </c>
-      <c r="Z17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="b">
-        <v>0</v>
-      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
@@ -3310,7 +3274,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>gateway connection; network router; prerequisite establishment; connection confirmation; verification process</t>
+          <t>gateway connection; network router; prerequisite establishment; verification process; confirm gateway connection</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3319,54 +3283,22 @@
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Gateway Connection Verification</t>
-        </is>
-      </c>
-      <c r="S18" t="b">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Establishes required prerequisites and confirms the gateway is correctly connected to the network router.</t>
-        </is>
-      </c>
-      <c r="X18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>gateway connection, network router, prerequisite establishment, connection confirmation, verification process</t>
-        </is>
-      </c>
-      <c r="Z18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="b">
-        <v>0</v>
-      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
@@ -3431,12 +3363,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Router Console Access</t>
+          <t>Router Management Access</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Installs the router and its management console.</t>
+          <t>Installs the router management console.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3462,7 +3394,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>router management console; router console; management interface; installation; access</t>
+          <t>router console installation; management console access; router management console; console setup; router administration</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3471,54 +3403,22 @@
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Router Console Access</t>
-        </is>
-      </c>
-      <c r="S19" t="b">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Installs the router and accesses its management console to configure and monitor VPN settings.</t>
-        </is>
-      </c>
-      <c r="X19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>router console, management interface, installation, access, configuration</t>
-        </is>
-      </c>
-      <c r="Z19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="b">
-        <v>0</v>
-      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
@@ -3588,7 +3488,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Plans authentication controls by using contextual intuition to determine appropriate methods.</t>
+          <t>Plans authentication controls using contextual intuition to determine appropriate methods.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3632,16 +3532,16 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name 'Authentication Controls' does not reflect the planning action described in the evidence</t>
+          <t>MIS re-refinement: Skill name 'Authentication Controls' does not reflect the evidence which describes planning control methods; the name lacks the planning action present in the evidence</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Authentication Controls Planning":1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3673,7 +3573,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Skill name 'Authentication Controls' does not reflect the planning action described in the evidence</t>
+          <t>Skill name 'Authentication Controls' does not reflect the evidence which describes planning control methods; the name lacks the planning action present in the evidence</t>
         </is>
       </c>
       <c r="AG20" t="b">
@@ -3748,7 +3648,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Develops and documents authentication system protocols to meet specified requirements.</t>
+          <t>Develops and documents authentication system designs and protocols to meet specified requirements.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3774,7 +3674,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>identity management; security protocols; access control; IAM; authentication</t>
+          <t>authentication; identity management; security protocols; access control; IAM</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3792,16 +3692,16 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>keep:2, "Authentication Documentation Development":1</t>
+          <t>keep:1, "Authentication Documentation Development":2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3825,13 +3725,9 @@
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 3.1 Develop and document authentication systems and protocol</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
@@ -3908,7 +3804,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Demonstrates intuitive analysis to identify authentication failures, generate possible solutions, and identify security incidents.</t>
+          <t>Demonstrates intuitive analysis to identify authentication failures, generate insights into security incidents, and define problem scope.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3952,16 +3848,16 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name lacks an action verb and does not reflect the evidence action of using intuition to identify authentication failures</t>
+          <t>MIS re-refinement: Skill name is a noun phrase (problem) not an action, while evidence describes using intuition to identify authentication failures</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Authentication Failure Identification":1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3993,7 +3889,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>Skill name lacks an action verb and does not reflect the evidence action of using intuition to identify authentication failures</t>
+          <t>Skill name is a noun phrase (problem) not an action, while evidence describes using intuition to identify authentication failures</t>
         </is>
       </c>
       <c r="AG22" t="b">
@@ -4068,7 +3964,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Determines user and organisational authentication requirements according to the security plan.</t>
+          <t>Determines user and organisational authentication requirements per security plan.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4145,9 +4041,13 @@
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FS implicit in PCs — covered by: 1.1 Determine user and organisational security requirements </t>
+        </is>
+      </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
@@ -4250,7 +4150,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>identity management; access control; realm configuration; authentication protocols; authentication system</t>
+          <t>identity management; access control; realm configuration; authentication system; authentication protocols</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -4301,9 +4201,13 @@
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 2.1 Create required authentication realm and reuse according</t>
+        </is>
+      </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
@@ -4375,12 +4279,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Feedback Response Coordination</t>
+          <t>Feedback Response</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Submits required documents in response to feedback from required personnel.</t>
+          <t>Submits required documentation and responds to feedback from personnel.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4421,15 +4325,19 @@
         </is>
       </c>
       <c r="S25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9333333333333332</v>
-      </c>
-      <c r="U25" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: Skill name uses 'Coordination' which is not an action verb in the evidence (evidence verbs are 'Submit' and 'respond')</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Feedback Response":1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -4465,7 +4373,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>Skill name uses 'Coordination' which is not an action verb present in the evidence (evidence actions are 'Submit' and 'respond')</t>
+          <t>Skill name uses 'Coordination' which is not an action verb in the evidence (evidence verbs are 'Submit' and 'respond')</t>
         </is>
       </c>
       <c r="AG25" t="b">
@@ -4540,7 +4448,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Determines, documents, monitors and reports security monitoring and incident response procedures in line with the organization’s security plan.</t>
+          <t>Determines and documents security monitoring and incident response procedures in line with the organization’s security plan.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4566,7 +4474,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>security monitoring; incident management; SIEM; security plan documentation; reporting processes</t>
+          <t>security monitoring; incident management; security plan documentation; reporting processes; risk compliance</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4584,16 +4492,16 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Management' but evidence actions are 'determine' and 'document' without a management verb</t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>keep:1, "Incident Management Documentation":1, "Security Process Documentation":1</t>
+          <t>keep:0, "Incident Management Documentation":3</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -4617,21 +4525,13 @@
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 4.2 Determine and document security monitoring, incident man</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Management' but evidence actions are 'determine' and 'document' without a management verb</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4704,7 +4604,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Reviews authentication systems to meet user requirements and service quality standards.</t>
+          <t>Reviews authentication systems with security controls meeting user requirements and service quality standards.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4748,16 +4648,16 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>MIS re-refinement: Skill name uses 'Monitoring' but evidence describes 'Review' of authentication system; actions do not match</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>keep:0, "Authentication System Review":2, "Security Monitoring Review":1</t>
+          <t>keep:0, "Security Monitoring Review":1, "Authentication System Review":1, "Authentication Monitoring":1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4777,21 +4677,25 @@
         <v>1</v>
       </c>
       <c r="AA27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>Authentication System</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FS implicit in PCs — covered by: 4.1 Review authentication system according to user security </t>
+        </is>
+      </c>
       <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Monitoring' but evidence describes 'Review' of authentication system; actions do not match</t>
+        </is>
+      </c>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4864,7 +4768,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Determines authentication and authorisation steps in accordance with organisational security policies.</t>
+          <t>Determines authentication and authorisation steps in line with organisational security policies.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4890,7 +4794,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>authentication; authorisation; access control; identity management; security policy</t>
+          <t>authentication; access control; identity management; security policy; authorisation</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4912,12 +4816,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Alignment' but evidence action is 'Determine'</t>
+          <t>MIS re-refinement: Skill name uses 'Alignment' (align) which does not match evidence action 'Determine'</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>keep:0, "Authentication Policy Alignment/Authentication Process Alignment/Authentication Alignment":3</t>
+          <t>keep:0, "Authentication Policy Alignment/Authentication Process Alignment":3</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4941,15 +4845,19 @@
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 1.3 Determine required authentication and authorisation proc</t>
+        </is>
+      </c>
       <c r="AE28" t="b">
         <v>1</v>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>Skill name uses 'Alignment' but evidence action is 'Determine'</t>
+          <t>Skill name uses 'Alignment' (align) which does not match evidence action 'Determine'</t>
         </is>
       </c>
       <c r="AG28" t="b">
@@ -5050,7 +4958,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>protocol compliance; information security; policy adherence; access control; self-management</t>
+          <t>protocol compliance; self-management; information security; policy adherence; access control</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -5072,12 +4980,12 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>keep:1, "Protocol Self‑Management":2</t>
+          <t>keep:0, "Protocol Self‑management":3</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -5101,9 +5009,13 @@
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>FS describes work style (following protocols and meeting role expectations) not a distinct task; activity is implicit in PCs</t>
+        </is>
+      </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
@@ -5175,12 +5087,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Technical Data Analysis</t>
+          <t>Technical Data Interpretation</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Analyses technical data against user and organisational plans to determine system requirements.</t>
+          <t>Analyzes technical data against user and organisational plans to define system requirements.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5206,7 +5118,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>data analysis; requirements engineering; technical specifications; engineering standards; technical data</t>
+          <t>data interpretation; data analysis; requirements engineering; technical specifications; engineering standards</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -5221,19 +5133,15 @@
         </is>
       </c>
       <c r="S30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>keep:1, "Technical Data Analysis":2</t>
+          <t>keep:2, "Technical Data Analysis":1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -5242,7 +5150,7 @@
         </is>
       </c>
       <c r="X30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -5257,13 +5165,9 @@
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>FS activity mirrors PC1.1 Determine user and organisational security requirements</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
@@ -5366,7 +5270,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>identity management; access control; role-based access; authentication systems; user attribute</t>
+          <t>user attribute; identity management; access control; role-based access; authentication systems</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -5388,12 +5292,12 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>keep:0, "User Attribute Setup":2, "User Attribute Configuration":1</t>
+          <t>keep:0, "User Attribute Configuration":3</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -5495,12 +5399,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Permission Configuration Storage</t>
+          <t>Permission Configuration Recording</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Records and securely stores permission and configuration information in compliance with authentication system requirements.</t>
+          <t>Records and securely stores permission and configuration information in accordance with authentication system requirements.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5522,11 +5426,11 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>permission records; configuration data; secure storage; authentication system; authentication system requirements</t>
+          <t>permission data; configuration information; secure storage; authentication system; record keeping</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -5535,54 +5439,22 @@
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Permission Configuration Storage</t>
-        </is>
-      </c>
-      <c r="S32" t="b">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Records and securely stores permission and configuration information in compliance with authentication system requirements.</t>
-        </is>
-      </c>
-      <c r="X32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>permission records, configuration data, secure storage, authentication system, archival process</t>
-        </is>
-      </c>
-      <c r="Z32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="b">
-        <v>0</v>
-      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
@@ -5644,12 +5516,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Data Manipulation</t>
+          <t>Item Manipulation Scripting</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Incorporates item manipulation to transform data items within the chosen scripting language.</t>
+          <t>Incorporates item manipulation using the chosen scripting language, automating transformations within the language.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5675,7 +5547,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>data transformation; automation; Python; PowerShell; manipulation</t>
+          <t>data transformation; automation; item manipulation; Python; PowerShell</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5693,16 +5565,16 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>keep:2, "Item Manipulation Scripting":1</t>
+          <t>keep:1, "Item Manipulation Scripting":2</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -5801,7 +5673,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>IDE Selection</t>
+          <t>IDE Identification</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5832,7 +5704,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>development environment; code editor; language support; software development tools; IDE selection</t>
+          <t>development environment; code editor; language support; software development tools; IDE</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5854,12 +5726,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>MIS re-refinement: Skill name uses 'Selection' (select) while evidence action is 'Identify' (identify) – different activity</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>keep:0, "IDE Selection":3</t>
+          <t>keep:1, "IDE Selection":2</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5891,9 +5763,13 @@
         </is>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Selection' (select) while evidence action is 'Identify' (identify) – different activity</t>
+        </is>
+      </c>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5989,7 +5865,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>code comments; technical documentation; script standards; internal documentation; software development procedures</t>
+          <t>code comments; technical documentation; script standards; software development procedures; internal documentation</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -6007,12 +5883,12 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Script Documentation":1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -6268,12 +6144,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Protocol Model Identification</t>
+          <t>Protocol Object Model</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Identifies communication protocols and underlying object model of the chosen scripting language.</t>
+          <t>Identifies communication protocols and underlying object model in the chosen scripting language.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -6314,15 +6190,19 @@
         </is>
       </c>
       <c r="S37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>keep:2, "Protocol Object Model Identification":1</t>
+          <t>keep:1, "Protocol Object Model Identification":2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -6346,13 +6226,9 @@
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 2.3 Identify protocols and object model used in chosen scrip</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
@@ -6426,7 +6302,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Creates detailed pseudocode and describes script logic to support development and debugging.</t>
+          <t>Creates pseudocode and describes script logic to support development and debugging.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -6627,12 +6503,12 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Script Debugging":3</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -6915,7 +6791,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>pseudo-code; scripting languages; code conversion; basic syntax; script translation</t>
+          <t>pseudo-code; scripting languages; code conversion; basic syntax; translation</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -6937,12 +6813,12 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Script Translation":2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -7042,7 +6918,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Identifies main characteristics of scripting languages to support appropriate selection.</t>
+          <t>Identifies key characteristics of scripting languages for appropriate selection.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -7068,7 +6944,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>interpreted languages; scripting language; automation scripting; Python; JavaScript</t>
+          <t>interpreted languages; dynamic typing; Python; JavaScript; scripting language</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -7090,12 +6966,12 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>keep:0, "Scripting Language Identification":2, "Scripting Language Characteristics":1</t>
+          <t>keep:0, "Scripting Language Identification/Scripting Language Characteristics Identification":3</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -7115,9 +6991,13 @@
         <v>1</v>
       </c>
       <c r="AA42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Systematic Problem (LLM verified, sim=0.81)</t>
+        </is>
+      </c>
       <c r="AC42" t="b">
         <v>0</v>
       </c>
@@ -7190,12 +7070,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Software Requirements Identification</t>
+          <t>Software Application Identification</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Identifies required software outcomes by defining functional specifications.</t>
+          <t>Identifies required software outcomes, identifying user needs and functional specifications.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -7221,7 +7101,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>requirements gathering; functional specifications; use case modeling; stakeholder analysis; software</t>
+          <t>requirements gathering; functional specifications; use case modeling; software; application</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -7239,16 +7119,16 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name 'Software Requirements' lacks the action verb present in evidence ('Identify'), resulting in a mismatch between name and evidence</t>
+          <t>MIS re-refinement: Skill name 'Software Requirements' is a noun phrase and does not describe the action 'Identify' shown in the evidence</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>keep:2, "Software Outcome Identification":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -7272,19 +7152,15 @@
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 1.1 Identify required software application outcomes</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="b">
         <v>1</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>Skill name 'Software Requirements' lacks the action verb present in evidence ('Identify'), resulting in a mismatch between name and evidence</t>
+          <t>Skill name 'Software Requirements' is a noun phrase and does not describe the action 'Identify' shown in the evidence</t>
         </is>
       </c>
       <c r="AG43" t="b">
@@ -7429,9 +7305,13 @@
         <v>1</v>
       </c>
       <c r="AA44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Stakeholder Expectation (LLM verified, sim=0.72)</t>
+        </is>
+      </c>
       <c r="AC44" t="b">
         <v>0</v>
       </c>
@@ -7553,7 +7433,7 @@
         <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -7562,7 +7442,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Expectation Discussion":1</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -7586,9 +7466,13 @@
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FS implicit in PCs — covered by: 1.2 Discuss expectations of final software application with </t>
+        </is>
+      </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
@@ -7688,7 +7572,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>algorithmic analysis; scripting languages; pseudo‑code evaluation; systematic analysis; problem identification</t>
+          <t>algorithmic analysis; scripting languages; pseudo‑code evaluation; systematic; problem</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -7706,7 +7590,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -7715,7 +7599,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Problem Solving":1</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -7859,7 +7743,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7868,7 +7752,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Technical Reading":1</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -7995,7 +7879,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>cloud computing; business value analysis; ROI assessment; solution evaluation; benefits documentation</t>
+          <t>cloud computing; business value analysis; ROI assessment; solution evaluation; benefits</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -8013,12 +7897,12 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Benefits Identification and Documentation":1</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -8038,17 +7922,17 @@
         <v>1</v>
       </c>
       <c r="AA48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>Challenges Documentation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 3.1 Identify and document benefits of adopting best cloud so</t>
+        </is>
+      </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
@@ -8167,12 +8051,12 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>keep:2, "Challenges Documentation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -8192,9 +8076,13 @@
         <v>0</v>
       </c>
       <c r="AA49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Benefits Documentation</t>
+        </is>
+      </c>
       <c r="AC49" t="b">
         <v>0</v>
       </c>
@@ -8299,7 +8187,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>cloud vendor evaluation; service model comparison; cost‑benefit analysis; scalability and compliance; cloud service platform</t>
+          <t>cloud vendor evaluation; service model comparison; cost‑benefit analysis; scalability and compliance; cloud service</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -8435,7 +8323,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Seeks evaluation feedback on cloud solutions and services.</t>
+          <t>Finalises cloud solution assessments, seeks stakeholder feedback, and responds to feedback accordingly.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -8461,7 +8349,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>cloud computing; solution assessment; cost analysis; service level agreement; services evaluation</t>
+          <t>cloud computing; solution assessment; cost analysis; service level agreement; evaluation feedback</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -8479,7 +8367,7 @@
         <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -8488,7 +8376,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>keep:2, "Cloud Solutions Evaluation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -8742,7 +8630,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Evaluation Document Management</t>
+          <t>Evaluation Document</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -8773,7 +8661,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>document control; records management; versioning; compliance filing; evaluation document</t>
+          <t>evaluation document; document control; records management; versioning; compliance filing</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -8795,7 +8683,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>MIS re-refinement: Skill name uses 'Management' which does not match evidence actions 'Save' and 'lodge'</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -8832,9 +8720,13 @@
         </is>
       </c>
       <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Management' which does not match evidence actions 'Save' and 'lodge'</t>
+        </is>
+      </c>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -8900,7 +8792,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Emerging Cloud Model</t>
+          <t>Emerging Model Identification</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -8949,16 +8841,16 @@
         <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>MIS re-refinement: Skill name 'Emerging Model' lacks the research/identify actions described in the evidence</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>keep:1, "Emerging Cloud Model Research":2</t>
+          <t>keep:1, "Emerging Model Identification":1, "Emerging Model Research":1</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -8990,9 +8882,13 @@
         </is>
       </c>
       <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Skill name 'Emerging Model' lacks the research/identify actions described in the evidence</t>
+        </is>
+      </c>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -9063,7 +8959,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Communicates evaluation results to designated staff through briefings.</t>
+          <t>Conveys evaluation results to designated staff through concise reports or briefings.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -9111,12 +9007,12 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>keep:0, "Evaluation Outcomes Communication":3</t>
+          <t>keep:1, "Evaluation Outcomes Communication":2</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -9125,7 +9021,7 @@
         </is>
       </c>
       <c r="X55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -9136,17 +9032,17 @@
         <v>1</v>
       </c>
       <c r="AA55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>Report Writing (LLM verified, sim=0.78)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 3.4 Communicate outcomes of evaluation to required personnel</t>
+        </is>
+      </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
@@ -9221,7 +9117,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Analyses information from multiple sources against defined criteria.</t>
+          <t>Analyses data from multiple sources against defined criteria.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -9302,7 +9198,7 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>FS activity mirrors PC2.1 (Identify and review capability and characteristics against requirements)</t>
+          <t>FS activity mirrors PC2.1 (identifies and reviews capabilities against business requirements)</t>
         </is>
       </c>
       <c r="AE56" t="b">
@@ -9379,7 +9275,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Obtains and responds to feedback from relevant personnel using concise verbal language.</t>
+          <t>Obtains feedback from relevant personnel and responds with concise verbal language.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -9405,7 +9301,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>verbal communication; active listening; concise feedback; stakeholder interaction; interpersonal communication</t>
+          <t>verbal communication; active listening; concise feedback; oral feedback; interpersonal communication</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -9423,7 +9319,7 @@
         <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -9432,7 +9328,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Oral Feedback Response":1</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -9449,7 +9345,7 @@
         </is>
       </c>
       <c r="Z57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -9590,7 +9486,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>keep:0, "Policy Identification/Policy Requirement Identification":3</t>
+          <t>keep:0, "Policy Identification":3</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -9690,12 +9586,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Report Writing</t>
+          <t>Documentation Preparation</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Records required data and prepares concise documentation summarizing findings and analysis.</t>
+          <t>Records required data and prepares concise reports summarizing findings and analysis.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -9721,7 +9617,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>technical documentation; analysis reporting; findings presentation; Word processing; writing</t>
+          <t>technical documentation; analysis reporting; findings presentation; Word processing; records</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -9736,15 +9632,19 @@
         </is>
       </c>
       <c r="S59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U59" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>keep:1, "Findings Documentation":1, "Documentation Preparation":1</t>
+          <t>keep:1, "Documentation Preparation":2</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -9768,9 +9668,13 @@
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 3.1 Identify and document benefits of adopting best cloud so</t>
+        </is>
+      </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
@@ -9889,12 +9793,12 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Routine Task Management":1</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -9990,7 +9894,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Decision Making</t>
+          <t>Self‑management Decision‑making</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -10021,7 +9925,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>routine decision‑making; low‑impact choices; predefined solutions; operational judgment; familiar situations</t>
+          <t>routine decision‑making; low‑impact choices; predefined solutions; self‑management; autonomous problem solving</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -10036,19 +9940,15 @@
         </is>
       </c>
       <c r="S61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>keep:1, "Decision Making":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -10072,13 +9972,9 @@
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>generic FS capability "Decision Making" is implicit in other skills</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
@@ -10148,7 +10044,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Total Cost Ownership</t>
+          <t>Cost of Ownership</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -10206,7 +10102,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>keep:1, "Total Cost Ownership Analysis":2</t>
+          <t>keep:1, "Cost of Ownership Analysis":2</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -10307,7 +10203,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Identifies and confirms business and industry technology terminology, characteristics and concepts for cloud solution evaluation.</t>
+          <t>Identifies and confirms business and industry technology terminology, characteristics and concepts for cloud solutions.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -10333,7 +10229,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>technology terminology; industry concepts; business characteristics; terminology verification; industry technology terminology</t>
+          <t>business terminology; industry terminology; technology concepts; industry technology terminology; terminology verification</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -10342,54 +10238,22 @@
         </is>
       </c>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Technology Terminology</t>
-        </is>
-      </c>
-      <c r="S63" t="b">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Identifies and confirms business and industry technology terminology, characteristics and concepts for cloud solution evaluation.</t>
-        </is>
-      </c>
-      <c r="X63" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>technology terminology, industry concepts, business characteristics, cloud evaluation, terminology verification</t>
-        </is>
-      </c>
-      <c r="Z63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA63" t="b">
-        <v>0</v>
-      </c>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr"/>
-      <c r="AC63" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC63" t="inlineStr"/>
       <c r="AD63" t="inlineStr"/>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr"/>
@@ -10457,7 +10321,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Identifies and reviews cloud service platforms and delivery models, matching capabilities and characteristics to business requirements.</t>
+          <t>Identifies and reviews capability and characteristics of cloud service platforms and delivery models against business requirements.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -10479,11 +10343,11 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>cloud platforms; service models; business requirements; capability assessment; delivery models</t>
+          <t>cloud platforms; service characteristics; delivery models; business requirements; capability review</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -10492,54 +10356,22 @@
         </is>
       </c>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Cloud Platform Assessment</t>
-        </is>
-      </c>
-      <c r="S64" t="b">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Analyzes cloud service platforms and delivery models, matching capabilities and characteristics to business requirements.</t>
-        </is>
-      </c>
-      <c r="X64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>cloud platforms, service models, business requirements, capability assessment, characteristic review</t>
-        </is>
-      </c>
-      <c r="Z64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA64" t="b">
-        <v>0</v>
-      </c>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
       <c r="AB64" t="inlineStr"/>
-      <c r="AC64" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC64" t="inlineStr"/>
       <c r="AD64" t="inlineStr"/>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr"/>
@@ -10638,7 +10470,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>risk assessment; critical function identification; business continuity; impact analysis; business resilience</t>
+          <t>risk assessment; critical function identification; impact analysis; business resilience; business continuity</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -10770,12 +10602,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Contingency Documentation</t>
+          <t>Documentation Preparation</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Prepares comprehensive contingency documentation detailing evaluations and strategies in prescribed language and formats.</t>
+          <t>Prepares comprehensive contingency plans, preparing evaluations and strategies in prescribed language and formats.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -10801,7 +10633,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>business continuity; risk assessment; documentation standards; strategy evaluation; contingency planning</t>
+          <t>business continuity; risk assessment; documentation standards; strategy evaluation; language and formats</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -10823,12 +10655,12 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Planning' but evidence only requires 'Prepare' documentation</t>
+          <t>MIS re-refinement: Skill name uses 'Planning' but evidence only describes 'Prepare' documentation; the action does not match</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>keep:1, "Documentation Preparation":1, "Contingency Documentation":1</t>
+          <t>keep:1, "Contingency Documentation":1, "Documentation Preparation":1</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -10852,19 +10684,15 @@
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 2.2 Evaluate and document risk minimisation alternatives aga</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="b">
         <v>1</v>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' but evidence only requires 'Prepare' documentation</t>
+          <t>Skill name uses 'Planning' but evidence only describes 'Prepare' documentation; the action does not match</t>
         </is>
       </c>
       <c r="AG66" t="b">
@@ -10986,7 +10814,7 @@
         <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -10995,7 +10823,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>keep:2, "Critical Data Software Identification":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -11031,7 +10859,7 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>Skill name lacks the action verb present in evidence (evidence requires 'Identify', name only 'Critical Data'</t>
+          <t>Skill name lacks verb and does not reflect evidence action 'Identify'</t>
         </is>
       </c>
       <c r="AG67" t="b">
@@ -11109,7 +10937,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Develops comprehensive disaster recovery plans, documents them, and submits them to designated stakeholders.</t>
+          <t>Develops comprehensive disaster recovery plans, documents them, and submits them to designated personnel.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -11135,7 +10963,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>disaster recovery plan; business continuity; risk assessment; recovery time objective; contingency planning</t>
+          <t>business continuity; risk assessment; recovery time objective; contingency planning; disaster recovery</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -11294,7 +11122,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>business continuity; risk assessment; backup and replication; disaster recovery; continuity planning</t>
+          <t>business continuity; risk assessment; backup and replication; continuity planning; disaster recovery</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -11312,7 +11140,7 @@
         <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -11321,7 +11149,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>keep:2, "Prevention Recovery Strategy Formulation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -11426,7 +11254,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Numerical Data Interpretation</t>
+          <t>System Data Analysis</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -11457,7 +11285,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>quantitative analysis; financial data reporting; technical system metrics; data visualization; numerical data interpretation</t>
+          <t>quantitative analysis; financial data reporting; technical system metrics; data visualization; numerical data</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -11472,15 +11300,19 @@
         </is>
       </c>
       <c r="S70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>keep:0, "System Data Analysis":1, "System Data Interpretation":1, "Data Analysis Documentation":1</t>
+          <t>keep:0, "System Data Analysis":3</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -11612,7 +11444,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>data analysis; feedback loops; continuous improvement; process optimization; problem</t>
+          <t>problem; data analysis; feedback loops; continuous improvement; process optimization</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -11744,12 +11576,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Compliance Requirement Identification</t>
+          <t>Regulatory Requirement Identification</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Identifies statutory, commercial and contingency requirements for organisational compliance obligations.</t>
+          <t>Identifies statutory, commercial and contingency requirements for compliance obligations.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -11775,7 +11607,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>regulatory frameworks; statutory requirements; compliance software; commercial requirements; contingency requirements</t>
+          <t>regulatory frameworks; statutory requirements; commercial requirements; audit and monitoring; contingency requirements</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -11802,7 +11634,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>keep:0, "Compliance Requirement Identification/Requirement Identification":2, "Regulatory Requirements Identification":1</t>
+          <t>keep:0, "Regulatory Requirement Identification/Regulatory Requirements Identification":2, "Compliance Requirements Identification":1</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -11907,12 +11739,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Risk Minimisation</t>
+          <t>Risk Minimisation Alternatives</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Evaluates risk‑minimisation options and documents findings against organisational cost limits in hybrid projects.</t>
+          <t>Evaluates risk‑minimisation options and documents findings in hybrid projects.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -11938,7 +11770,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>risk assessment; cost‑benefit analysis; mitigation strategies; financial modeling; risk minimisation</t>
+          <t>risk assessment; cost‑benefit analysis; mitigation strategies; risk register; risk minimisation alternatives</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -11956,16 +11788,16 @@
         <v>1</v>
       </c>
       <c r="T73" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.9</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Risk Minimisation Alternatives Evaluation":2</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -12075,7 +11907,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Identifies and documents internal and external system threats through hybrid risk threat analysis.</t>
+          <t>Identifies and documents internal and external system threats.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -12101,7 +11933,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>threat modeling; risk assessment; threat intelligence; vulnerability analysis; business environment system</t>
+          <t>threat modeling; risk assessment; vulnerability analysis; threat intelligence; business environment system</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -12238,7 +12070,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Documents feedback from relevant parties, seeks input, and submits responses in hybrid settings.</t>
+          <t>Documents and submits to relevant parties, seeks input, and incorporates feedback in hybrid settings.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -12401,7 +12233,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Demonstrates priorities across flexible hybrid teams to achieve efficient outcomes.</t>
+          <t>Demonstrates prioritisation of outcomes across flexible hybrid teams to achieve efficient results.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -12445,7 +12277,7 @@
         <v>1</v>
       </c>
       <c r="T76" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -12454,7 +12286,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Strategic Planning":1</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -12478,13 +12310,9 @@
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>FS activity of strategic planning of priorities is already covered by PC related to formulating prevention and recovery strategy</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
@@ -12559,12 +12387,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Collaboration Facilitation</t>
+          <t>Teamwork Collaboration</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Maintains team collaboration by employing communication tools and strategies to sustain working relationships.</t>
+          <t>Uses communication tools and strategies to maintain effective working relationships.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -12590,7 +12418,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>communication tools; effective working relationships; relationship building; facilitation techniques; interpersonal dynamics</t>
+          <t>communication tools; relationship building; collaboration platforms; interpersonal dynamics; teamwork</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -12608,16 +12436,16 @@
         <v>1</v>
       </c>
       <c r="T77" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>keep:0, "Collaboration Facilitation":2, "Teamwork Facilitation":1</t>
+          <t>keep:0, "Teamwork Collaboration":1, "Teamwork Communication":1, "Collaboration Facilitation":1</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -12718,7 +12546,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Oral Communication</t>
+          <t>Technical Oral Communication</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -12764,19 +12592,15 @@
         </is>
       </c>
       <c r="S78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr">
         <is>
-          <t>keep:1, "Oral Communication":2</t>
+          <t>keep:2, "Oral Communication":1</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -12877,7 +12701,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Specification Research</t>
+          <t>Specification Analysis</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -12908,7 +12732,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>technical documentation; specification analysis; information retrieval; data extraction; research</t>
+          <t>technical documentation; specification analysis; information retrieval; data extraction; textual information</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -12926,16 +12750,16 @@
         <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name 'Technical Specification' does not describe the research and analysis actions in the evidence</t>
+          <t>MIS re-refinement: Skill name 'Technical Specification' implies managing specifications, but evidence describes researching and analysing specifications</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>keep:2, "Technical Information Research":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -12967,7 +12791,7 @@
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>Skill name 'Technical Specification' does not describe the research and analysis actions in the evidence</t>
+          <t>Skill name 'Technical Specification' implies managing specifications, but evidence describes researching and analysing specifications</t>
         </is>
       </c>
       <c r="AG79" t="b">
@@ -13045,7 +12869,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Assesses how business risks and threats could affect ICT systems and potential impact levels.</t>
+          <t>Assesses how business risks and threats could affect ICT systems.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -13067,11 +12891,11 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>business risk; threat analysis; ICT systems; impact assessment; risk evaluation</t>
+          <t>business risk; ICT systems; threat analysis; impact evaluation; risk assessment</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -13080,54 +12904,22 @@
         </is>
       </c>
       <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Risk Impact</t>
-        </is>
-      </c>
-      <c r="S80" t="b">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Evaluates how business risks and threats could affect ICT systems and determines potential impact levels.</t>
-        </is>
-      </c>
-      <c r="X80" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>business risk, threat analysis, ICT systems, impact assessment, risk evaluation</t>
-        </is>
-      </c>
-      <c r="Z80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA80" t="b">
-        <v>0</v>
-      </c>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC80" t="inlineStr"/>
       <c r="AD80" t="inlineStr"/>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="inlineStr"/>
       <c r="AJ80" t="inlineStr"/>
@@ -13200,12 +12992,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Reviews industry standard operational procedures and checks that required risk safeguards and contingency plans are in place.</t>
+          <t>The worker reviews industry standard operational procedures and checks that required risk safeguards and contingency plans are in place.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>technical</t>
+          <t>cognitive</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -13218,15 +13010,15 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>practical</t>
+          <t>theoretical</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>industry standards; operational procedures; risk safeguards; contingency plans; compliance checks</t>
+          <t>industry standard procedures; risk safeguards; contingency plans; compliance verification; operational review</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -13235,54 +13027,22 @@
         </is>
       </c>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>Operational Procedure Review</t>
-        </is>
-      </c>
-      <c r="S81" t="b">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Reviews industry standard operational procedures and verifies that required risk safeguards and contingency plans are implemented.</t>
-        </is>
-      </c>
-      <c r="X81" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>industry standards, operational procedures, risk safeguards, contingency plans, compliance checks</t>
-        </is>
-      </c>
-      <c r="Z81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA81" t="b">
-        <v>0</v>
-      </c>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr"/>
-      <c r="AC81" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC81" t="inlineStr"/>
       <c r="AD81" t="inlineStr"/>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="inlineStr"/>
       <c r="AJ81" t="inlineStr"/>
@@ -13355,12 +13115,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Identifies required cut‑over criteria and secures final sign‑off for the disaster recovery task.</t>
+          <t>Identifies cut‑over criteria and secures final sign‑off from stakeholders to confirm task completion.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>technical</t>
+          <t>interpersonal</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -13381,7 +13141,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>cut‑over criteria; cut‑over criteria plan; sign‑off process; task approval; plan validation</t>
+          <t>cut‑over criteria plan; sign‑off process; stakeholder approval; final task sign off; documentation</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -13391,54 +13151,22 @@
         </is>
       </c>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Cut‑over Sign‑off</t>
-        </is>
-      </c>
-      <c r="S82" t="b">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Identifies required cut‑over criteria and secures final sign‑off for the disaster recovery task.</t>
-        </is>
-      </c>
-      <c r="X82" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>cut‑over criteria, sign‑off process, task approval, plan validation, stakeholder confirmation</t>
-        </is>
-      </c>
-      <c r="Z82" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA82" t="b">
-        <v>0</v>
-      </c>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr"/>
-      <c r="AC82" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr"/>
@@ -13515,12 +13243,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Audit Report</t>
+          <t>Audit Report Preparation</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Prepares audit report and presents recommendations to stakeholders through formal presentations.</t>
+          <t>Prepares comprehensive audit reports and presents recommendations to stakeholders through formal presentations.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -13546,7 +13274,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>audit reporting; compliance documentation; presentation of findings; recommendations; risk assessment</t>
+          <t>audit reporting; risk assessment; compliance documentation; presentation of findings; recommendations</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -13568,7 +13296,7 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t>MIS re-refinement: Skill name 'Audit Report' is a noun and does not describe the actions 'prepare and present' indicated in the evidence</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -13605,9 +13333,13 @@
         </is>
       </c>
       <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF83" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>Skill name 'Audit Report' is a noun and does not describe the actions 'prepare and present' indicated in the evidence</t>
+        </is>
+      </c>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -13740,12 +13472,12 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Change Approval":3</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -13777,9 +13509,13 @@
         </is>
       </c>
       <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Approval' (approve) but evidence action is 'Obtain' approval; the name describes a different action than the evidence</t>
+        </is>
+      </c>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -13864,7 +13600,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Investigates built‑in and third‑party encryption tools and implements them to secure data systems.</t>
+          <t>Investigates built‑in and third‑party encryption tools, then implements them to secure data systems.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -13890,7 +13626,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>cryptography; key management; AES; data protection; encryption facility</t>
+          <t>cryptography; key management; AES; PKI; encryption facility</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -14062,7 +13798,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>information security; data classification; access control; file security categorisation; security labeling</t>
+          <t>information security; data classification; access control; security labeling; file security</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -14080,12 +13816,12 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U86" t="inlineStr"/>
       <c r="V86" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "File Security Categorisation":1</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
@@ -14199,12 +13935,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Password Guidelines</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Checks password strength with utilities, reviews policies, and tightens complexity requirements per guidelines.</t>
+          <t>Checks password strength with utilities, reviews policies, and reviews complexity requirements per guidelines.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -14252,7 +13988,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t>MIS re-refinement: Skill name 'Password Policy' implies creating or managing a policy, but evidence describes checking password strength and reviewing/tightening guidelines, a different activity</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -14285,9 +14021,13 @@
       </c>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>Skill name 'Password Policy' implies creating or managing a policy, but evidence describes checking password strength and reviewing/tightening guidelines, a different activity</t>
+        </is>
+      </c>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -14420,12 +14160,12 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Problem Solving":3</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -14445,9 +14185,13 @@
         <v>1</v>
       </c>
       <c r="AA88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>inherent in multiple other skills</t>
+        </is>
+      </c>
       <c r="AC88" t="b">
         <v>1</v>
       </c>
@@ -14544,7 +14288,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Reviews system logs and audit reports across hybrid environments to identify and report security threats.</t>
+          <t>Reviews system logs and audit reports across hybrid environments to identify and flag security threats.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -14629,13 +14373,9 @@
         </is>
       </c>
       <c r="AE89" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>Skill name 'Security Log' provides no verb and does not reflect evidence actions (access, review, identify)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -14769,7 +14509,7 @@
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr">
         <is>
-          <t>keep:2, "Security Procedures Evaluation":1</t>
+          <t>keep:2, "System Security Procedure Evaluation":1</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -14914,7 +14654,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>compliance; risk assessment; security policy; governance; recommendation</t>
+          <t>compliance; risk assessment; security policy; governance; security recommendation</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -15060,7 +14800,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Conducts user security spot checks following organisational policies.</t>
+          <t>Performs user security spot checks following organisational policies and procedures.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -15133,17 +14873,17 @@
         <v>1</v>
       </c>
       <c r="AA92" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>Security Procedure Evaluation (LLM verified, sim=0.78)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD92" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 3.1 Perform user spot checks according to organisational pol</t>
+        </is>
+      </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
@@ -15258,7 +14998,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>time management; task sequencing; workload planning; prioritisation techniques; self-management</t>
+          <t>time management; task sequencing; workload planning; prioritisation techniques; self‑management</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -15276,12 +15016,12 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>keep:1, "Task Prioritisation":1, "Workload Management":1</t>
+          <t>keep:0, "Task Management":1, "Task Prioritisation":1, "Self‑task Management":1</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -15422,7 +15162,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>technical writing; specifications; requirements analysis; compliance; recommendations</t>
+          <t>technical writing; specifications; requirements analysis; compliance; complex workplace documentation</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -15568,7 +15308,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Continuously monitors ICT systems and records identified security threats for response planning.</t>
+          <t>Continuously monitors ICT systems, records identified security threats, for response planning.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -15784,12 +15524,12 @@
         <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
-          <t>keep:2, "User Account Administration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
@@ -15952,7 +15692,7 @@
         <v>1</v>
       </c>
       <c r="T97" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -15961,7 +15701,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>keep:2, "Virus Checking Implementation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -16080,7 +15820,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Ensures displayed log‑on legal notices and system settings align with organisational and legislative compliance requirements.</t>
+          <t>Checks log‑on legal notices and system settings to ensure alignment with organisational and legislative compliance requirements.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -16102,11 +15842,11 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>legal notice compliance; logon display; legislation compliance; auditing; audit</t>
+          <t>legal notice compliance; legislation breaches; organisational standards; compliance monitoring; auditing</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -16116,54 +15856,22 @@
         </is>
       </c>
       <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>Legal Notice Auditing</t>
-        </is>
-      </c>
-      <c r="S98" t="b">
-        <v>0</v>
-      </c>
-      <c r="T98" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Ensures displayed log‑on legal notices and system settings align with organisational and legislative compliance requirements.</t>
-        </is>
-      </c>
-      <c r="X98" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>legal notice compliance, logon display, legislation compliance, organisational requirements, audit</t>
-        </is>
-      </c>
-      <c r="Z98" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA98" t="b">
-        <v>0</v>
-      </c>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr"/>
-      <c r="AC98" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC98" t="inlineStr"/>
       <c r="AD98" t="inlineStr"/>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE98" t="inlineStr"/>
       <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
       <c r="AI98" t="inlineStr"/>
       <c r="AJ98" t="inlineStr"/>
@@ -16245,7 +15953,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>The worker documents where security procedures are not followed and implements approved changes to system security.</t>
+          <t>Documents instances where security procedures are not followed and implements approved changes to ICT system security.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -16267,11 +15975,11 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>security procedures; non‑compliance documentation; change implementation; security changes; compliance monitoring</t>
+          <t>security non‑compliance documentation; change implementation; procedure adherence; security procedures; audit records</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -16281,54 +15989,22 @@
         </is>
       </c>
       <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>Security Procedure</t>
-        </is>
-      </c>
-      <c r="S99" t="b">
-        <v>0</v>
-      </c>
-      <c r="T99" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>The worker records where security procedures are not followed and implements approved changes to maintain system security.</t>
-        </is>
-      </c>
-      <c r="X99" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>security procedures, non‑compliance documentation, change implementation, system updates, compliance monitoring</t>
-        </is>
-      </c>
-      <c r="Z99" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA99" t="b">
-        <v>0</v>
-      </c>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
-      <c r="AC99" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC99" t="inlineStr"/>
       <c r="AD99" t="inlineStr"/>
-      <c r="AE99" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE99" t="inlineStr"/>
       <c r="AF99" t="inlineStr"/>
-      <c r="AG99" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
       <c r="AI99" t="inlineStr"/>
       <c r="AJ99" t="inlineStr"/>
@@ -16450,7 +16126,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>keep:2, "Research Report Drafting":1</t>
+          <t>keep:2, "Report Drafting":1</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -16551,12 +16227,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Data Analysis</t>
+          <t>Information Analysis</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Analyses stored data following a research strategy to support decision-making.</t>
+          <t>Analyses stored data following a research strategy for decision-making.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -16600,16 +16276,16 @@
         <v>1</v>
       </c>
       <c r="T101" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>keep:1, "Information Analysis":1, "Data Analysis":1</t>
+          <t>keep:0, "Information Analysis Synthesis":2, "Information Analysis":1</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -16629,17 +16305,17 @@
         <v>1</v>
       </c>
       <c r="AA101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB101" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>Theme Identification (LLM verified, sim=0.83)</t>
+        </is>
+      </c>
       <c r="AC101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD101" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 2.1 Access and extract relevant information in a format suit</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD101" t="inlineStr"/>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
@@ -16741,7 +16417,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>information retrieval; digital technology; digital research tools; data analysis; research software</t>
+          <t>information retrieval; digital technologies; digital research tools; data analysis; research software</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -16763,12 +16439,12 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>keep:1, "Digital Technology Utilisation/Digital Tool Utilisation":2</t>
+          <t>keep:0, "Digital Technology Utilisation/Technology Utilisation/Digital Tool Utilisation":3</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
@@ -16788,9 +16464,13 @@
         <v>1</v>
       </c>
       <c r="AA102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB102" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>Information Extraction (LLM verified, sim=0.79)</t>
+        </is>
+      </c>
       <c r="AC102" t="b">
         <v>0</v>
       </c>
@@ -16914,7 +16594,7 @@
         <v>1</v>
       </c>
       <c r="T103" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -16923,7 +16603,7 @@
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Conclusion Justification":1</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -17183,12 +16863,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Information Extraction Planning</t>
+          <t>Information Extraction</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Accesses and extracts relevant information in a format suitable for analysis and distribution.</t>
+          <t>Accesses and extracts relevant information, formatting it for analysis and distribution.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -17229,15 +16909,19 @@
         </is>
       </c>
       <c r="S105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" t="n">
         <v>0.9</v>
       </c>
-      <c r="U105" t="inlineStr"/>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Information Extraction":3</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
@@ -17269,13 +16953,9 @@
         </is>
       </c>
       <c r="AE105" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Planning' but evidence describes 'Access and extract' actions</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -17373,7 +17053,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>public speaking; audience analysis; persuasive communication; presentation design; visual aids</t>
+          <t>public speaking; audience analysis; persuasive communication; presentation design; oral presentation</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -17391,16 +17071,16 @@
         <v>1</v>
       </c>
       <c r="T106" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>keep:0, "Oral Presentation":3</t>
+          <t>keep:2, "Oral Presentation":1</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
@@ -17417,7 +17097,7 @@
         </is>
       </c>
       <c r="Z106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -17502,7 +17182,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Identifies and resolves anticipated issues within routine tasks using established procedures.</t>
+          <t>Identifies anticipated issues within routine tasks using established procedures.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -17528,7 +17208,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>troubleshooting; root cause analysis; process improvement; standard operating procedures; problem solving</t>
+          <t>troubleshooting; root cause analysis; process improvement; problem solving; familiar work contexts</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -17546,7 +17226,7 @@
         <v>1</v>
       </c>
       <c r="T107" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -17555,7 +17235,7 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Problem Solving":1</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
@@ -17564,7 +17244,7 @@
         </is>
       </c>
       <c r="X107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
@@ -17989,7 +17669,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>literature review; information retrieval; research design; relevance assessment; research strategy</t>
+          <t>literature review; information retrieval; research design; research strategy; academic databases</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -18272,7 +17952,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Self‑management Execution</t>
+          <t>Self‑management Planning</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -18303,7 +17983,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>task scheduling; prioritisation; goal setting; self‑management; execution</t>
+          <t>task scheduling; prioritisation; workflow optimisation; goal setting; self‑management</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -18318,19 +17998,15 @@
         </is>
       </c>
       <c r="S112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>keep:1, "Self‑management Execution":2</t>
+          <t>keep:2, "Task Planning":1</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -18458,7 +18134,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>information verification; bias assessment; citation analysis; media literacy; source reliability</t>
+          <t>information verification; bias assessment; citation analysis; reliability; source</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -18476,16 +18152,16 @@
         <v>1</v>
       </c>
       <c r="T113" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>keep:2, "Source Reliability Assessment":1</t>
+          <t>keep:1, "Source Reliability Assessment":2</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
@@ -18617,7 +18293,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>thematic analysis; pattern recognition; qualitative research; content coding; theme</t>
+          <t>thematic analysis; pattern recognition; qualitative research; content coding; research methodology</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -18661,7 +18337,7 @@
         </is>
       </c>
       <c r="Z114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -18750,7 +18426,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Identify reporting methods that align with the target audience and meet organisational requirements, and report accordingly.</t>
+          <t>Identifies reporting methods that align with the target audience and meet organisational standards and requirements.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -18776,7 +18452,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>reporting methods; intended audience; organisational requirements; method alignment; methodology</t>
+          <t>reporting methods; intended audience; organisational requirements; method selection; methodology</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -18785,54 +18461,22 @@
         </is>
       </c>
       <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>Audience Reporting Methodology</t>
-        </is>
-      </c>
-      <c r="S115" t="b">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>Select reporting methods that suit the target audience and meet organisational requirements effectively.</t>
-        </is>
-      </c>
-      <c r="X115" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>reporting methods, intended audience, organisational requirements, method alignment, reporting selection</t>
-        </is>
-      </c>
-      <c r="Z115" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA115" t="b">
-        <v>0</v>
-      </c>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr"/>
       <c r="AB115" t="inlineStr"/>
-      <c r="AC115" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC115" t="inlineStr"/>
       <c r="AD115" t="inlineStr"/>
-      <c r="AE115" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE115" t="inlineStr"/>
       <c r="AF115" t="inlineStr"/>
-      <c r="AG115" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
       <c r="AI115" t="inlineStr"/>
       <c r="AJ115" t="inlineStr"/>
@@ -18901,12 +18545,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>WHS Barrier</t>
+          <t>Barrier Identification</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Identifies and reports obstacles to consultation participation.</t>
+          <t>Identifies barriers to WHS consultation and participation, and reports obstacles to required personnel.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -18932,7 +18576,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>occupational health and safety; hazard identification; risk assessment; consultation barriers; safety culture</t>
+          <t>occupational health and safety; risk assessment; consultation barriers; safety culture; consultation processes</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -18954,7 +18598,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>MIS re-refinement: Skill name 'WHS Barrier' does not describe the actions 'identify and report' in the evidence</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -18976,7 +18620,7 @@
         </is>
       </c>
       <c r="Z116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -18987,9 +18631,13 @@
       </c>
       <c r="AD116" t="inlineStr"/>
       <c r="AE116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF116" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>Skill name 'WHS Barrier' does not describe the actions 'identify and report' in the evidence</t>
+        </is>
+      </c>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -19066,7 +18714,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Selects WHS consultation and communication methods aligned with organisational policies.</t>
+          <t>Selects WHS consultation and communication methods aligned to organisational policies.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -19092,7 +18740,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>WHS consultation; stakeholder engagement; communication channels; policy compliance; consultation methods</t>
+          <t>WHS consultation; stakeholder engagement; communication channels; policy compliance; WHS consultation methods</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -19252,7 +18900,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>occupational health and safety; stakeholder engagement; WHS legislation compliance; safety committee facilitation; WHS consultation</t>
+          <t>occupational health and safety; stakeholder engagement; WHS legislation compliance; risk management; consultation</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -19430,12 +19078,12 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>keep:1, "WHS Issue Raising":2</t>
+          <t>keep:0, "WHS Issue Raising":3</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
@@ -19537,12 +19185,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Meeting Outcomes</t>
+          <t>Outcome Follow-up</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Follows up post‑meeting actions according to role responsibilities and company policies.</t>
+          <t>Follows up post‑meeting actions by tracking outcomes in line with role responsibilities and company policies.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -19568,7 +19216,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>meeting coordination; outcome tracking; policy compliance; stakeholder communication; action item management</t>
+          <t>follow up meeting; outcome tracking; policy compliance; stakeholder communication; action item management</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -19590,12 +19238,12 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Coordination' which is not the action described in evidence; evidence calls for 'Follow up' of meeting outcomes</t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>keep:2, "Meeting Outcome Follow-up":1</t>
+          <t>keep:0, "Outcome Follow-up":3</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
@@ -19612,7 +19260,7 @@
         </is>
       </c>
       <c r="Z120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -19627,13 +19275,9 @@
         </is>
       </c>
       <c r="AE120" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Coordination' which is not the action described in evidence; evidence calls for 'Follow up' of meeting outcomes</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -19736,7 +19380,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>WHS communication; policy compliance; stakeholder messaging; plain language writing; WHS information</t>
+          <t>WHS communication; risk communication; policy compliance; plain language writing; WHS information</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -20025,12 +19669,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Solution Suggestion</t>
+          <t>Suggestion Development</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Makes suggestions to eliminate barriers, enhancing workplace health and safety consultations.</t>
+          <t>Makes actionable suggestions to eliminate barriers, enhancing workplace health and safety consultations.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -20074,16 +19718,16 @@
         <v>1</v>
       </c>
       <c r="T123" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>keep:2, "Suggestion Development":1</t>
+          <t>keep:0, "Suggestion Development":2, "Barrier Solution Suggestion":1</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
@@ -20107,13 +19751,9 @@
       </c>
       <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 2.3 Make suggestions that could assist in removing identifie</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD123" t="inlineStr"/>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
@@ -20247,7 +19887,7 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>keep:0, "WHS Stakeholder Identification/Stakeholder Identification":3</t>
+          <t>keep:0, "Stakeholder Identification":3</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
@@ -20358,7 +19998,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Records WHS discussions and communicates outcomes in line with organisational policies.</t>
+          <t>Documents WHS discussions and disseminates outcomes in line with organisational policies.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -20402,16 +20042,16 @@
         <v>1</v>
       </c>
       <c r="T125" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>keep:0, "WHS discussion documentation":3</t>
+          <t>keep:1, "WHS discussion communication":1, "WHS Discussion Documentation":1</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
@@ -20420,7 +20060,7 @@
         </is>
       </c>
       <c r="X125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y125" t="inlineStr">
         <is>
@@ -20513,12 +20153,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>WHS Understanding Confirmation</t>
+          <t>WHS Understanding Verification</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Participates in confirming personnel comprehension of WHS information, instructions and signs.</t>
+          <t>Participates in confirming personnel understanding of WHS information, instructions and signs.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -20544,7 +20184,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>occupational health and safety; hazard communication; safety compliance; understanding; confirmation</t>
+          <t>occupational health and safety; hazard communication; safety compliance; training verification; understanding</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -20562,16 +20202,16 @@
         <v>1</v>
       </c>
       <c r="T126" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name 'WHS Information' does not describe the action of confirming understanding present in the evidence</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>keep:1, "WHS Understanding Verification":1, "WHS Information Understanding":1</t>
+          <t>keep:0, "WHS Understanding Verification":2, "WHS Understanding Confirmation":1</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
@@ -20595,21 +20235,13 @@
       </c>
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 3.3 Participate in confirming that required personnel unders</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD126" t="inlineStr"/>
       <c r="AE126" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>Skill name 'WHS Information' does not describe the action of confirming understanding present in the evidence</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -20681,12 +20313,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>WHS Legislative</t>
+          <t>WHS Obligations</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Researches and collates WHS legislative obligations on communication and consultation for organisational compliance.</t>
+          <t>Researches WHS legislative obligations on communication and consultation for organisational compliance.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -20712,7 +20344,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>occupational health and safety legislation; compliance analysis; risk assessment; consultation and communication processes; regulatory research tools</t>
+          <t>occupational health and safety legislation; compliance analysis; risk assessment; consultation and communication processes; WHS obligations</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -20730,16 +20362,16 @@
         <v>1</v>
       </c>
       <c r="T127" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t>MIS re-refinement: Skill name 'WHS Legislative' does not describe the evidence actions 'research and collate', indicating the name does not reflect the activity</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "WHS Obligations Research":1</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
@@ -20756,22 +20388,26 @@
         </is>
       </c>
       <c r="Z127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
       </c>
       <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD127" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 1.3 Research and collate information on organisational WHS o</t>
+        </is>
+      </c>
       <c r="AE127" t="b">
         <v>1</v>
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>Skill name 'WHS Legislative' does not describe an action; evidence involves researching and collating legislative obligations</t>
+          <t>Skill name 'WHS Legislative' does not describe the evidence actions 'research and collate', indicating the name does not reflect the activity</t>
         </is>
       </c>
       <c r="AG127" t="b">
@@ -20876,7 +20512,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>forms of communication; communication methods; required individuals; form selection; appropriate channels</t>
+          <t>communication methods; required individuals; form selection; stakeholder communication; forms of communication</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -20885,54 +20521,22 @@
         </is>
       </c>
       <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>Communication Form Selection</t>
-        </is>
-      </c>
-      <c r="S128" t="b">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>Selects the most suitable communication methods for each required individual or party in WHS contexts.</t>
-        </is>
-      </c>
-      <c r="X128" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>communication methods, required individuals, WHS context, form selection, appropriate channels</t>
-        </is>
-      </c>
-      <c r="Z128" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA128" t="b">
-        <v>0</v>
-      </c>
+      <c r="W128" t="inlineStr"/>
+      <c r="X128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr"/>
+      <c r="Z128" t="inlineStr"/>
+      <c r="AA128" t="inlineStr"/>
       <c r="AB128" t="inlineStr"/>
-      <c r="AC128" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC128" t="inlineStr"/>
       <c r="AD128" t="inlineStr"/>
-      <c r="AE128" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE128" t="inlineStr"/>
       <c r="AF128" t="inlineStr"/>
-      <c r="AG128" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
       <c r="AI128" t="inlineStr"/>
       <c r="AJ128" t="inlineStr"/>
@@ -21006,7 +20610,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Communicates WHS meeting outcomes to required individuals and parties promptly and clearly, ensuring understanding and follow‑up.</t>
+          <t>Communicates WHS meeting outcomes to required individuals or parties using appropriate channels and formats.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -21032,7 +20636,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>WHS outcomes; meeting communication; required individuals; stakeholder notification; outcome dissemination</t>
+          <t>WHS outcomes; meeting minutes; required individuals; communication channels; follow-up actions</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -21041,54 +20645,22 @@
         </is>
       </c>
       <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>WHS Outcome Communication</t>
-        </is>
-      </c>
-      <c r="S129" t="b">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>Communicates WHS meeting outcomes to required individuals and parties promptly and clearly, ensuring understanding and follow‑up.</t>
-        </is>
-      </c>
-      <c r="X129" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>WHS outcomes, meeting communication, required individuals, stakeholder notification, outcome dissemination</t>
-        </is>
-      </c>
-      <c r="Z129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="b">
-        <v>0</v>
-      </c>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr"/>
+      <c r="AA129" t="inlineStr"/>
       <c r="AB129" t="inlineStr"/>
-      <c r="AC129" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC129" t="inlineStr"/>
       <c r="AD129" t="inlineStr"/>
-      <c r="AE129" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE129" t="inlineStr"/>
       <c r="AF129" t="inlineStr"/>
-      <c r="AG129" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
       <c r="AI129" t="inlineStr"/>
       <c r="AJ129" t="inlineStr"/>
@@ -21369,15 +20941,19 @@
         </is>
       </c>
       <c r="S131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U131" t="inlineStr"/>
+        <v>0.925</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>keep:2, "Device Configuration Backup":1</t>
+          <t>keep:1, "Device Configuration Backup":2</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
@@ -21491,7 +21067,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Determines required firewall configurations for hybrid environments according to organisational requirements.</t>
+          <t>Determines required firewall security according to organisational requirements for hybrid environments.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -21817,7 +21393,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tests penetration attempts and verifies network perimeter compliance with security standards.</t>
+          <t>Tests penetration tests and verifies network perimeter compliance with security standards.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -21843,7 +21419,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>penetration testing; vulnerability assessment; red team operations; Metasploit; perimeter validation</t>
+          <t>cybersecurity; vulnerability assessment; red team operations; perimeter validation; penetration testing</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -21861,16 +21437,16 @@
         <v>1</v>
       </c>
       <c r="T134" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>keep:1, "Penetration Testing":2</t>
+          <t>keep:2, "Penetration Testing":1</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
@@ -22010,7 +21586,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>network security; firewall implementation; security appliances; perimeter device deployment; security policy compliance</t>
+          <t>network security; firewall implementation; security appliances; intrusion detection systems; perimeter device deployment</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -22138,12 +21714,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Perimeter Security</t>
+          <t>Perimeter Security Options</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Researches perimeter security solutions against organisational requirements in hybrid environments.</t>
+          <t>Researches and identifies perimeter security options according to organisational requirements in hybrid environments.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -22169,7 +21745,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>network security; firewall; intrusion detection; security assessment; perimeter security</t>
+          <t>network security; firewall; intrusion detection; security assessment; perimeter security options</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -22187,16 +21763,16 @@
         <v>1</v>
       </c>
       <c r="T136" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t>MIS re-refinement: Skill name 'Perimeter Security' does not describe the action in the evidence (research and identify options)</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Perimeter Security Options Research":1</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
@@ -22216,21 +21792,25 @@
         <v>1</v>
       </c>
       <c r="AA136" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>Security Perimeter</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD136" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 1.3 Research and identify available perimeter security optio</t>
+        </is>
+      </c>
       <c r="AE136" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF136" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>Skill name 'Perimeter Security' does not describe the action in the evidence (research and identify options)</t>
+        </is>
+      </c>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -22336,7 +21916,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>perimeter security; IPsec; SSL/TLS tunneling; network authentication; remote access</t>
+          <t>perimeter security; IPsec; SSL/TLS tunneling; remote access; firewall configuration</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -22354,7 +21934,7 @@
         <v>1</v>
       </c>
       <c r="T137" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -22363,7 +21943,7 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Remote Access VPN Configuration":1</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
@@ -22387,9 +21967,13 @@
       </c>
       <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD137" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 4.2 Configure perimeter as a remote access VPN server</t>
+        </is>
+      </c>
       <c r="AE137" t="b">
         <v>0</v>
       </c>
@@ -22554,13 +22138,9 @@
         </is>
       </c>
       <c r="AC138" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 1.2 Determine required firewall security according to organi</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD138" t="inlineStr"/>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
@@ -22729,13 +22309,9 @@
         </is>
       </c>
       <c r="AE139" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>Skill name lacks the action verb present in evidence (evidence requires 'Identify' but name is just 'Security Threat')</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -22815,7 +22391,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Designs and configures perimeter solutions for service continuity during device upgrades in hybrid environments.</t>
+          <t>Designs and configures perimeter solutions to enable service continuity during device upgrades in hybrid environments.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -22868,7 +22444,7 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>keep:1, "Service Continuity Design":2</t>
+          <t>keep:1, "Service Continuity Enablement":2</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
@@ -22982,7 +22558,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Configures network perimeter devices for site‑to‑site VPN tunnels.</t>
+          <t>Configures network perimeter devices for site-to-site VPN tunnels.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -23059,13 +22635,9 @@
       </c>
       <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 4.1 Configure perimeter for site-to-site virtual private net</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD141" t="inlineStr"/>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
@@ -23202,7 +22774,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>keep:0, "Performance Documentation/Performance Results Documentation":3</t>
+          <t>keep:0, "Performance Results Documentation/Performance Documentation":3</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
@@ -23505,7 +23077,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>IPsec; SSL VPN; site-to-site; tunnel forwarding; NAT traversal</t>
+          <t>IPsec; SSL VPN; site-to-site; NAT traversal; tunnel forwarding</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -23523,7 +23095,7 @@
         <v>1</v>
       </c>
       <c r="T144" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -23642,7 +23214,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Test basic firewall and VPN features to ensure they meet defined network security requirements.</t>
+          <t>Tests basic firewall and VPN features to ensure they meet defined security requirements.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -23664,11 +23236,11 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>basic feature testing; network security requirements; functionality verification; security perimeter; test execution</t>
+          <t>basic feature verification; security requirement compliance; functional testing; network security validation; functionality</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -23677,54 +23249,22 @@
         </is>
       </c>
       <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>Feature Functionality Testing</t>
-        </is>
-      </c>
-      <c r="S145" t="b">
-        <v>0</v>
-      </c>
-      <c r="T145" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>Conduct practical tests to verify basic firewall and VPN features meet defined network security requirements.</t>
-        </is>
-      </c>
-      <c r="X145" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>basic feature testing, network security requirements, functionality verification, security perimeter, test execution</t>
-        </is>
-      </c>
-      <c r="Z145" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA145" t="b">
-        <v>0</v>
-      </c>
+      <c r="W145" t="inlineStr"/>
+      <c r="X145" t="inlineStr"/>
+      <c r="Y145" t="inlineStr"/>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr"/>
       <c r="AB145" t="inlineStr"/>
-      <c r="AC145" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC145" t="inlineStr"/>
       <c r="AD145" t="inlineStr"/>
-      <c r="AE145" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr"/>
-      <c r="AG145" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
       <c r="AI145" t="inlineStr"/>
       <c r="AJ145" t="inlineStr"/>
@@ -23830,16 +23370,16 @@
         <v>1</v>
       </c>
       <c r="T146" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Design' action not present in evidence which only 'Recognises' principles</t>
+          <t>MIS re-refinement: Skill name uses 'Design' but evidence only describes 'Recognises' principles</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Digital Tool Design Recognition":1</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
@@ -23871,7 +23411,7 @@
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>Skill name uses 'Design' action not present in evidence which only 'Recognises' principles</t>
+          <t>Skill name uses 'Design' but evidence only describes 'Recognises' principles</t>
         </is>
       </c>
       <c r="AG146" t="b">
@@ -23938,7 +23478,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Identifies and documents emerging technologies and practices relevant to organisational context.</t>
+          <t>Identifies and documents emerging technologies and practices, ensuring relevance to organisational needs.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -23982,7 +23522,7 @@
         <v>1</v>
       </c>
       <c r="T147" t="n">
-        <v>0.925</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -23991,7 +23531,7 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>keep:2, "Emerging Technology Identification":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
@@ -24127,19 +23667,15 @@
         </is>
       </c>
       <c r="S148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>keep:1, "Industry Terminology Translation/Terminology Translation":2</t>
+          <t>keep:2, "Terminology Translation":1</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
@@ -24234,7 +23770,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Accesses IT industry sources to stay informed on emerging technologies.</t>
+          <t>Accesses relevant IT industry sources to stay informed on emerging technologies.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -24260,7 +23796,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>technology scouting; IT industry trends; information retrieval; information source; information access</t>
+          <t>technology scouting; IT industry trends; information retrieval; emerging tech monitoring; access sources</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -24282,12 +23818,12 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Assessment' while evidence action is 'Access'</t>
+          <t>MIS re-refinement: Skill name uses 'Assessment' but evidence action is 'Access'</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>keep:2, "Information Source Evaluation":1</t>
+          <t>keep:2, "Information Source Access":1</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -24323,7 +23859,7 @@
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>Skill name uses 'Assessment' while evidence action is 'Access'</t>
+          <t>Skill name uses 'Assessment' but evidence action is 'Access'</t>
         </is>
       </c>
       <c r="AG149" t="b">
@@ -24475,7 +24011,7 @@
       </c>
       <c r="AF150" t="inlineStr">
         <is>
-          <t>Skill name 'IT Industry' does not describe an action and does not match the evidence action 'Discusses'</t>
+          <t>Skill name 'IT Industry' does not describe an action; evidence action is 'Discusses'</t>
         </is>
       </c>
       <c r="AG150" t="b">
@@ -24537,12 +24073,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Organisational Change</t>
+          <t>Change Documentation</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Identifies and documents changes to organisational technologies and practices required based on strategies.</t>
+          <t>Identifies changes to required technology and practice, documenting them for implementation.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -24568,7 +24104,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>change management; technology adoption; organisational change; stakeholder analysis; process redesign</t>
+          <t>change management; technology adoption; strategic roadmap; stakeholder analysis; document changes</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -24586,16 +24122,16 @@
         <v>1</v>
       </c>
       <c r="T151" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>keep:2, "Organisational Change Identification":1</t>
+          <t>keep:1, "Change Documentation/Organisational Change Documentation":2</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
@@ -24619,13 +24155,9 @@
       </c>
       <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 3.2 Identify and document changes to organisational technolo</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD151" t="inlineStr"/>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
@@ -24720,7 +24252,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>continuous learning; career development; learning &amp; development; professional recognition; professional development</t>
+          <t>continuous learning; career development; learning &amp; development; CPD opportunities; professional recognition</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -24738,12 +24270,12 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Professional Development Opportunity Recognition":1</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
@@ -24838,7 +24370,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Takes personal responsibility for ensuring work complies with applicable laws and regulations by following procedures.</t>
+          <t>Ensures personal work complies with applicable laws and regulations by following procedures.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -24864,7 +24396,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>legal obligations; risk management; governance frameworks; compliance management systems; regulatory responsibility</t>
+          <t>legal obligations; governance frameworks; compliance management systems; regulatory responsibility; personal responsibility</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -24981,7 +24513,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Information Application</t>
+          <t>Information Evaluation</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -25012,7 +24544,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>literature review; critical appraisal; academic databases; citation management; information application</t>
+          <t>literature review; critical appraisal; academic databases; citation management; technical documentation</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -25039,7 +24571,7 @@
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>keep:0, "Information Application":2, "Information Evaluation":1</t>
+          <t>keep:0, "Information Evaluation":2, "Information Application":1</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
@@ -25129,12 +24661,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Risk Opportunity</t>
+          <t>Opportunity Threat</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Risk and opportunity analysis of emerging technologies regarding organisational impacts.</t>
+          <t>Risk and opportunity analysis of emerging technologies to organisational impacts.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -25160,7 +24692,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>risk assessment; opportunity identification; emerging technology impact; threat modeling; technology and practice</t>
+          <t>opportunity identification; emerging technology impact; threat modeling; strategic scenario planning; opportunities and threats</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -25178,16 +24710,16 @@
         <v>1</v>
       </c>
       <c r="T155" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t>MIS re-refinement: Skill name uses 'Analysis' but evidence only describes potential opportunities and threats without any analysis action</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>keep:2, "Opportunity Threat Analysis":1</t>
+          <t>keep:1, "Opportunity Threat Analysis":2</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
@@ -25215,9 +24747,13 @@
       </c>
       <c r="AD155" t="inlineStr"/>
       <c r="AE155" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF155" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Analysis' but evidence only describes potential opportunities and threats without any analysis action</t>
+        </is>
+      </c>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -25460,7 +24996,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>technology foresight; scenario planning; change management; digital transformation strategy; emerging technology</t>
+          <t>emerging technology; technology foresight; scenario planning; change management; digital transformation strategy</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -25482,12 +25018,12 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>keep:1, "Strategy Development":2</t>
+          <t>keep:0, "Strategy Development":3</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -25608,7 +25144,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>technical manuals; engineering drawings; specification sheets; diagram analysis; technical documentation</t>
+          <t>technical documentation; technical manuals; engineering drawings; specification sheets; diagram analysis</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -25882,7 +25418,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Uses proven methods to implement technology solutions on schedule.</t>
+          <t>Uses proven methods to technology solutions on schedule.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -25930,12 +25466,12 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>keep:0, "Technology Strategy Planning/Technology Adoption Planning":2, "Technology Impact Evaluation":1</t>
+          <t>keep:0, "Technology Strategy Planning/Emerging Technology Strategy Planning":3</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
@@ -26035,7 +25571,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Abstract Script</t>
+          <t>Abstract Design</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -26066,7 +25602,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>script development; code abstraction; modular design; abstract; design patterns</t>
+          <t>abstract design; code abstraction; modular design; software architecture; design patterns</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -26084,16 +25620,16 @@
         <v>1</v>
       </c>
       <c r="T161" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>keep:2, "Abstract Design":1</t>
+          <t>keep:0, "Abstract Design Creation":2, "Abstract Design":1</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
@@ -26228,7 +25764,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>algorithm; computational thinking; data structures; complexity analysis; pseudocode</t>
+          <t>computational thinking; data structures; complexity analysis; pseudocode; algorithm</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -26364,7 +25900,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Develops algorithms that cover all possible situations and demonstrates guaranteed termination in theoretical models.</t>
+          <t>Develops algorithms covering all cases and proves guaranteed termination in theoretical models.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -26390,7 +25926,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>algorithm analysis; termination proof; formal verification; theoretical computer science; possible situations</t>
+          <t>algorithm analysis; termination proof; formal verification; computational complexity; possible situations</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -26408,7 +25944,7 @@
         <v>1</v>
       </c>
       <c r="T163" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -26417,7 +25953,7 @@
       </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Algorithm Termination Design":1</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
@@ -26530,7 +26066,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Identifies applicable procedures for system design from automation guidelines and instructions.</t>
+          <t>Identifies automation guidelines and instructions applicable to system procedures.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -26574,16 +26110,16 @@
         <v>1</v>
       </c>
       <c r="T164" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>MIS re-refinement: Skill name uses 'Interpretation' which is not present in evidence action 'Identify'</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>keep:0, "Automation Guideline Identification/Automation Guidelines Identification":3</t>
+          <t>keep:2, "Automation Guideline Identification":1</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
@@ -26607,13 +26143,21 @@
       </c>
       <c r="AB164" t="inlineStr"/>
       <c r="AC164" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD164" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 1.2 Identify automation guidelines and instructions</t>
+        </is>
+      </c>
       <c r="AE164" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF164" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>Skill name uses 'Interpretation' which is not present in evidence action 'Identify'</t>
+        </is>
+      </c>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -26714,7 +26258,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>static analysis; code review; semantic checking; script; verification</t>
+          <t>static analysis; code review; semantic checking; linting; script verification</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -26761,17 +26305,17 @@
         <v>1</v>
       </c>
       <c r="AA165" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB165" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>Code Debugging (LLM verified, sim=0.73)</t>
+        </is>
+      </c>
       <c r="AC165" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 4.2 Identify any areas that are not covered and any areas th</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD165" t="inlineStr"/>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
@@ -26850,7 +26394,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Checks scripts and amends syntax and semantic errors to ensure functional code.</t>
+          <t>Checks scripts for syntax and semantic errors to ensure functional code.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -26898,12 +26442,12 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>keep:0, "Code Debugging":3</t>
+          <t>keep:0, "Code Debugging":2, "Script Error Debugging":1</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
@@ -27060,12 +26604,12 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>keep:1, "Team Collaboration":2</t>
+          <t>keep:0, "Team Collaboration":3</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
@@ -27085,17 +26629,17 @@
         <v>0</v>
       </c>
       <c r="AA167" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>Feedback Incorporation (LLM verified, sim=0.77)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB167" t="inlineStr"/>
       <c r="AC167" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD167" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>FS capability overlaps PC1.3 Discuss and establish potential solutions with team members</t>
+        </is>
+      </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
@@ -27169,7 +26713,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Feedback Acquisition</t>
+          <t>Feedback Sign‑off</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -27200,7 +26744,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>stakeholder engagement; sign‑off workflow; feedback loop; collaboration tools; acquisition</t>
+          <t>stakeholder engagement; sign‑off workflow; feedback loop; collaboration tools; hybrid communication</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -27227,7 +26771,7 @@
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>keep:0, "Feedback Incorporation":2, "Feedback Sign-off":1</t>
+          <t>keep:0, "Feedback Incorporation":3</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
@@ -27244,7 +26788,7 @@
         </is>
       </c>
       <c r="Z168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -27335,7 +26879,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Formula Processing</t>
+          <t>Numerical Formula Manipulation</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -27366,7 +26910,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>algebraic manipulation; formula processing; mathematical modeling; symbolic computation; numerical methods</t>
+          <t>algebraic manipulation; formula manipulation; mathematical modeling; symbolic computation; numerical methods</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -27381,19 +26925,15 @@
         </is>
       </c>
       <c r="S169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T169" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>keep:1, "Formula Processing":2</t>
+          <t>keep:0, "Complex Formula Manipulation":1, "Formula Processing":1, "Formula Interpretation and Manipulation":1</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
@@ -27579,13 +27119,9 @@
       </c>
       <c r="AB170" t="inlineStr"/>
       <c r="AC170" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 1.1 Identify process requiring automation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD170" t="inlineStr"/>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
@@ -27659,7 +27195,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Script Development</t>
+          <t>Script Coding</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -27690,7 +27226,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>scripting; automation; code development; programming languages; script</t>
+          <t>scripting; automation; code development; software engineering; programming languages</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -27708,16 +27244,16 @@
         <v>1</v>
       </c>
       <c r="T171" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>keep:1, "Script Development":2</t>
+          <t>keep:2, "Script Implementation":1</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
@@ -27734,7 +27270,7 @@
         </is>
       </c>
       <c r="Z171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -27852,7 +27388,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>collaborative ideation; requirements gathering; problem‑solving facilitation; remote teamwork; solution</t>
+          <t>collaborative ideation; requirements gathering; problem‑solving facilitation; remote teamwork; virtual whiteboard tools</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -27875,7 +27411,7 @@
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>keep:0, "Collaborative Solution Ideation":1, "Team Solution Discussion":1, "Solution Brainstorming":1</t>
+          <t>keep:0, "Collaborative Solution Development":1, "Solution Discussion":1, "Solution Brainstorming":1</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
@@ -27892,20 +27428,20 @@
         </is>
       </c>
       <c r="Z172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA172" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB172" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>Team Collaboration (LLM verified, sim=0.79)</t>
+        </is>
+      </c>
       <c r="AC172" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 1.3 Discuss and establish potential solutions and process id</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD172" t="inlineStr"/>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
@@ -27984,7 +27520,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Analyses complex technical documentation and amends inconsistencies and errors to ensure accuracy.</t>
+          <t>Analyses complex technical documentation and amends inconsistencies and errors.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -28010,7 +27546,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>documentation review; error correction; technical writing standards; quality assurance; inconsistencies</t>
+          <t>documentation review; error correction; technical writing standards; quality assurance; technical documentation</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -28028,16 +27564,16 @@
         <v>1</v>
       </c>
       <c r="T173" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>keep:1, "Technical Documentation Review":2</t>
+          <t>keep:2, "Technical Documentation Review":1</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
@@ -28146,7 +27682,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Creates internal technical documents following organisational guidelines and policies to ensure consistency.</t>
+          <t>Produces internal technical documents following organisational guidelines and policies to ensure consistency.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -28172,7 +27708,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>technical writing; internal documentation; SOP; documentation standards; knowledge base</t>
+          <t>technical writing; SOP; documentation standards; internal documentation; knowledge base</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -28208,7 +27744,7 @@
         </is>
       </c>
       <c r="X174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y174" t="inlineStr">
         <is>
@@ -28223,13 +27759,9 @@
       </c>
       <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 3.5 Create internal documentation according to organisationa</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD174" t="inlineStr"/>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
@@ -28334,7 +27866,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>technical writing; user guides; API documentation; technical documentation; documentation tools</t>
+          <t>technical writing; user guides; API documentation; documentation tools; technical documentation</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -28356,12 +27888,12 @@
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>keep:1, "Documentation Preparation":2</t>
+          <t>keep:0, "Documentation Preparation":3</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
@@ -28385,9 +27917,13 @@
       </c>
       <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD175" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 4.4 Create and finalise user-level and technical level docum</t>
+        </is>
+      </c>
       <c r="AE175" t="b">
         <v>0</v>
       </c>
@@ -28466,7 +28002,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Describes algorithmic solutions for identified problems using sequence, selection, and iteration structures.</t>
+          <t>The worker describes algorithmic solutions for the identified problem using sequence, selection, and iteration structures.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -28492,7 +28028,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>algorithmic solution; sequence structure; selection structure; iteration structure; problem description</t>
+          <t>algorithm description; sequence structures; selection structures; iteration structures; algorithmic solutions</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -28501,54 +28037,22 @@
         </is>
       </c>
       <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>Algorithmic Solution</t>
-        </is>
-      </c>
-      <c r="S176" t="b">
-        <v>0</v>
-      </c>
-      <c r="T176" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>Describes algorithmic solutions for identified problems using sequence, selection, and iteration structures.</t>
-        </is>
-      </c>
-      <c r="X176" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>algorithmic solution, sequence structure, selection structure, iteration structure, problem description</t>
-        </is>
-      </c>
-      <c r="Z176" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA176" t="b">
-        <v>0</v>
-      </c>
+      <c r="W176" t="inlineStr"/>
+      <c r="X176" t="inlineStr"/>
+      <c r="Y176" t="inlineStr"/>
+      <c r="Z176" t="inlineStr"/>
+      <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr"/>
-      <c r="AC176" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC176" t="inlineStr"/>
       <c r="AD176" t="inlineStr"/>
-      <c r="AE176" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE176" t="inlineStr"/>
       <c r="AF176" t="inlineStr"/>
-      <c r="AG176" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
       <c r="AI176" t="inlineStr"/>
       <c r="AJ176" t="inlineStr"/>
@@ -28615,12 +28119,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Abstract Design Translation</t>
+          <t>Abstract Design Revision</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Reviews abstract designs, amends omissions and errors, and translates them into code following organisational guidelines.</t>
+          <t>Reviews abstract designs, corrects omissions and errors, and translates them into code following organisational guidelines.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -28638,7 +28142,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>practical</t>
+          <t>theoretical</t>
         </is>
       </c>
       <c r="N177" t="n">
@@ -28646,7 +28150,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>abstract design; error amendment; language translation; organisational guidelines; omissions</t>
+          <t>abstract design review; error amendment; design translation; organisational guidelines; revision</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -28656,54 +28160,22 @@
         </is>
       </c>
       <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr">
-        <is>
-          <t>Abstract Design Translation</t>
-        </is>
-      </c>
-      <c r="S177" t="b">
-        <v>0</v>
-      </c>
-      <c r="T177" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>Reviews abstract designs, amends omissions and errors, and translates them into code following organisational guidelines.</t>
-        </is>
-      </c>
-      <c r="X177" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>abstract design, design review, error amendment, language translation, organisational guidelines</t>
-        </is>
-      </c>
-      <c r="Z177" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA177" t="b">
-        <v>0</v>
-      </c>
+      <c r="W177" t="inlineStr"/>
+      <c r="X177" t="inlineStr"/>
+      <c r="Y177" t="inlineStr"/>
+      <c r="Z177" t="inlineStr"/>
+      <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr"/>
-      <c r="AC177" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="inlineStr"/>
-      <c r="AE177" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE177" t="inlineStr"/>
       <c r="AF177" t="inlineStr"/>
-      <c r="AG177" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
       <c r="AI177" t="inlineStr"/>
       <c r="AJ177" t="inlineStr"/>
@@ -28775,7 +28247,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Confirms identified problems with team members and collaboratively resolves issues as required.</t>
+          <t>Confirms identified problems with team members and resolves issues as required during the automation process.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -28801,7 +28273,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>problem identification; team communication; issue resolution; collaborative confirmation; team members</t>
+          <t>problem confirmation; team communication; issue resolution; collaborative verification; team members</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -28810,54 +28282,22 @@
         </is>
       </c>
       <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr">
-        <is>
-          <t>Problem Confirmation</t>
-        </is>
-      </c>
-      <c r="S178" t="b">
-        <v>0</v>
-      </c>
-      <c r="T178" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>Confirms identified problems with team members and collaboratively resolves issues as required.</t>
-        </is>
-      </c>
-      <c r="X178" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>problem identification, team communication, issue resolution, collaborative confirmation, stakeholder engagement</t>
-        </is>
-      </c>
-      <c r="Z178" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA178" t="b">
-        <v>0</v>
-      </c>
+      <c r="W178" t="inlineStr"/>
+      <c r="X178" t="inlineStr"/>
+      <c r="Y178" t="inlineStr"/>
+      <c r="Z178" t="inlineStr"/>
+      <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
-      <c r="AC178" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC178" t="inlineStr"/>
       <c r="AD178" t="inlineStr"/>
-      <c r="AE178" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE178" t="inlineStr"/>
       <c r="AF178" t="inlineStr"/>
-      <c r="AG178" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
       <c r="AI178" t="inlineStr"/>
       <c r="AJ178" t="inlineStr"/>
@@ -28977,12 +28417,12 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Active Listening":3</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
@@ -29160,17 +28600,17 @@
         <v>1</v>
       </c>
       <c r="AA180" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB180" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>Log Analysis (LLM verified, sim=0.77)</t>
+        </is>
+      </c>
       <c r="AC180" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 5.1 Design and document auditing and incidents response proc</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD180" t="inlineStr"/>
       <c r="AE180" t="b">
         <v>0</v>
       </c>
@@ -29298,7 +28738,7 @@
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>keep:2, "Logging Analysis":1</t>
+          <t>keep:1, "Security Audit Execution":1, "Security Audit":1</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
@@ -29429,7 +28869,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>vulnerability scanning; CVE database; NIST standards; penetration testing; network vulnerability</t>
+          <t>network vulnerability; vulnerability scanning; NIST standards; penetration testing; risk assessment</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -29591,7 +29031,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>ethical hacking; vulnerability assessment; Metasploit; Nmap; penetration testing</t>
+          <t>ethical hacking; vulnerability assessment; exploit development; penetration testing; testing techniques</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -29609,16 +29049,16 @@
         <v>1</v>
       </c>
       <c r="T183" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>keep:0, "Penetration Testing":2, "Security Audit Execution":1</t>
+          <t>keep:0, "Penetration Testing":1, "Security Testing Execution":1, "Penetration Testing Technique":1</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
@@ -29727,7 +29167,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Designs and determines risk management components based on network security design specifications in hybrid environments.</t>
+          <t>Determines risk management components based on network security design specifications in hybrid environments.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -29771,7 +29211,7 @@
         <v>1</v>
       </c>
       <c r="T184" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
@@ -29966,13 +29406,17 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>Threat Modelling (LLM verified, sim=0.81)</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="AC185" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD185" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 3.3 Categorise and document assets and determine their value</t>
+        </is>
+      </c>
       <c r="AE185" t="b">
         <v>0</v>
       </c>
@@ -30051,7 +29495,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Tests security controls using penetration testing methods to detect vulnerabilities.</t>
+          <t>Tests security controls using penetration testing methods to identify vulnerabilities.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -30077,7 +29521,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>penetration testing; vulnerability assessment; audit; Metasploit; risk assessment</t>
+          <t>penetration testing; vulnerability assessment; audit; risk assessment; security measures</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -30099,12 +29543,12 @@
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V186" t="inlineStr">
         <is>
-          <t>keep:1, "Security Audit Testing":1, "Security Testing Execution":1</t>
+          <t>keep:1, "Security Audit Testing":2</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
@@ -30253,12 +29697,12 @@
         <v>0</v>
       </c>
       <c r="T187" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>keep:1, "Security Control Assessment":1, "Security Controls Planning":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
@@ -30440,7 +29884,7 @@
       </c>
       <c r="AD188" t="inlineStr">
         <is>
-          <t>FS activity mirrors PC3.3 which determines asset value, so cost calculation is embedded in the PC</t>
+          <t>FS activity mirrors PC3.3 (determine asset value) and does not add a distinct skill</t>
         </is>
       </c>
       <c r="AE188" t="b">
@@ -30547,7 +29991,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>network security; security architecture; security policy compliance; threat modeling; security design</t>
+          <t>network security; security architecture; security design; security policy compliance; threat modeling</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -30565,7 +30009,7 @@
         <v>1</v>
       </c>
       <c r="T189" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U189" t="inlineStr">
         <is>
@@ -30574,7 +30018,7 @@
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Security Design Planning":1</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
@@ -30598,9 +30042,13 @@
       </c>
       <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD189" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 1.1 Define planning phase for network security design accord</t>
+        </is>
+      </c>
       <c r="AE189" t="b">
         <v>0</v>
       </c>
@@ -30679,7 +30127,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Develops and documents security policies across hybrid environments, in line with organisational standards.</t>
+          <t>Develops and documents security policies across hybrid environments; technical controls and organizational standards.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -30705,7 +30153,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>information security; policy management; compliance frameworks; ISO 27001; security policies</t>
+          <t>information security; policy management; compliance frameworks; ISO 27001; document security</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -30832,7 +30280,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Security Data Analysis</t>
+          <t>Security Analysis</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -30863,7 +30311,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>cybersecurity; threat intelligence; SIEM tools; data aggregation; data analysis</t>
+          <t>cybersecurity; threat intelligence; SIEM tools; data aggregation; digital tools</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -30890,7 +30338,7 @@
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>keep:0, "Security Data Analysis/Security Analysis":2, "Security Problem Solving":1</t>
+          <t>keep:1, "Security Analysis/Security Data Analysis":2</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
@@ -30914,7 +30362,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>Security Controls Evaluation (LLM verified, sim=0.72)</t>
+          <t>Log Analysis (LLM verified, sim=0.73)</t>
         </is>
       </c>
       <c r="AC191" t="b">
@@ -30999,7 +30447,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Develops and documents technical information with factual data and industry terms to plan organisational plans, policies and breach documentation.</t>
+          <t>Develops, documents and plans technical information with factual data and industry terms to produce plans, policies, breach reports.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -31025,7 +30473,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>technical writing; security policy documentation; incident reporting; compliance standards; security breaches</t>
+          <t>technical writing; security policy documentation; incident reporting; security breaches; documentation tools</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -31043,7 +30491,7 @@
         <v>1</v>
       </c>
       <c r="T192" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U192" t="inlineStr">
         <is>
@@ -31052,7 +30500,7 @@
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Security Documentation Writing":1</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
@@ -31080,7 +30528,7 @@
       </c>
       <c r="AD192" t="inlineStr">
         <is>
-          <t>FS evidence restates PC4.3 (Develop and document security policies) verbatim</t>
+          <t>FS implicit in PCs — covered by: 4.3 Develop and document security policies</t>
         </is>
       </c>
       <c r="AE192" t="b">
@@ -31187,7 +30635,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>network security; attack surface analysis; STRIDE methodology; security architecture; threat modelling</t>
+          <t>network security; attack surface analysis; STRIDE methodology; security architecture; threat model</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -31238,13 +30686,9 @@
       </c>
       <c r="AB193" t="inlineStr"/>
       <c r="AC193" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 2.2 Determine the potential origin of major threats accordin</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD193" t="inlineStr"/>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
@@ -31323,7 +30767,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Identifies organisational assets that require protection.</t>
+          <t>Identifies organisational assets that require protection for network security planning.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -31349,7 +30793,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>asset inventory; critical assets; protection requirements; organisational resources; assets requiring protection</t>
+          <t>organisational assets; protection requirements; asset inventory; critical resources; assets requiring protection</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -31358,54 +30802,22 @@
         </is>
       </c>
       <c r="Q194" t="inlineStr"/>
-      <c r="R194" t="inlineStr">
-        <is>
-          <t>Asset Identification</t>
-        </is>
-      </c>
-      <c r="S194" t="b">
-        <v>0</v>
-      </c>
-      <c r="T194" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr"/>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>Identifies and records organisational assets that require protection to support security design and risk management.</t>
-        </is>
-      </c>
-      <c r="X194" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>asset inventory, critical assets, protection requirements, organisational resources, security baseline</t>
-        </is>
-      </c>
-      <c r="Z194" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA194" t="b">
-        <v>0</v>
-      </c>
+      <c r="W194" t="inlineStr"/>
+      <c r="X194" t="inlineStr"/>
+      <c r="Y194" t="inlineStr"/>
+      <c r="Z194" t="inlineStr"/>
+      <c r="AA194" t="inlineStr"/>
       <c r="AB194" t="inlineStr"/>
-      <c r="AC194" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC194" t="inlineStr"/>
       <c r="AD194" t="inlineStr"/>
-      <c r="AE194" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE194" t="inlineStr"/>
       <c r="AF194" t="inlineStr"/>
-      <c r="AG194" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG194" t="inlineStr"/>
       <c r="AH194" t="inlineStr"/>
       <c r="AI194" t="inlineStr"/>
       <c r="AJ194" t="inlineStr"/>
@@ -31477,7 +30889,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Documents security information for designated personnel, seeks feedback and submits responses for improvement.</t>
+          <t>Submit security documents to designated personnel and seek and address their feedback.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -31512,54 +30924,22 @@
         </is>
       </c>
       <c r="Q195" t="inlineStr"/>
-      <c r="R195" t="inlineStr">
-        <is>
-          <t>Document Distribution</t>
-        </is>
-      </c>
-      <c r="S195" t="b">
-        <v>0</v>
-      </c>
-      <c r="T195" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr"/>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>Distributes security documents to designated personnel, actively seeks feedback and responds to comments for improvement.</t>
-        </is>
-      </c>
-      <c r="X195" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>document distribution, feedback solicitation, stakeholder communication, revision handling, security documentation</t>
-        </is>
-      </c>
-      <c r="Z195" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA195" t="b">
-        <v>0</v>
-      </c>
+      <c r="W195" t="inlineStr"/>
+      <c r="X195" t="inlineStr"/>
+      <c r="Y195" t="inlineStr"/>
+      <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="inlineStr"/>
       <c r="AB195" t="inlineStr"/>
-      <c r="AC195" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC195" t="inlineStr"/>
       <c r="AD195" t="inlineStr"/>
-      <c r="AE195" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE195" t="inlineStr"/>
       <c r="AF195" t="inlineStr"/>
-      <c r="AG195" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr"/>
       <c r="AI195" t="inlineStr"/>
       <c r="AJ195" t="inlineStr"/>
@@ -31821,7 +31201,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>configuration; metrics-driven scaling; infrastructure as code; virtual machine scaling; autoscaling</t>
+          <t>cloud infrastructure; autoscaling; metrics-driven scaling; configuration; virtual machine scaling</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -31950,7 +31330,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Compares hybrid cloud options and discusses models and services against business requirements.</t>
+          <t>Discusses hybrid cloud options by comparing models and services against business requirements.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -31976,7 +31356,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>cloud computing; service models; cloud solution; Azure; cost-benefit analysis</t>
+          <t>cloud computing; service models; Azure; cost-benefit analysis; cloud computing solution</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -32139,7 +31519,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>active listening; constructive feedback; communication skills; feedback response; feedback loop</t>
+          <t>active listening; constructive feedback; communication skills; feedback loop; feedback response</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -32166,7 +31546,7 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>keep:0, "Feedback Response":3</t>
+          <t>keep:0, "Feedback Response/Feedback Seeking and Response":3</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
@@ -32276,7 +31656,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Deploys managed databases into virtual networks, managing configuration to meet business requirements.</t>
+          <t>Deploys managed databases into virtual networks, managing configuration with business requirements.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -32302,7 +31682,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>cloud database; virtual network; Azure SQL Database; DBaaS; managed database deployment</t>
+          <t>database deployment; virtual network; Azure SQL Database; infrastructure as code; DBaaS</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -32590,7 +31970,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Plans and implements routine tasks, making limited decisions on sequencing, timing and collaboration.</t>
+          <t>Plans routine tasks and implements workload sequencing, timing and limited collaboration.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -32631,19 +32011,15 @@
         </is>
       </c>
       <c r="S202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>MIS re-refinement: Skill name uses 'Management' which is not an action verb present in the evidence (evidence describes planning, implementing, and limited decision‑making)</t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>keep:0, "Routine Task Management":3</t>
+          <t>keep:2, "Routine Task Management":1</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
@@ -32671,13 +32047,9 @@
       </c>
       <c r="AD202" t="inlineStr"/>
       <c r="AE202" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>Skill name uses 'Management' which is not an action verb present in the evidence (evidence describes planning, implementing, and limited decision‑making)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -32753,7 +32125,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Tests automatic scaling and fixes errors to ensure performance reliability.</t>
+          <t>Tests automatic scaling to ensure performance reliability.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -32801,12 +32173,12 @@
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>keep:0, "Autoscaling Testing":2, "Scaling Test":1</t>
+          <t>keep:0, "Autoscaling Testing":3</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
@@ -32960,7 +32332,7 @@
         <v>1</v>
       </c>
       <c r="T204" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U204" t="inlineStr">
         <is>
@@ -32969,7 +32341,7 @@
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>keep:2, "Security Responsibility Assessment":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
@@ -32989,13 +32361,9 @@
         <v>1</v>
       </c>
       <c r="AA204" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>Security Responsibility</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB204" t="inlineStr"/>
       <c r="AC204" t="b">
         <v>1</v>
       </c>
@@ -33109,7 +32477,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>stakeholder management; documentation; reporting; liaison; work</t>
+          <t>stakeholder management; documentation; reporting; work; liaison</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -33131,12 +32499,12 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>keep:0, "Work Communication":2, "Work Documentation":1</t>
+          <t>keep:0, "Work Communication":3</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
@@ -33246,7 +32614,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Defines, adds and expands VM storage volumes to meet business requirements.</t>
+          <t>Defines, adds, and expands VM storage volumes to meet business requirements.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -33290,7 +32658,7 @@
         <v>1</v>
       </c>
       <c r="T206" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U206" t="inlineStr">
         <is>
@@ -33299,7 +32667,7 @@
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>keep:2, "Storage Allocation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
@@ -33405,7 +32773,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Documents and communicates clear technical information to relevant personnel for project alignment.</t>
+          <t>Documents work and communicates it to relevant personnel for project alignment.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -33431,7 +32799,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>technical writing; documentation standards; communication; collaboration tools; user manuals</t>
+          <t>technical writing; documentation standards; collaboration tools; user manuals; communication</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -33453,12 +32821,12 @@
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>keep:0, "Documentation Preparation":3</t>
+          <t>keep:1, "Documentation Preparation":2</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
@@ -33478,13 +32846,9 @@
         <v>1</v>
       </c>
       <c r="AA207" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>Work Communication</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB207" t="inlineStr"/>
       <c r="AC207" t="b">
         <v>1</v>
       </c>
@@ -33598,7 +32962,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>virtual machine; hypervisor; infrastructure as code; OS deployment; virtualization platform</t>
+          <t>hypervisor; virtual machine; infrastructure as code; OS deployment; virtualization platform</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -33731,7 +33095,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Creates multi‑tier virtual networks that support core services and enable autoscaling.</t>
+          <t>Creates a multi‑tier virtual network that supports core services and enables autoscaling.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -33920,7 +33284,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>capacity planning; business requirements analysis; resource allocation; workload management tools; workload definition</t>
+          <t>capacity planning; business requirements analysis; resource allocation; workload definition; workload management tools</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -33942,12 +33306,12 @@
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Workload Definition":3</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
@@ -34052,12 +33416,12 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Security Responsibility</t>
+          <t>Security Role Assignment</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Identifies and allocates security duties based on policies, business protocols and specific work functions.</t>
+          <t>Identifies and allocates security responsibilities in line with policies, business protocols and work functions.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -34079,11 +33443,11 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>security responsibilities; security policies; business protocols; work function; responsibility allocation</t>
+          <t>security responsibilities; policy compliance; role allocation; business protocols; work function</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -34092,54 +33456,22 @@
         </is>
       </c>
       <c r="Q211" t="inlineStr"/>
-      <c r="R211" t="inlineStr">
-        <is>
-          <t>Security Responsibility</t>
-        </is>
-      </c>
-      <c r="S211" t="b">
-        <v>0</v>
-      </c>
-      <c r="T211" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr"/>
-      <c r="W211" t="inlineStr">
-        <is>
-          <t>Identifies and allocates security duties based on policies, business protocols and specific work functions.</t>
-        </is>
-      </c>
-      <c r="X211" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y211" t="inlineStr">
-        <is>
-          <t>security responsibilities, security policies, business protocols, work function, responsibility allocation</t>
-        </is>
-      </c>
-      <c r="Z211" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA211" t="b">
-        <v>0</v>
-      </c>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr"/>
+      <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="inlineStr"/>
       <c r="AB211" t="inlineStr"/>
-      <c r="AC211" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC211" t="inlineStr"/>
       <c r="AD211" t="inlineStr"/>
-      <c r="AE211" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE211" t="inlineStr"/>
       <c r="AF211" t="inlineStr"/>
-      <c r="AG211" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr"/>
       <c r="AI211" t="inlineStr"/>
       <c r="AJ211" t="inlineStr"/>
@@ -34212,7 +33544,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Creates users and groups to manage cloud infrastructure per business needs.</t>
+          <t>Creates users and groups to manage access to cloud infrastructure per business needs.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -34238,7 +33570,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>user creation; group configuration; access control; infrastructure management; cloud environment</t>
+          <t>cloud users; access groups; infrastructure permissions; business requirements; identity configuration</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -34247,54 +33579,22 @@
         </is>
       </c>
       <c r="Q212" t="inlineStr"/>
-      <c r="R212" t="inlineStr">
-        <is>
-          <t>User Group Management</t>
-        </is>
-      </c>
-      <c r="S212" t="b">
-        <v>0</v>
-      </c>
-      <c r="T212" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>Creates and configures users and groups to control access and manage cloud infrastructure per business needs.</t>
-        </is>
-      </c>
-      <c r="X212" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>user creation, group configuration, access control, infrastructure management, cloud environment</t>
-        </is>
-      </c>
-      <c r="Z212" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA212" t="b">
-        <v>0</v>
-      </c>
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr"/>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
       <c r="AB212" t="inlineStr"/>
-      <c r="AC212" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr"/>
-      <c r="AE212" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE212" t="inlineStr"/>
       <c r="AF212" t="inlineStr"/>
-      <c r="AG212" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr"/>
       <c r="AI212" t="inlineStr"/>
       <c r="AJ212" t="inlineStr"/>
@@ -34393,7 +33693,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>document storage; organisational policy; archival process; compliance; repository management</t>
+          <t>document storage; repository management; version control; compliance; archiving</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -34402,54 +33702,22 @@
         </is>
       </c>
       <c r="Q213" t="inlineStr"/>
-      <c r="R213" t="inlineStr">
-        <is>
-          <t>Documentation Archiving</t>
-        </is>
-      </c>
-      <c r="S213" t="b">
-        <v>0</v>
-      </c>
-      <c r="T213" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>Stores user documentation in designated repositories in line with organisational policies and procedures.</t>
-        </is>
-      </c>
-      <c r="X213" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>document storage, organisational policy, archival process, compliance, repository management</t>
-        </is>
-      </c>
-      <c r="Z213" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA213" t="b">
-        <v>0</v>
-      </c>
+      <c r="W213" t="inlineStr"/>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr"/>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
       <c r="AB213" t="inlineStr"/>
-      <c r="AC213" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC213" t="inlineStr"/>
       <c r="AD213" t="inlineStr"/>
-      <c r="AE213" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE213" t="inlineStr"/>
       <c r="AF213" t="inlineStr"/>
-      <c r="AG213" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG213" t="inlineStr"/>
       <c r="AH213" t="inlineStr"/>
       <c r="AI213" t="inlineStr"/>
       <c r="AJ213" t="inlineStr"/>
@@ -34526,7 +33794,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Performs scheduled data backups and restores systems using defined recovery procedures.</t>
+          <t>Executes scheduled data backups and restores systems using defined recovery procedures.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -34588,7 +33856,7 @@
         </is>
       </c>
       <c r="X214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y214" t="inlineStr">
         <is>
@@ -34684,7 +33952,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Directory Service Configuration</t>
+          <t>Directory Service Administration</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -34715,7 +33983,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>Active Directory; LDAP; group policy; directory service; service configuration</t>
+          <t>Active Directory; LDAP; identity management; access control; directory service administration</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -34730,19 +33998,15 @@
         </is>
       </c>
       <c r="S215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T215" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
-          <t>keep:0, "Directory Service Configuration":3</t>
+          <t>keep:2, "Directory Service Configuration":1</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
@@ -34856,7 +34120,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Creates disk partitioning scheme, file systems and virtual memory according to business needs.</t>
+          <t>Creates disk partitioning scheme, file systems, and virtual memory according to business requirements.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -34882,7 +34146,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>disk partitioning; file system layout; logical volume management; partitioning tools; virtual memory management</t>
+          <t>storage architecture; file system layout; disk; partitioning tools; virtual memory management</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -34900,7 +34164,7 @@
         <v>1</v>
       </c>
       <c r="T216" t="n">
-        <v>0.95</v>
+        <v>0.925</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -35067,12 +34331,12 @@
         <v>0</v>
       </c>
       <c r="T217" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Equipment Disposal Compliance":1</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
@@ -35216,7 +34480,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>e-waste compliance; asset disposition; recycling procedures; inventory decommissioning; equipment</t>
+          <t>e-waste compliance; asset disposition; equipment disposal; recycling procedures; inventory decommissioning</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -35238,12 +34502,12 @@
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Equipment Disposal":3</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
@@ -35352,7 +34616,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Server Service Configuration</t>
+          <t>Network Service Configuration</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -35383,7 +34647,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>network operating system; server application deployment; configuration; system installation; network services (DHCP; DNS; VPN)</t>
+          <t>network operating system; server application deployment; network service configuration; system installation; network services (DHCP; DNS; VPN)</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -35398,19 +34662,15 @@
         </is>
       </c>
       <c r="S219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T219" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U219" t="inlineStr"/>
       <c r="V219" t="inlineStr">
         <is>
-          <t>keep:0, "Server Service Configuration/Server Configuration":3</t>
+          <t>keep:1, "Network Service Setup":1, "Server Configuration":1</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
@@ -35434,9 +34694,13 @@
       </c>
       <c r="AB219" t="inlineStr"/>
       <c r="AC219" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD219" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 2.2 Install and configure network operating system, server a</t>
+        </is>
+      </c>
       <c r="AE219" t="b">
         <v>0</v>
       </c>
@@ -35515,12 +34779,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Patch Execution</t>
+          <t>Patch Management Execution</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Operates patch management to maintain operating system and applications in line with security and reliability requirements.</t>
+          <t>Operates patch management to meet security and reliability standards for operating systems and applications.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -35546,7 +34810,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>vulnerability remediation; OS and application updates; execution; configuration management; patch deployment tools</t>
+          <t>vulnerability remediation; OS and application updates; security compliance; configuration management; patch deployment tools</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -35561,19 +34825,15 @@
         </is>
       </c>
       <c r="S220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T220" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U220" t="inlineStr"/>
       <c r="V220" t="inlineStr">
         <is>
-          <t>keep:1, "Patch Execution":2</t>
+          <t>keep:1, "Patch Management":1, "Patch Implementation":1</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
@@ -35590,7 +34850,7 @@
         </is>
       </c>
       <c r="Z220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -35687,7 +34947,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Creates and manages user security and network permissions according to organisational policies.</t>
+          <t>Creates and manages user security and network permissions in line with organisational policies.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -35713,7 +34973,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>identity and access management; role‑based access control; user provisioning; authentication/authorization tools; network access</t>
+          <t>identity and access management; role‑based access control; network security policies; user provisioning; network access</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -35731,7 +34991,7 @@
         <v>1</v>
       </c>
       <c r="T221" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -35740,7 +35000,7 @@
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "User Access Management":1</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
@@ -36012,7 +35272,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Server Documentation</t>
+          <t>Server Documentation Preparation</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -36058,19 +35318,15 @@
         </is>
       </c>
       <c r="S223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T223" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
-          <t>keep:1, "Server Documentation":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
@@ -36179,12 +35435,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Server Installation</t>
+          <t>Server Requirements</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Identifies required server applications and features and prepares server installation.</t>
+          <t>Prepares server installations by identifying organisational needs and installing appropriate applications and features.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -36210,7 +35466,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>server deployment; application requirements; infrastructure planning; capacity sizing; server installation</t>
+          <t>server deployment; application requirements; infrastructure planning; capacity sizing; server applications</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -36232,7 +35488,7 @@
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Planning' which is not an action verb in the evidence (evidence verbs are 'Prepare' and 'Identify')</t>
+          <t>MIS re-refinement: Skill name uses 'Planning' which is not an action verb in the evidence (evidence verbs are 'prepare' and 'identify')</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
@@ -36261,19 +35517,15 @@
       </c>
       <c r="AB224" t="inlineStr"/>
       <c r="AC224" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 1.1 Identify required server applications and features accor</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD224" t="inlineStr"/>
       <c r="AE224" t="b">
         <v>1</v>
       </c>
       <c r="AF224" t="inlineStr">
         <is>
-          <t>Skill name uses 'Planning' which is not an action verb in the evidence (evidence verbs are 'Prepare' and 'Identify')</t>
+          <t>Skill name uses 'Planning' which is not an action verb in the evidence (evidence verbs are 'prepare' and 'identify')</t>
         </is>
       </c>
       <c r="AG224" t="b">
@@ -36548,7 +35800,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>IT infrastructure; network diagnostics; system administration; troubleshooting; server</t>
+          <t>server; network diagnostics; system administration; troubleshooting; hardware failure</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -36711,7 +35963,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>stakeholder engagement; communication planning; site access coordination; deployment scheduling; downtime notification</t>
+          <t>stakeholder engagement; site access coordination; deployment scheduling; downtime notification; advise users</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -36755,7 +36007,7 @@
         </is>
       </c>
       <c r="Z227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -36852,7 +36104,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Configures and operates user environments using OS policies and scripts to automate settings.</t>
+          <t>Configures user environments by operating OS policies and scripts to automate settings.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -37014,12 +36266,12 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Connectivity Reconfiguration</t>
+          <t>Connectivity Device Reconfiguration</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Reinstalls and adjusts network connectivity devices to restore and optimise server communication links.</t>
+          <t>Reconnects and reconfigures network connectivity devices to ensure proper communication after changes.</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -37041,11 +36293,11 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>network devices; reconnection; configuration; connectivity; reconfiguration</t>
+          <t>network devices; connectivity configuration; device reconnection; reconfiguration; hardware settings</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -37054,54 +36306,22 @@
         </is>
       </c>
       <c r="Q229" t="inlineStr"/>
-      <c r="R229" t="inlineStr">
-        <is>
-          <t>Connectivity Reconfiguration</t>
-        </is>
-      </c>
-      <c r="S229" t="b">
-        <v>0</v>
-      </c>
-      <c r="T229" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R229" t="inlineStr"/>
+      <c r="S229" t="inlineStr"/>
+      <c r="T229" t="inlineStr"/>
+      <c r="U229" t="inlineStr"/>
       <c r="V229" t="inlineStr"/>
-      <c r="W229" t="inlineStr">
-        <is>
-          <t>Reinstalls and adjusts network connectivity devices to restore and optimise server communication links.</t>
-        </is>
-      </c>
-      <c r="X229" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>network devices, reconnection, configuration, server links, optimisation</t>
-        </is>
-      </c>
-      <c r="Z229" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA229" t="b">
-        <v>0</v>
-      </c>
+      <c r="W229" t="inlineStr"/>
+      <c r="X229" t="inlineStr"/>
+      <c r="Y229" t="inlineStr"/>
+      <c r="Z229" t="inlineStr"/>
+      <c r="AA229" t="inlineStr"/>
       <c r="AB229" t="inlineStr"/>
-      <c r="AC229" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC229" t="inlineStr"/>
       <c r="AD229" t="inlineStr"/>
-      <c r="AE229" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE229" t="inlineStr"/>
       <c r="AF229" t="inlineStr"/>
-      <c r="AG229" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG229" t="inlineStr"/>
       <c r="AH229" t="inlineStr"/>
       <c r="AI229" t="inlineStr"/>
       <c r="AJ229" t="inlineStr"/>
@@ -37173,12 +36393,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Server Performance Feedback</t>
+          <t>Server Performance</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Seeks feedback on server performance from required personnel and responds as needed.</t>
+          <t>Seeks feedback on server performance from required personnel and responds promptly.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -37204,7 +36424,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>server performance feedback; stakeholder input; corrective actions; performance monitoring; personnel</t>
+          <t>server performance feedback; stakeholder input; response actions; performance monitoring; feedback loop</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -37213,54 +36433,22 @@
         </is>
       </c>
       <c r="Q230" t="inlineStr"/>
-      <c r="R230" t="inlineStr">
-        <is>
-          <t>Server Performance Feedback</t>
-        </is>
-      </c>
-      <c r="S230" t="b">
-        <v>0</v>
-      </c>
-      <c r="T230" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R230" t="inlineStr"/>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>Collects feedback on server performance from required personnel and implements corrective actions as needed.</t>
-        </is>
-      </c>
-      <c r="X230" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>server performance feedback, stakeholder input, corrective actions, performance monitoring, communication</t>
-        </is>
-      </c>
-      <c r="Z230" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA230" t="b">
-        <v>0</v>
-      </c>
+      <c r="W230" t="inlineStr"/>
+      <c r="X230" t="inlineStr"/>
+      <c r="Y230" t="inlineStr"/>
+      <c r="Z230" t="inlineStr"/>
+      <c r="AA230" t="inlineStr"/>
       <c r="AB230" t="inlineStr"/>
-      <c r="AC230" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC230" t="inlineStr"/>
       <c r="AD230" t="inlineStr"/>
-      <c r="AE230" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE230" t="inlineStr"/>
       <c r="AF230" t="inlineStr"/>
-      <c r="AG230" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG230" t="inlineStr"/>
       <c r="AH230" t="inlineStr"/>
       <c r="AI230" t="inlineStr"/>
       <c r="AJ230" t="inlineStr"/>
@@ -37370,12 +36558,12 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>keep:1, "Collaborative Technology Identification":2</t>
+          <t>keep:0, "Collaborative Tool Identification/Collaborative Technology Identification":3</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
@@ -37465,12 +36653,12 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Virtual Collaboration Protocol</t>
+          <t>Conflict Mediation in Virtual Teams</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Mediates conflicting perspectives in remote teams using mediation techniques during virtual meetings.</t>
+          <t>Mediates differing viewpoints in remote teams using mediation techniques during virtual meetings.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -37496,7 +36684,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>virtual collaboration; conflict resolution; mediation techniques; remote team communication; protocol</t>
+          <t>virtual collaboration; conflict resolution; mediation techniques; remote team communication; digital meeting platforms</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -37511,19 +36699,15 @@
         </is>
       </c>
       <c r="S232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T232" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U232" t="inlineStr"/>
       <c r="V232" t="inlineStr">
         <is>
-          <t>keep:1, "Virtual Collaboration Protocol Development":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
@@ -37540,16 +36724,12 @@
         </is>
       </c>
       <c r="Z232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA232" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>Team Interaction (LLM verified, sim=0.65)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB232" t="inlineStr"/>
       <c r="AC232" t="b">
         <v>0</v>
       </c>
@@ -37648,7 +36828,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>security protocols; security policy; compliance standards; incident response; access control</t>
+          <t>risk assessment; security policy; security protocols; incident response; access control</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -37800,7 +36980,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>data integration; information retrieval; content management systems; metadata tagging; digital technology</t>
+          <t>data integration; information retrieval; content management systems; digital technology; cloud collaboration tools</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -38092,7 +37272,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>knowledge sharing; knowledge management; information governance; team collaboration; corporate policy compliance</t>
+          <t>knowledge management; information governance; team collaboration; corporate policy compliance; knowledge sharing</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -38115,7 +37295,7 @@
       <c r="U236" t="inlineStr"/>
       <c r="V236" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Knowledge Sharing Protocol Development":1, "Knowledge Sharing Protocol":1</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
@@ -38258,12 +37438,12 @@
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>keep:1, "Oral Communication":2</t>
+          <t>keep:0, "Oral Communication":3</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
@@ -38540,7 +37720,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>compliance governance; protocol audit; virtual collaboration; remote team coordination; digital workflow management</t>
+          <t>compliance governance; protocol audit; virtual collaboration; remote team coordination; virtual environments</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -38584,7 +37764,7 @@
         </is>
       </c>
       <c r="Z239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -38706,16 +37886,16 @@
         <v>1</v>
       </c>
       <c r="T240" t="n">
-        <v>0.9</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>keep:1, "Protocol Improvement Determination":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
@@ -38840,7 +38020,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>team communication protocols; role assignment; responsibility matrix; organizational roles; team members</t>
+          <t>team members; team communication protocols; role assignment; responsibility matrix; organizational roles</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -38867,7 +38047,7 @@
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>keep:1, "Roles and Responsibilities Definition":1, "Team Role Definition":1</t>
+          <t>keep:2, "Roles and Responsibilities Definition":1</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
@@ -38961,12 +38141,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Team Interaction</t>
+          <t>Teamwork Coordination</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Collaborates to facilitate group interaction and achieve shared outcomes.</t>
+          <t>Facilitates group interaction and collaborates on tasks and communication to achieve shared outcomes.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -38992,7 +38172,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>collaboration; group dynamics; facilitation; communication; team interaction</t>
+          <t>collaboration; teamwork; facilitation; communication; conflict resolution</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -39007,19 +38187,15 @@
         </is>
       </c>
       <c r="S242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T242" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U242" t="inlineStr"/>
       <c r="V242" t="inlineStr">
         <is>
-          <t>keep:0, "Team Interaction Facilitation/Group Interaction Facilitation":2, "Team Interaction Coordination":1</t>
+          <t>keep:0, "Team Collaboration":1, "Teamwork Facilitation":1, "Teamwork":1</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
@@ -39109,7 +38285,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Virtual Collaboration Compliance</t>
+          <t>Collaboration Protocol Compliance</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -39158,16 +38334,16 @@
         <v>1</v>
       </c>
       <c r="T243" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.9</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Collaboration Protocol Compliance Review/Virtual Collaboration Compliance Review":2</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
@@ -39187,21 +38363,13 @@
         <v>0</v>
       </c>
       <c r="AA243" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>Protocol Compliance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB243" t="inlineStr"/>
       <c r="AC243" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FS implicit in PCs — covered by: 2.2 Develop protocols to share knowledge collaboratively in </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD243" t="inlineStr"/>
       <c r="AE243" t="b">
         <v>0</v>
       </c>
@@ -39270,7 +38438,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Develops collaborative virtual knowledge‑sharing protocols according to task details and team goals.</t>
+          <t>Develops collaborative virtual knowledge‑sharing protocols in line with task details and team goals.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -39608,7 +38776,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>cybersecurity; intrusion detection; incident response; SIEM; data security</t>
+          <t>cybersecurity; intrusion detection; incident response; data compliance; data security</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -39635,7 +38803,7 @@
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>keep:1, "Data Security Monitoring/Security Monitoring":2</t>
+          <t>keep:1, "Data Security Monitoring":2</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
@@ -39667,9 +38835,13 @@
       </c>
       <c r="AD246" t="inlineStr"/>
       <c r="AE246" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF246" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>Skill name 'Data Security' does not describe the actions (manage, maintain, monitor) indicated in the evidence</t>
+        </is>
+      </c>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
@@ -39920,7 +39092,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>cryptography; security policy; encryption standards; implementation roadmap; encryption implementation strategy</t>
+          <t>cryptography; key management; encryption standards; implementation roadmap; encryption implementation strategy</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -39942,7 +39114,7 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name uses 'Implementation' but evidence describes planning, documenting, and submitting a strategy, not implementing</t>
+          <t>MIS re-refinement: Skill name 'Encryption Implementation' suggests carrying out encryption, but evidence describes planning, documenting, and submitting a strategy</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
@@ -39983,7 +39155,7 @@
       </c>
       <c r="AF248" t="inlineStr">
         <is>
-          <t>Skill name uses 'Implementation' but evidence describes planning, documenting, and submitting a strategy, not implementing</t>
+          <t>Skill name 'Encryption Implementation' suggests carrying out encryption, but evidence describes planning, documenting, and submitting a strategy</t>
         </is>
       </c>
       <c r="AG248" t="b">
@@ -40054,7 +39226,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Determines function and performance of encryption tools by measuring performance metrics in operational settings.</t>
+          <t>Determines encryption tools by measuring performance metrics in operational settings.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -40080,7 +39252,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>cryptography; encryption algorithms; performance benchmarking; security analysis; encryption technologies</t>
+          <t>cryptography; encryption algorithms; performance benchmarking; OpenSSL; encryption technologies</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -40131,17 +39303,17 @@
       </c>
       <c r="AB249" t="inlineStr"/>
       <c r="AC249" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD249" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 1.2 Obtain and review available range of encryption technolo</t>
+        </is>
+      </c>
       <c r="AE249" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>Skill name 'Encryption Performance' does not contain the action verb from evidence; it is a noun phrase that does not reflect the evidence verb 'Determine'</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="b">
         <v>0</v>
       </c>
@@ -40210,7 +39382,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Uses AES, DES, and other symmetric algorithms to provide secure data protection.</t>
+          <t>Uses AES, DES, and other symmetric algorithms to secure data protection schemes.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -40357,12 +39529,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Encryption Technology Evaluation</t>
+          <t>Encryption Implementation</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Evaluates encryption solutions and reports on implementation compliance.</t>
+          <t>Assesses encryption solutions and reports on implementation compliance.</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -40388,7 +39560,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>cryptography; encryption standards; key management; security assessment; encryption technology</t>
+          <t>cryptography; encryption standards; key management; encryption technologies; compliance</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
@@ -40403,15 +39575,19 @@
         </is>
       </c>
       <c r="S251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T251" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U251" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>keep:2, "Encryption Implementation Evaluation":1</t>
+          <t>keep:0, "Encryption Implementation Evaluation":3</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
@@ -40435,13 +39611,9 @@
       </c>
       <c r="AB251" t="inlineStr"/>
       <c r="AC251" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 3.1 Evaluate implementation of encryption technologies accor</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD251" t="inlineStr"/>
       <c r="AE251" t="b">
         <v>0</v>
       </c>
@@ -40514,7 +39686,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Seeks user feedback on encryption tools' functionality and performance.</t>
+          <t>Seeks user feedback on encryption tools' functionality and performance to inform improvements.</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -40562,12 +39734,12 @@
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Feedback Solicitation":3</t>
         </is>
       </c>
       <c r="W252" t="inlineStr">
@@ -40718,12 +39890,12 @@
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>keep:0, "Protocol Compliance":2, "Protocol Adherence":1</t>
+          <t>keep:0, "Protocol Compliance":3</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
@@ -40822,7 +39994,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Reports encryption analysis and submits notifications to affected users and staff of incident impacts.</t>
+          <t>Reports encryption analysis and submits notification of impact to affected users and staff.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -40870,12 +40042,12 @@
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name implies performing analysis, but evidence only involves submitting an analysis report and informing impact, not the analysis activity itself</t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Analysis Reporting/Encryption Impact Reporting":3</t>
+          <t>keep:0, "Encryption Impact Reporting/Encryption Analysis Reporting":3</t>
         </is>
       </c>
       <c r="W254" t="inlineStr">
@@ -40903,13 +40075,9 @@
       </c>
       <c r="AD254" t="inlineStr"/>
       <c r="AE254" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF254" t="inlineStr">
-        <is>
-          <t>Skill name implies performing analysis, but evidence only involves submitting an analysis report and informing impact, not the analysis activity itself</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF254" t="inlineStr"/>
       <c r="AG254" t="b">
         <v>0</v>
       </c>
@@ -41031,7 +40199,7 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Plan Creation":2, "Encryption Implementation Planning":1</t>
+          <t>keep:0, "Encryption Plan Creation":2, "Encryption Plan Development":1</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
@@ -41125,7 +40293,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Security Requirements</t>
+          <t>Security Needs</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -41156,7 +40324,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>cybersecurity; network security; data protection; compliance governance; computer network</t>
+          <t>cybersecurity; risk assessment; network security; data protection; security needs</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -41174,16 +40342,16 @@
         <v>1</v>
       </c>
       <c r="T256" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t>MIS re-refinement: Skill name 'Security Requirements' is a noun phrase with no action verb, does not reflect the evidence action 'Identify'</t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>keep:2, "Security Requirements Identification":1</t>
+          <t>keep:1, "Security Requirements Identification":2</t>
         </is>
       </c>
       <c r="W256" t="inlineStr">
@@ -41215,9 +40383,13 @@
         </is>
       </c>
       <c r="AE256" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF256" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>Skill name 'Security Requirements' is a noun phrase with no action verb, does not reflect the evidence action 'Identify'</t>
+        </is>
+      </c>
       <c r="AG256" t="b">
         <v>0</v>
       </c>
@@ -41281,12 +40453,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Communication Method</t>
+          <t>Communication Determination</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Determines the appropriate communication form, channel, and mode for tasks based on role responsibilities.</t>
+          <t>Determines appropriate communication form, channel, and mode for tasks based on role responsibilities.</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -41312,7 +40484,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>communication method; communication channels; role‑based messaging; collaboration tools; information flow</t>
+          <t>communication channels; stakeholder management; role‑based messaging; collaboration tools; mode of communication</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
@@ -41334,12 +40506,12 @@
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>MIS re-refinement: Skill name 'Communication Coordination' does not reflect evidence action of determining communication form, channel and mode</t>
+          <t>MIS re-refinement: Skill name uses 'Coordination' which does not match evidence action 'Determines' and the term does not appear in evidence or PCs</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>keep:1, "Communication Coordination":2</t>
+          <t>keep:0, "Communication Coordination":3</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
@@ -41371,7 +40543,7 @@
       </c>
       <c r="AF257" t="inlineStr">
         <is>
-          <t>Skill name 'Communication Coordination' does not reflect evidence action of determining communication form, channel and mode</t>
+          <t>Skill name uses 'Coordination' which does not match evidence action 'Determines' and the term does not appear in evidence or PCs</t>
         </is>
       </c>
       <c r="AG257" t="b">
@@ -41442,7 +40614,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Prepares workplace documents that incorporate an evaluation of technical information using specialised and cohesive language.</t>
+          <t>Prepares workplace documents using specialized, cohesive language.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -41593,7 +40765,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Connectivity Security Troubleshooting</t>
+          <t>Security Issue Troubleshooting</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -41624,7 +40796,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>network security; connectivity troubleshooting; security protocols; firewall configuration; debugging</t>
+          <t>network security; incident response; connectivity troubleshooting; security protocols; firewall configuration</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
@@ -41646,12 +40818,12 @@
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>keep:1, "Connectivity Security Troubleshooting/Connectivity and Security Troubleshooting":2</t>
+          <t>keep:0, "Security Issue Troubleshooting":3</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
@@ -41668,7 +40840,7 @@
         </is>
       </c>
       <c r="Z259" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -41776,7 +40948,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>encryption technologies; security policy analysis; user responsibility mapping; risk and compliance documentation; impact analysis</t>
+          <t>encryption technologies; role-based access control; security policy analysis; user responsibility mapping; impact analysis</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
@@ -41794,16 +40966,16 @@
         <v>1</v>
       </c>
       <c r="T260" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>keep:2, "User Impact Analysis":1</t>
+          <t>keep:1, "User Impact Analysis":2</t>
         </is>
       </c>
       <c r="W260" t="inlineStr">
@@ -41823,9 +40995,13 @@
         <v>1</v>
       </c>
       <c r="AA260" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB260" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>Encryption Impact</t>
+        </is>
+      </c>
       <c r="AC260" t="b">
         <v>1</v>
       </c>
@@ -41901,12 +41077,12 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Encryption Plan Review</t>
+          <t>Encryption Plan Feedback</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Seeks feedback on encryption plans from relevant personnel to meet organisational requirements.</t>
+          <t>Seeks feedback on the encryption plan from relevant personnel to meet organisational requirements.</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -41932,7 +41108,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>encryption plan; feedback collection; stakeholder response; proposed encryption plan; plan revision</t>
+          <t>encryption plan; feedback collection; stakeholder response; plan adjustment; encryption plan feedback</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
@@ -41941,54 +41117,22 @@
         </is>
       </c>
       <c r="Q261" t="inlineStr"/>
-      <c r="R261" t="inlineStr">
-        <is>
-          <t>Encryption Plan Review</t>
-        </is>
-      </c>
-      <c r="S261" t="b">
-        <v>0</v>
-      </c>
-      <c r="T261" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R261" t="inlineStr"/>
+      <c r="S261" t="inlineStr"/>
+      <c r="T261" t="inlineStr"/>
+      <c r="U261" t="inlineStr"/>
       <c r="V261" t="inlineStr"/>
-      <c r="W261" t="inlineStr">
-        <is>
-          <t>Collects and addresses feedback on encryption plans from relevant personnel to meet organisational requirements.</t>
-        </is>
-      </c>
-      <c r="X261" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y261" t="inlineStr">
-        <is>
-          <t>encryption plan, feedback collection, stakeholder response, organisational needs, plan revision</t>
-        </is>
-      </c>
-      <c r="Z261" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA261" t="b">
-        <v>0</v>
-      </c>
+      <c r="W261" t="inlineStr"/>
+      <c r="X261" t="inlineStr"/>
+      <c r="Y261" t="inlineStr"/>
+      <c r="Z261" t="inlineStr"/>
+      <c r="AA261" t="inlineStr"/>
       <c r="AB261" t="inlineStr"/>
-      <c r="AC261" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC261" t="inlineStr"/>
       <c r="AD261" t="inlineStr"/>
-      <c r="AE261" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE261" t="inlineStr"/>
       <c r="AF261" t="inlineStr"/>
-      <c r="AG261" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG261" t="inlineStr"/>
       <c r="AH261" t="inlineStr"/>
       <c r="AI261" t="inlineStr"/>
       <c r="AJ261" t="inlineStr"/>
@@ -42089,54 +41233,22 @@
         </is>
       </c>
       <c r="Q262" t="inlineStr"/>
-      <c r="R262" t="inlineStr">
-        <is>
-          <t>Encryption Issue</t>
-        </is>
-      </c>
-      <c r="S262" t="b">
-        <v>0</v>
-      </c>
-      <c r="T262" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>added from uncovered PCs</t>
-        </is>
-      </c>
+      <c r="R262" t="inlineStr"/>
+      <c r="S262" t="inlineStr"/>
+      <c r="T262" t="inlineStr"/>
+      <c r="U262" t="inlineStr"/>
       <c r="V262" t="inlineStr"/>
-      <c r="W262" t="inlineStr">
-        <is>
-          <t>Document encryption problems and compromises, then submit detailed reports to the organisational help desk support.</t>
-        </is>
-      </c>
-      <c r="X262" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y262" t="inlineStr">
-        <is>
-          <t>encryption issues, security compromises, help desk submission, documentation process, organisational reporting</t>
-        </is>
-      </c>
-      <c r="Z262" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA262" t="b">
-        <v>0</v>
-      </c>
+      <c r="W262" t="inlineStr"/>
+      <c r="X262" t="inlineStr"/>
+      <c r="Y262" t="inlineStr"/>
+      <c r="Z262" t="inlineStr"/>
+      <c r="AA262" t="inlineStr"/>
       <c r="AB262" t="inlineStr"/>
-      <c r="AC262" t="b">
-        <v>0</v>
-      </c>
+      <c r="AC262" t="inlineStr"/>
       <c r="AD262" t="inlineStr"/>
-      <c r="AE262" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE262" t="inlineStr"/>
       <c r="AF262" t="inlineStr"/>
-      <c r="AG262" t="b">
-        <v>1</v>
-      </c>
+      <c r="AG262" t="inlineStr"/>
       <c r="AH262" t="inlineStr"/>
       <c r="AI262" t="inlineStr"/>
       <c r="AJ262" t="inlineStr"/>

--- a/vet_skills_refined.xlsx
+++ b/vet_skills_refined.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>VPN; encryption; key exchange; IPsec; configuration</t>
+          <t>VPN; tunneling protocols; key exchange; ipsec; configuration</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>keep:1, "IKE/IPSec Configuration":2</t>
+          <t>keep:0, "IKE/IPSec Configuration":3</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Problem Response Initiative</t>
+          <t>Problem Response Initiation</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Initiates standard protocols to resolve issues promptly across stable and evolving work situations.</t>
+          <t>Initiates standard procedures to resolve issues promptly across stable and evolving work situations.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>standard operating procedures; adaptive response; process initiation; problem solving; initiative</t>
+          <t>standard operating procedures; troubleshooting; problem solving; adaptive response; changing contexts</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>keep:0, "Problem Response Initiative":2, "Problem Response Initiation":1</t>
+          <t>keep:0, "Problem Response Initiation":2, "Standard Procedure Initiation":1</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Creates and applies router audit rules, then monitors assets for security compliance.</t>
+          <t>Creates and applies router audit rules, then runs and monitors asset security compliance.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1112,15 +1112,19 @@
         </is>
       </c>
       <c r="S4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0.95</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>keep:2, "Router Audit Rule Creation":1</t>
+          <t>keep:1, "Network Router Auditing":2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1218,12 +1222,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Work Brief Confirmation</t>
+          <t>Security Procedures Planning</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Confirms work briefs and tasks with organisational security policies.</t>
+          <t>Confirms work briefs and tasks against organisational security policies.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1249,7 +1253,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>risk assessment; security policy compliance; procedural documentation; access control planning; work brief</t>
+          <t>risk assessment; security policy compliance; procedural documentation; procedures; access control planning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1276,7 +1280,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>keep:0, "Work Brief Confirmation":2, "Security Procedure Confirmation":1</t>
+          <t>keep:0, "Security Procedures Planning/Security Procedure Planning":2, "Work Brief Confirmation":1</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1378,12 +1382,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reading Industry Regulations</t>
+          <t>Industry Regulation Reading</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Gathers and interprets current industry regulations from multiple sources to ensure compliance.</t>
+          <t>Collects, interprets and analyses current industry regulations from multiple sources to ensure compliance.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1409,7 +1413,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>regulatory compliance; policy interpretation; industry standards; legal research; industry regulations</t>
+          <t>reading; regulatory compliance; policy interpretation; industry standards; legal research</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1424,15 +1428,19 @@
         </is>
       </c>
       <c r="S6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>keep:1, "Industry Regulation Analysis":1, "Industry Regulation Interpretation":1</t>
+          <t>keep:0, "Industry Regulation Reading":2, "Industry Regulations Analysis":1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1579,12 +1587,12 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Risk Identification Planning":1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1731,12 +1739,12 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>keep:2, "VPN Configuration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1838,7 +1846,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Security Documentation Development</t>
+          <t>System Settings Documentation Development</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1869,7 +1877,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>system configuration; compliance; policy management; access control; audit trail</t>
+          <t>system configuration; compliance; policy management; access control; system settings</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1884,15 +1892,19 @@
         </is>
       </c>
       <c r="S9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "System Settings Documentation Development/System Documentation Development":2</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1909,7 +1921,7 @@
         </is>
       </c>
       <c r="Z9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -1990,12 +2002,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Asset Security Monitoring</t>
+          <t>Security Monitoring Implementation</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Runs asset security monitoring tools to monitor threats.</t>
+          <t>Runs and monitors asset security monitoring tools to address threats.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2021,7 +2033,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>cybersecurity; asset monitoring; SIEM; intrusion detection; asset security monitoring</t>
+          <t>cybersecurity; asset monitoring; SIEM; intrusion detection; real-time alerting</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2036,19 +2048,15 @@
         </is>
       </c>
       <c r="S10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>keep:1, "Asset Security Monitoring":2</t>
+          <t>keep:0, "Asset Security Monitoring Execution":1, "Asset Security Monitoring":1, "Asset Security Monitoring Implementation":1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -2065,7 +2073,7 @@
         </is>
       </c>
       <c r="Z10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="b">
         <v>1</v>
@@ -2150,7 +2158,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Self‑management of Security Tasks</t>
+          <t>Security Task Self‑management</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2181,7 +2189,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>risk assessment; information security; security procedures; personal accountability; self‑management</t>
+          <t>risk assessment; security procedures; personal accountability; risk mitigation; self‑management</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2196,15 +2204,19 @@
         </is>
       </c>
       <c r="S11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Security Task Self‑Management":2, "Security Task Management":1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2302,7 +2314,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Technology Function Identification</t>
+          <t>Specialist System Function Identification</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2333,7 +2345,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>system analysis; functional specification; feature identification; technology; function</t>
+          <t>system analysis; functional specification; feature identification; specialist systems; function identification</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2348,15 +2360,19 @@
         </is>
       </c>
       <c r="S12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Specialist System Function Identification":2, "Technology Feature Identification":1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2454,12 +2470,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Remote Access Server Troubleshooting</t>
+          <t>Network Fault Rectification</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tests remote access server and rectifies faults.</t>
+          <t>Tests remote access server to rectify any faults.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2485,7 +2501,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>network diagnostics; remote server access; fault isolation; TCP/IP troubleshooting; remote access server</t>
+          <t>network diagnostics; remote server access; fault isolation; TCP/IP troubleshooting; rectification</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2507,12 +2523,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>keep:0, "Remote Access Server Troubleshooting":3</t>
+          <t>keep:0, "Network Fault Rectification":2, "Network Fault Troubleshooting":1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2610,7 +2626,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Site-to-site VPN Authentication</t>
+          <t>Site-to-site VPN User Authentication</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2641,7 +2657,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>IPsec; RADIUS; MFA; site-to-site; authentication</t>
+          <t>SSL/TLS; RADIUS; MFA; site-to-site; user authentication</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2663,12 +2679,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>keep:0, "Site-to-site VPN authentication":3</t>
+          <t>keep:1, "Site-to-Site VPN User Authentication":2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2771,7 +2787,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tests network for vulnerabilities following work briefs and organisational policies.</t>
+          <t>Tests network for vulnerabilities following work briefs and organizational policies.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2797,7 +2813,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>penetration testing; network security assessment; vulnerability scanning; risk assessment; network testing</t>
+          <t>penetration testing; network security assessment; vulnerability scanning; risk assessment; network router testing</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2922,7 +2938,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Writing Technical Reports</t>
+          <t>Technical Report Writing</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2953,7 +2969,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>technical documentation; report formatting; organizational standards; word processing tools; template compliance</t>
+          <t>technical documentation; report formatting; organizational standards; template compliance; writing</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2968,15 +2984,19 @@
         </is>
       </c>
       <c r="S16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>keep:0, "Documentation Preparation":1, "Workplace Documentation":1, "Technical Documentation Writing":1</t>
+          <t>keep:0, "Technical Report Writing":3</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2993,7 +3013,7 @@
         </is>
       </c>
       <c r="Z16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -3078,12 +3098,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Network Asset Procurement</t>
+          <t>Network Component Sourcing</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sources required network hardware, software and tools, then confirms each component is serviceable for configuration tasks.</t>
+          <t>Sources appropriate network hardware, software and tools, then confirms each component is serviceable before deployment.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3105,11 +3125,11 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>network hardware procurement; software acquisition; tool sourcing; component serviceability verification; configuration assets</t>
+          <t>network hardware selection; software tool acquisition; component serviceability verification; network component sourcing; equipment readiness assessment</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3121,14 +3141,14 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Network Asset Procurement</t>
+          <t>Network Component Sourcing</t>
         </is>
       </c>
       <c r="S17" t="b">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3138,7 +3158,7 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Sources required network hardware, software and tools, then verifies each component is serviceable for configuration tasks.</t>
+          <t>Selects appropriate network hardware, software and tools, then verifies each component is serviceable before deployment.</t>
         </is>
       </c>
       <c r="X17" t="b">
@@ -3146,11 +3166,11 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>network hardware procurement, software acquisition, tool sourcing, component serviceability verification, configuration assets</t>
+          <t>network hardware selection, software tool acquisition, component serviceability verification, VPN configuration resources, equipment readiness assessment</t>
         </is>
       </c>
       <c r="Z17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -3262,7 +3282,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>prerequisite establishment; gateway connection; network router; verification process; secure VPN setup</t>
+          <t>gateway connection; prerequisite establishment; network router; verification process; secure VPN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3298,7 +3318,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>prerequisite establishment, gateway connection, network router, verification process, secure VPN setup</t>
+          <t>gateway connection, prerequisite establishment, network router, verification process, secure VPN</t>
         </is>
       </c>
       <c r="Z18" t="b">
@@ -3414,7 +3434,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>router console installation; management console access; router management console; console setup; network configuration</t>
+          <t>router console installation; management console access; router management console; network device configuration; console authentication</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3450,7 +3470,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>router console installation, management console access, network configuration, router monitoring, console setup</t>
+          <t>router console installation, management console access, network device configuration, router interface setup, console authentication</t>
         </is>
       </c>
       <c r="Z19" t="b">
@@ -3566,7 +3586,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>access control; identity and access management; security policy design; authentication; compliance frameworks</t>
+          <t>access control; identity and access management; security policy design; risk assessment; authentication</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3581,19 +3601,15 @@
         </is>
       </c>
       <c r="S20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>keep:1, "Authentication Controls Planning/Authentication Control Planning":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3691,7 +3707,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Authentication Documentation Preparation</t>
+          <t>Authentication System Development</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3722,7 +3738,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>authentication; identity management; security protocols; access control; IAM</t>
+          <t>identity management; security protocols; access control; IAM; authentication system</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3737,15 +3753,19 @@
         </is>
       </c>
       <c r="S21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>keep:1, "Authentication System Documentation":1, "Authentication Documentation Development":1</t>
+          <t>keep:0, "Authentication System Development/Authentication System Documentation Development":2, "Authentication Documentation":1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3843,12 +3863,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Authentication Failure Problem Solving</t>
+          <t>Authentication Failure Identification</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Demonstrates intuitive analysis to identify authentication failures and security incidents, and generate problem scope.</t>
+          <t>Demonstrates intuitive analysis to identify authentication failures, generate solutions for security incidents, and define problem scope.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3889,15 +3909,19 @@
         </is>
       </c>
       <c r="S22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Authentication Failure Identification":2, "Authentication Failure Analysis":1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -4000,7 +4024,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Determines and plans user and organizational authentication requirements per security plan.</t>
+          <t>Plans and determines user and organizational authentication requirements per security plan.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4044,12 +4068,12 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>keep:2, "Authentication Requirements Determination":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -4156,7 +4180,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Creates authentication realms and reuses them per system and organisational policies.</t>
+          <t>Creates required authentication realm and reuses it per system and organisational policies.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4200,12 +4224,12 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Authentication System Configuration":1</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -4308,7 +4332,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Submits required documents and promptly addresses personnel comments.</t>
+          <t>Submits required documentation and responds promptly to feedback from personnel.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4352,12 +4376,12 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.95</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Feedback Response Management":1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -4455,12 +4479,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Incident Management Documentation</t>
+          <t>Incident Management Reporting</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Determines and documents security monitoring and incident response procedures, monitors and reports in line with the organization’s security plan.</t>
+          <t>Determines, documents, monitors and reports security monitoring and incident response procedures in line with the organization’s security plan.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4486,7 +4510,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>security monitoring; incident response; SIEM; security plan documentation; reporting processes</t>
+          <t>security monitoring; incident response; SIEM; security plan documentation; reporting</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4501,19 +4525,15 @@
         </is>
       </c>
       <c r="S26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Management Documentation":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -4611,12 +4631,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Authentication Review</t>
+          <t>Security Monitoring Implementation</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Reviews authentication systems against user security and service quality requirements.</t>
+          <t>Reviews authentication systems against user security and quality of service requirements.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4642,7 +4662,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>authentication; access control; identity management; quality of service; user security</t>
+          <t>authentication; access control; identity management; quality of service; security information and event management</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4657,19 +4677,15 @@
         </is>
       </c>
       <c r="S27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>keep:0, "Authentication Review/Authentication Monitoring Review":2, "Security Monitoring":1</t>
+          <t>keep:1, "Security Monitoring Determination":1, "Authentication System Monitoring Implementation":1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4686,7 +4702,7 @@
         </is>
       </c>
       <c r="Z27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -4767,7 +4783,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Authentication Alignment</t>
+          <t>Authentication Process Determination</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4798,7 +4814,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>authentication; access control; identity management; security policy; alignment</t>
+          <t>authentication; access control; identity management; security policy; compliance</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4820,12 +4836,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>keep:0, "Authentication Alignment/Authentication Process Alignment":2, "Authentication Process Determination":1</t>
+          <t>keep:0, "Authentication Authorisation Determination/Authentication Process Determination":3</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4842,16 +4858,12 @@
         </is>
       </c>
       <c r="Z28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>Authentication Requirements Analysis (LLM verified, sim=0.68)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="b">
         <v>0</v>
       </c>
@@ -4927,7 +4939,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Protocol Self‑management</t>
+          <t>Security Protocol Self‑management</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4973,19 +4985,15 @@
         </is>
       </c>
       <c r="S29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>keep:1, "Protocol Self‑Management":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -5239,7 +5247,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>User Attribute Configuration</t>
+          <t>User Attribute Determination</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -5270,7 +5278,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>identity management; access control; authentication systems; user attribute configuration; role-based access</t>
+          <t>identity management; access control; role-based access; authentication systems; user attribute</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -5297,7 +5305,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>keep:0, "User Attribute Configuration":2, "User Attribute Setup":1</t>
+          <t>keep:0, "User Attribute Determination":2, "User Attribute Configuration":1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -5395,7 +5403,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Permission Recordkeeping</t>
+          <t>Permission Data Management</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -5426,7 +5434,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>permission records; configuration data; secure storage; authentication system; authentication system requirements</t>
+          <t>permission records; configuration information; secure storage; authentication system; data management</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -5437,7 +5445,7 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Permission Recordkeeping</t>
+          <t>Permission Data Management</t>
         </is>
       </c>
       <c r="S32" t="b">
@@ -5462,11 +5470,11 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>permission records, configuration data, secure storage, authentication system, recordkeeping</t>
+          <t>permission records, configuration information, secure storage, authentication system, data management</t>
         </is>
       </c>
       <c r="Z32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -5544,12 +5552,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Data Manipulation Scripting</t>
+          <t>Item Manipulation Incorporation</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Incorporates item manipulation using the chosen scripting language, automating transformations within the language.</t>
+          <t>Incorporates scripts to manipulate data items, automating transformations within chosen language.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5575,7 +5583,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>data transformation; automation; Python; PowerShell; scripting</t>
+          <t>data transformation; automation; Python; PowerShell; item manipulation</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5590,15 +5598,19 @@
         </is>
       </c>
       <c r="S33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U33" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>keep:2, "Item Manipulation Scripting":1</t>
+          <t>keep:0, "Item Manipulation Incorporation":2, "Item Manipulation Scripting":1</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -5693,7 +5705,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>IDE Selection</t>
+          <t>IDE Identification</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5724,7 +5736,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>development environment; code editor; language support; IDE; selection</t>
+          <t>development environment; code editor; language support; software development tools; IDE</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5751,7 +5763,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>keep:0, "IDE Selection":2, "IDE Identification":1</t>
+          <t>keep:0, "IDE Identification":2, "IDE Selection":1</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5877,7 +5889,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>code comments; technical documentation; script standards; software development procedures; internal documentation</t>
+          <t>code comments; technical documentation; script standards; internal documentation; software development procedures</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5895,12 +5907,12 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Script Documentation":1, "Internal Documentation Creation":1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -6053,7 +6065,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>keep:0, "Pseudo Code Review":2, "Pseudo Code Correction":1</t>
+          <t>keep:0, "Pseudo Code Review":2, "Logic Correction":1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -6152,12 +6164,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Protocol Model Identification</t>
+          <t>Protocol Object Model Identification</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Identifies communication protocols and underlying object model of the chosen scripting language.</t>
+          <t>Identifies communication protocols and underlying object model in the chosen scripting language.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -6183,7 +6195,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>software engineering; scripting language; protocol analysis; object model; UML modeling</t>
+          <t>software engineering; scripting language; protocol analysis; object model; chosen scripting language</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -6198,15 +6210,19 @@
         </is>
       </c>
       <c r="S37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>keep:2, "Protocol Object Model Identification":1</t>
+          <t>keep:0, "Protocol Model Identification/Protocol Object Model Identification":3</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -6223,7 +6239,7 @@
         </is>
       </c>
       <c r="Z37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -6306,7 +6322,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Creates detailed pseudocode and describes script logic to support development and debugging.</t>
+          <t>Creates pseudocode and describes script logic to support development and debugging.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -6350,12 +6366,12 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Pseudocode Development":1</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -6634,7 +6650,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>version control; approval workflow; script deployment; collaboration tools; finalisation</t>
+          <t>version control; approval workflow; change management; script deployment; finalisation</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -6656,12 +6672,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>keep:1, "Script Finalisation":2</t>
+          <t>keep:0, "Script Finalisation":3</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -6787,7 +6803,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>pseudo-code; scripting languages; code conversion; basic syntax; translation</t>
+          <t>pseudo-code; scripting languages; code conversion; basic syntax; script translation</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -6809,12 +6825,12 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>keep:0, "Script Translation":3</t>
+          <t>keep:0, "Script Translation":2, "Pseudo Code Translation":1</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6918,7 +6934,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Identifies key characteristics of scripting languages for appropriate selection.</t>
+          <t>Identifies main characteristics of scripting languages for appropriate selection.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -7066,12 +7082,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Software Outcome Identification</t>
+          <t>Software Requirements Analysis</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Identifies required software outcomes based on user needs and functional specifications.</t>
+          <t>Identifies required software outcomes in line with user needs and functional specifications.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -7097,7 +7113,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>requirements gathering; functional specifications; use case modeling; stakeholder analysis; software outcomes</t>
+          <t>requirements gathering; functional specifications; use case modeling; stakeholder analysis; software</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -7112,19 +7128,15 @@
         </is>
       </c>
       <c r="S43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>keep:1, "Software Outcome Identification/Software Requirements Identification":2</t>
+          <t>keep:2, "Software Application Requirements Analysis":1</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -7144,9 +7156,13 @@
         <v>1</v>
       </c>
       <c r="AA43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Stakeholder Expectation Discussion (LLM verified, sim=0.65)</t>
+        </is>
+      </c>
       <c r="AC43" t="b">
         <v>0</v>
       </c>
@@ -7219,12 +7235,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Stakeholder Communication</t>
+          <t>Stakeholder Communication Facilitation</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Uses listening, questioning, and confirming requirements in industry terminology.</t>
+          <t>Uses listening, questioning, and confirms requirements in industry terminology.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -7250,7 +7266,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>stakeholder engagement; active listening; requirements elicitation; industry terminology; questioning techniques</t>
+          <t>stakeholder engagement; active listening; requirements elicitation; industry terminology; facilitation techniques</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -7265,19 +7281,15 @@
         </is>
       </c>
       <c r="S44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>keep:1, "Stakeholder Communication":2</t>
+          <t>keep:2, "Stakeholder Communication":1</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -7294,7 +7306,7 @@
         </is>
       </c>
       <c r="Z44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -7372,7 +7384,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Expectation Discussion</t>
+          <t>Stakeholder Expectation Discussion</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -7418,19 +7430,15 @@
         </is>
       </c>
       <c r="S45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>keep:1, "Expectation Discussion":2</t>
+          <t>keep:1, "Stakeholder Expectation Discussion":1, "Stakeholder Expectation Review":1</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -7530,7 +7538,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Identifies and evaluates scripting language texts and pseudo‑code in hybrid environments.</t>
+          <t>Systematic analysis to identify and evaluate scripting language texts and pseudo‑code in hybrid environments.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -7674,7 +7682,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Technical Reading Comprehension</t>
+          <t>Technical Documentation Interpretation</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7705,7 +7713,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>technical documentation; requirements analysis; information extraction; reading; comprehension strategies</t>
+          <t>technical documentation; requirements analysis; information extraction; interpretation; comprehension strategies</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -7720,15 +7728,19 @@
         </is>
       </c>
       <c r="S47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U47" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Technical Documentation Interpretation":2, "Technical Documentation Comprehension":1</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -7898,9 +7910,13 @@
         <v>1</v>
       </c>
       <c r="AA48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Challenges Documentation</t>
+        </is>
+      </c>
       <c r="AC48" t="b">
         <v>0</v>
       </c>
@@ -8005,7 +8021,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>cloud adoption; risk assessment; business requirements; cloud governance; migration challenges</t>
+          <t>cloud adoption; business requirements; cloud governance; migration challenges; challenges of adopting</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -8020,15 +8036,19 @@
         </is>
       </c>
       <c r="S49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U49" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Challenges Documentation":2</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -8045,16 +8065,12 @@
         </is>
       </c>
       <c r="Z49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>Benefits Documentation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="b">
         <v>0</v>
       </c>
@@ -8128,12 +8144,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Cloud Service Selection</t>
+          <t>Cloud Service Platform Selection</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Identifies organisational requirements and the most suitable cloud service and delivery platform according to organisational needs.</t>
+          <t>Identifies organisational requirements to determine the most suitable cloud service and delivery platform.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -8159,7 +8175,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>cloud vendor evaluation; service model comparison; cost‑benefit analysis; scalability and compliance; cloud service selection</t>
+          <t>cloud vendor evaluation; service model comparison; cost‑benefit analysis; scalability and compliance; cloud platform selection</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -8174,15 +8190,19 @@
         </is>
       </c>
       <c r="S50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U50" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Cloud Service Platform Selection":3</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -8278,7 +8298,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Cloud Solution Evaluation</t>
+          <t>Cloud Solutions Evaluation</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -8309,7 +8329,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>cloud computing; solution assessment; vendor comparison; cost analysis; service level agreement</t>
+          <t>cloud computing; solution assessment; cloud solutions; cost analysis; service level agreement</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -8324,15 +8344,19 @@
         </is>
       </c>
       <c r="S51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U51" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "cloud solutions evaluation/Cloud Solutions Services Evaluation/Cloud Solutions Evaluation":3</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -8349,7 +8373,7 @@
         </is>
       </c>
       <c r="Z51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -8433,7 +8457,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Discusses differences, advantages and disadvantages of cloud and hybrid cost models to inform deployment decisions.</t>
+          <t>Discusses cloud and hybrid cost models, articulating pros and cons to inform deployment decisions.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -8459,7 +8483,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>cloud computing; total cost of ownership; hybrid cloud; cost model; comparison</t>
+          <t>cloud computing; total cost of ownership; hybrid cloud; cost‑benefit analysis; cost model</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -8477,12 +8501,12 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>keep:2, "Cost Model Comparison":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -8732,7 +8756,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Emerging Model Research</t>
+          <t>Cloud Deployment Model Research</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -8763,7 +8787,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>cloud computing; deployment models; multi‑cloud architecture; technology scouting; emerging cloud deployment</t>
+          <t>cloud computing; deployment models; multi‑cloud architecture; edge computing; research</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -8778,15 +8802,19 @@
         </is>
       </c>
       <c r="S54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U54" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>keep:2, "Emerging Cloud Model Research":1</t>
+          <t>keep:0, "Cloud Deployment Model Research/Emerging Cloud Model Research/Emerging Deployment Model Research":3</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -8887,7 +8915,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Communicates evaluation results to designated staff through briefings.</t>
+          <t>Communicates evaluation results to designated staff through concise briefings.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -8913,7 +8941,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>evaluation reporting; stakeholder communication; outcome presentation; performance feedback; outcomes</t>
+          <t>evaluation reporting; stakeholder communication; outcome presentation; performance feedback; evaluation outcomes</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -9221,7 +9249,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>verbal communication; active listening; concise feedback; oral feedback; interpersonal communication</t>
+          <t>verbal communication; active listening; concise feedback; interpersonal communication; feedback handling</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -9344,7 +9372,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Policy Identification</t>
+          <t>Organisational Policy Identification</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -9402,7 +9430,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>keep:0, "Policy Requirement Identification/Policy Identification":3</t>
+          <t>keep:0, "Organisational Policy Identification":3</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -9498,7 +9526,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Documentation Preparation</t>
+          <t>Report Writing</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -9529,7 +9557,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>technical documentation; analysis reporting; concise communication; findings presentation; records</t>
+          <t>technical documentation; analysis reporting; concise communication; findings presentation; writing</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -9544,19 +9572,15 @@
         </is>
       </c>
       <c r="S59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>keep:1, "Documentation Preparation":2</t>
+          <t>keep:2, "Documentation Writing":1</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -9656,7 +9680,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Routine Task Management</t>
+          <t>Routine Task Planning</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -9702,19 +9726,15 @@
         </is>
       </c>
       <c r="S60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>keep:1, "Routine Task Management":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -9841,7 +9861,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>routine decision‑making; low‑impact choices; predefined solutions; self‑management; operational judgment</t>
+          <t>routine decision‑making; low‑impact choices; predefined solutions; self‑management; autonomous problem solving</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -9856,15 +9876,19 @@
         </is>
       </c>
       <c r="S61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U61" t="inlineStr"/>
+        <v>0.925</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>keep:2, "Low‑impact Decision‑making":1</t>
+          <t>keep:1, "Self‑Management Decision‑Making":2</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -9960,12 +9984,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Total Cost Analysis</t>
+          <t>Ownership Cost Analysis</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Applies total cost of ownership of cloud solution to business requirements.</t>
+          <t>Applies cloud solution total cost of ownership to business requirements.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -9991,7 +10015,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>cloud economics; total cost of ownership; IT financial analysis; cloud pricing models; cost modeling</t>
+          <t>cloud economics; total cost of ownership; cloud pricing models; cost modeling; cloud computing solution</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -10006,15 +10030,19 @@
         </is>
       </c>
       <c r="S62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="U62" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>keep:2, "Total Cost Ownership Analysis":1</t>
+          <t>keep:0, "Total Cost Ownership Analysis/Ownership Cost Analysis":3</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -10031,7 +10059,7 @@
         </is>
       </c>
       <c r="Z62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -10115,7 +10143,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Identifies business and industry technology terminology, characteristics and concepts for cloud solutions.</t>
+          <t>Identifies and confirms business and industry technology terminology, characteristics and concepts for cloud solutions evaluation.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -10141,7 +10169,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>technology terminology; business terminology; industry concepts; terminology confirmation; industry technology terminology</t>
+          <t>business terminology; industry terminology; technology concepts; technology terminology; terminology verification</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -10169,15 +10197,15 @@
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Identifies and confirms business and industry technology terminology, characteristics and concepts for cloud solution reviews.</t>
+          <t>Identifies and confirms business and industry technology terminology, characteristics and concepts for cloud solutions evaluation.</t>
         </is>
       </c>
       <c r="X63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>technology terminology, business terminology, industry concepts, cloud characteristics, terminology confirmation</t>
+          <t>business terminology, industry terminology, technology concepts, cloud computing terms, terminology verification</t>
         </is>
       </c>
       <c r="Z63" t="b">
@@ -10260,7 +10288,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Cloud Platform Assessment</t>
+          <t>Cloud Service Assessment</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -10270,7 +10298,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>cognitive</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -10283,15 +10311,15 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>theoretical</t>
+          <t>practical</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>cloud platforms; delivery models; business requirements; capability review; service characteristics</t>
+          <t>cloud platforms; delivery models; business requirements; service characteristics; cloud deployment models</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -10302,14 +10330,14 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Cloud Platform Assessment</t>
+          <t>Cloud Service Assessment</t>
         </is>
       </c>
       <c r="S64" t="b">
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -10331,7 +10359,7 @@
         </is>
       </c>
       <c r="Z64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -10446,7 +10474,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>risk assessment; critical function identification; impact analysis; business resilience; business continuity</t>
+          <t>business continuity; risk assessment; critical function identification; impact analysis; business resilience</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -10464,12 +10492,12 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Business Continuity Impact Assessment":1</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -10579,7 +10607,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Prepares comprehensive contingency plans that include evaluations and strategies, using prescribed language and formats.</t>
+          <t>Prepares comprehensive contingency documentation detailing evaluations and strategies in prescribed language and formats.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -10623,12 +10651,12 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
-          <t>keep:2, "Contingency Documentation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -10652,13 +10680,9 @@
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 2.2 Evaluate and document risk minimisation alternatives aga</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
@@ -10733,12 +10757,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Critical Data Identification</t>
+          <t>Critical Data Software Identification</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Identifies essential data and appropriate software in hybrid environments for project objectives.</t>
+          <t>Identifies essential data and appropriate software in hybrid environments to support project objectives.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -10779,15 +10803,19 @@
         </is>
       </c>
       <c r="S67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0.9333333333333332</v>
-      </c>
-      <c r="U67" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Critical Data Software Identification/Critical Data Identification":2</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -10919,7 +10947,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>disaster recovery; risk assessment; recovery time objective; backup and restore; contingency planning</t>
+          <t>business continuity; risk assessment; recovery time objective; contingency planning; disaster recovery plan</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -11048,7 +11076,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Formulates and documents hybrid disaster prevention and recovery options, evaluating options for resilience.</t>
+          <t>Formulates and documents hybrid disaster prevention and recovery options, evaluating alternatives for resilience.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -11202,7 +11230,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>System Data Analysis</t>
+          <t>System Data Interpretation</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -11233,7 +11261,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>quantitative analysis; financial data reporting; technical system metrics; data visualization; system data</t>
+          <t>quantitative analysis; financial data reporting; technical system metrics; data visualization; data interpretation</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -11260,7 +11288,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>keep:0, "System Data Analysis":3</t>
+          <t>keep:0, "System Data Interpretation":3</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -11410,12 +11438,12 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.925</v>
       </c>
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Plan Improvement Problem Solving":1</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -11521,7 +11549,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Identifies statutory, commercial and contingency requirements within organisational processes to meet compliance obligations.</t>
+          <t>Identifies statutory, commercial and contingency requirements according to organisational compliance obligations.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -11574,7 +11602,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>keep:0, "Regulatory Requirement Identification/Regulatory Requirements Identification":3</t>
+          <t>keep:0, "Regulatory Requirements Identification/Regulatory Requirement Identification":3</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -11675,12 +11703,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Risk Minimisation Evaluation</t>
+          <t>Risk Minimisation Alternatives Evaluation</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Evaluates risk‑minimisation options, documents findings, in hybrid projects with organisational cost limits.</t>
+          <t>Evaluates risk‑minimisation options against organisational cost limits and documents findings in hybrid projects.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -11706,7 +11734,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>risk assessment; cost‑benefit analysis; mitigation strategies; financial modeling; risk minimisation</t>
+          <t>risk assessment; cost‑benefit analysis; mitigation strategies; alternatives; minimisation</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -11721,15 +11749,19 @@
         </is>
       </c>
       <c r="S73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U73" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>keep:2, "Risk Minimisation Alternatives Evaluation":1</t>
+          <t>keep:0, "Risk Minimisation Alternatives Evaluation":3</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -11830,12 +11862,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Threat Analysis</t>
+          <t>System Threat Analysis</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Identifies and documents internal and external system threats.</t>
+          <t>Identifies and documents internal and external system threats through hybrid risk threat analysis.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -11861,7 +11893,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>threat modeling; risk assessment; vulnerability analysis; threat intelligence; business environment</t>
+          <t>threat modeling; risk assessment; vulnerability analysis; threat intelligence; system threats</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -11888,7 +11920,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>keep:0, "Threat Analysis":2, "System Threat Identification":1</t>
+          <t>keep:0, "System Threat Analysis/Threat Analysis":2, "Threat Identification":1</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -11994,7 +12026,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Documents and submits materials to relevant parties, seeks input, and incorporates feedback in hybrid settings.</t>
+          <t>Documents feedback from relevant parties, seeks their input, and submits responses in hybrid settings.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -12038,12 +12070,12 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr">
         <is>
-          <t>keep:2, "Feedback Management":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -12175,7 +12207,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>strategic planning; roadmap development; priority alignment; outcome measurement; performance governance</t>
+          <t>roadmap development; priority alignment; outcome measurement; performance governance; strategic planning</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -12304,7 +12336,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Maintains working relationships by employing communication tools and strategies.</t>
+          <t>Maintains team collaboration by employing communication tools and strategies.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -12330,7 +12362,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>communication tools; relationship building; facilitation techniques; interpersonal dynamics; effective working relationships</t>
+          <t>communication tools; relationship building; collaboration platforms; interpersonal dynamics; effective working relationships</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -12357,7 +12389,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>keep:0, "Collaboration Facilitation":2, "Teamwork Facilitation":1</t>
+          <t>keep:1, "Collaboration Facilitation":2</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -12489,7 +12521,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>active listening; questioning techniques; industry terminology; audience analysis; oral communication</t>
+          <t>oral communication; active listening; questioning techniques; industry terminology; audience analysis</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -12511,12 +12543,12 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>keep:1, "Oral Communication":2</t>
+          <t>keep:0, "Audience Oral Communication/Oral Communication":3</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -12617,7 +12649,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Technical Specification Research</t>
+          <t>Technical Specification Analysis</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -12648,7 +12680,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>technical documentation; specification analysis; information retrieval; data extraction; research</t>
+          <t>technical documentation; specification analysis; information retrieval; engineering standards; data extraction</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -12663,15 +12695,19 @@
         </is>
       </c>
       <c r="S79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U79" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Technical Specification Analysis":3</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -12688,7 +12724,7 @@
         </is>
       </c>
       <c r="Z79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12777,7 +12813,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Independently assesses how business risks and threats could affect ICT systems.</t>
+          <t>Assesses the potential impact of business risks and threats on ICT systems to inform mitigation planning.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -12803,7 +12839,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>ICT risk assessment; business risk; threat impact; impact analysis; ICT systems</t>
+          <t>risk impact assessment; business risk; ICT systems; threat evaluation; mitigation planning</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -12831,19 +12867,19 @@
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
         <is>
-          <t>Independently evaluates how business risks and threats could affect ICT systems and documents potential impacts.</t>
+          <t>Assesses the potential impact of business risks and threats on ICT systems to inform mitigation planning.</t>
         </is>
       </c>
       <c r="X80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>ICT risk assessment, business risk, threat impact, system vulnerability, impact analysis</t>
+          <t>risk impact assessment, business risk, ICT systems, threat evaluation, mitigation planning</t>
         </is>
       </c>
       <c r="Z80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12927,12 +12963,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Operational Procedure Review</t>
+          <t>Procedure Compliance Review</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Independently reviews industry standard operational procedures and checks required risk safeguards and contingency plans are in place.</t>
+          <t>Independently reviews industry standard procedures and checks that required risk safeguards and contingency plans are in place.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -12954,7 +12990,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -12969,14 +13005,14 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Operational Procedure Review</t>
+          <t>Procedure Compliance Review</t>
         </is>
       </c>
       <c r="S81" t="b">
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -12986,7 +13022,7 @@
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr">
         <is>
-          <t>Independently reviews industry standard operational procedures and verifies required risk safeguards and contingency plans are in place.</t>
+          <t>Independently reviews industry standard procedures and verifies that required risk safeguards and contingency plans are implemented.</t>
         </is>
       </c>
       <c r="X81" t="b">
@@ -13082,17 +13118,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Cut‑over Criteria Definition</t>
+          <t>Cut‑over Sign‑off</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Identifies and plans the cut‑over criteria and obtains final sign‑off for implementation.</t>
+          <t>Identifies required cut‑over criteria and secures final sign‑off from stakeholders for task completion.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>technical</t>
+          <t>interpersonal</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -13109,11 +13145,11 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>cut‑over criteria; plan documentation; final sign‑off; implementation approval; project closure</t>
+          <t>cut‑over criteria plan; cut‑over criteria; sign‑off process; task completion; stakeholder approval</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -13125,14 +13161,14 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Cut‑over Criteria Definition</t>
+          <t>Cut‑over Sign‑off</t>
         </is>
       </c>
       <c r="S82" t="b">
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
@@ -13142,19 +13178,19 @@
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr">
         <is>
-          <t>Develops and documents the cut‑over criteria plan and secures final sign‑off for implementation.</t>
+          <t>Identifies required cut‑over criteria and secures final sign‑off from stakeholders for task completion.</t>
         </is>
       </c>
       <c r="X82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>cut‑over criteria, plan documentation, final sign‑off, implementation approval, project closure</t>
+          <t>cut‑over criteria, sign‑off process, task completion, stakeholder approval, documentation requirements</t>
         </is>
       </c>
       <c r="Z82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -13252,7 +13288,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Prepares comprehensive audit reports and presents recommendations to stakeholders through formal presentations.</t>
+          <t>Prepares and reports comprehensive audit findings and presents recommendations to stakeholders through formal presentations.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -13296,7 +13332,7 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr">
@@ -13411,12 +13447,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Change Approval Coordination</t>
+          <t>Change Approval Obtaining</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Recommends change approvals to decision‑makers for sign‑off.</t>
+          <t>Recommends changes to decision‑makers for approval.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -13442,7 +13478,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>stakeholder management; approval workflow; change management process; governance compliance; communication coordination</t>
+          <t>stakeholder management; approval workflow; change management process; recommended changes approval; communication coordination</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -13457,15 +13493,19 @@
         </is>
       </c>
       <c r="S84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
         <v>0.9</v>
       </c>
-      <c r="U84" t="inlineStr"/>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Change Approval Obtaining":2</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -13482,7 +13522,7 @@
         </is>
       </c>
       <c r="Z84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -13575,12 +13615,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Encryption Facility Deployment</t>
+          <t>Encryption Facility Implementation</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Investigates built‑in and third‑party encryption tools and implements them to secure data systems.</t>
+          <t>Investigates built‑in and third‑party encryption tools, then implements them to secure data systems.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -13606,7 +13646,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>cryptography; key management; PKI; data protection; encryption facility</t>
+          <t>cryptography; AES; PKI; data protection; encryption facility</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -13621,15 +13661,19 @@
         </is>
       </c>
       <c r="S85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T85" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U85" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>keep:2, "Encryption Facility Implementation":1</t>
+          <t>keep:0, "Encryption Facility Implementation/Encryption Facilities Implementation":3</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -13739,7 +13783,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>File Security Categorisation</t>
+          <t>File Security Categorisation Development</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -13770,7 +13814,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>information security; data classification; access control; confidentiality policy; file security categorisation</t>
+          <t>information security; data classification; access control; confidentiality policy; file categorisation</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -13785,15 +13829,19 @@
         </is>
       </c>
       <c r="S86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U86" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "File Security Categorisation Development":2, "File Security Categorisation":1</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
@@ -13908,7 +13956,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Checks password strength using required utilities, reviews organisational guidelines for password complexity and tightens requirements per guidelines.</t>
+          <t>Checks password strength with utilities, reviews organisational guidelines for password complexity, and tightens complexity requirements as required.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -14098,7 +14146,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>analytical thinking; root cause analysis; troubleshooting; critical thinking; problem</t>
+          <t>analytical thinking; root cause analysis; troubleshooting; critical thinking; problem solving</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -14120,12 +14168,12 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>keep:0, "Problem Solving":3</t>
+          <t>keep:0, "Problem Solving":2, "Problem Solving Analysis":1</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -14244,7 +14292,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Reviews system logs and audit reports across hybrid environments to identify and report security threats.</t>
+          <t>Reviews system logs and audit reports across hybrid environments to identify security threats.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -14293,7 +14341,7 @@
       <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr">
         <is>
-          <t>keep:2, "Log and Audit Analysis":1</t>
+          <t>keep:2, "Log Threat Identification":1</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -14403,7 +14451,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Security Procedure Evaluation</t>
+          <t>System Security Procedure Evaluation</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -14452,16 +14500,16 @@
         <v>1</v>
       </c>
       <c r="T90" t="n">
-        <v>0.925</v>
+        <v>0.9</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>keep:1, "Security Procedure Evaluation/System Security Procedure Evaluation":2</t>
+          <t>keep:0, "System Security Procedure Evaluation":3</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -14602,7 +14650,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>compliance; risk assessment; security policy; governance; security recommendation</t>
+          <t>compliance; risk assessment; security policy; governance; recommendation</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -14620,12 +14668,12 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Security Adherence Recommendation Development":1</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -14740,7 +14788,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Performs user security spot checks following organisational policies.</t>
+          <t>Checks user security spot checks following organisational policies to ensure compliance.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -14903,7 +14951,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Self‑management</t>
+          <t>Task Prioritisation</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -14961,7 +15009,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>keep:0, "Self‑management":2, "Task Prioritisation":1</t>
+          <t>keep:0, "Task Prioritisation":2, "Workload Prioritisation":1</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -15120,12 +15168,12 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Complex Documentation Writing":1, "Security Documentation":1</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
@@ -15244,7 +15292,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Continuously monitors ICT systems, records identified security threats for response planning.</t>
+          <t>Continuously monitors ICT systems, records identified security threats, for response planning.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -15412,7 +15460,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Creates user accounts by accessing ICT systems according to organisational procedures and creating settings to meet security policies.</t>
+          <t>Creates user accounts by accessing ICT systems in accordance with organisational procedures and settings according to security policies.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -15571,7 +15619,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Virus Scanning Implementation</t>
+          <t>Virus Checking Implementation</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -15602,7 +15650,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>malware detection; antivirus software; file integrity checking; signature‑based scanning; virus checking process</t>
+          <t>malware detection; antivirus software; file integrity checking; signature‑based scanning; virus checking</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -15617,15 +15665,19 @@
         </is>
       </c>
       <c r="S97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U97" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Virus Checking Implementation":3</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -15735,17 +15787,17 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Legal Notice Compliance</t>
+          <t>Legal Notice Auditing</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Aligns displayed legal notices at log‑on with organisational requirements and checks for legislation compliance breaches.</t>
+          <t>The worker checks that log‑on legal notices are aligned with organisational standards and checks for legislative compliance breaches.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>domain_knowledge</t>
+          <t>cognitive</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -15766,7 +15818,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>legal notice requirements; displayed legal notices; log‑on display; legislation compliance; breach control</t>
+          <t>legal notice; organisational requirements; legislation compliance; audit checks; auditing</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -15778,7 +15830,7 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Legal Notice Compliance</t>
+          <t>Legal Notice Auditing</t>
         </is>
       </c>
       <c r="S98" t="b">
@@ -15795,7 +15847,7 @@
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Ensures displayed legal notices at log‑on meet organisational standards and monitors for legislation compliance breaches.</t>
+          <t>The worker verifies that log‑on legal notices meet organisational standards and monitors for legislative compliance breaches.</t>
         </is>
       </c>
       <c r="X98" t="b">
@@ -15803,7 +15855,7 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>legal notice requirements, organisational standards, log‑on display, legislation compliance, breach control</t>
+          <t>legal notice, log on screen, organisational requirements, legislation compliance, audit checks</t>
         </is>
       </c>
       <c r="Z98" t="b">
@@ -15900,12 +15952,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Procedure Compliance Documentation</t>
+          <t>Security Procedure Implementation</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Documents non‑compliance with security procedures and implements approved changes to ensure system integrity.</t>
+          <t>Implements approved security changes and documents any instances where security procedures are not being followed.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -15927,11 +15979,11 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>security procedures; non‑compliance documentation; change implementation; approved changes; audit records</t>
+          <t>security procedures; security changes; procedure compliance; documentation; non‑compliance</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -15943,14 +15995,14 @@
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Procedure Compliance Documentation</t>
+          <t>Security Procedure Implementation</t>
         </is>
       </c>
       <c r="S99" t="b">
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -15960,19 +16012,19 @@
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Documents non‑compliance with security procedures and implements approved changes to maintain system integrity.</t>
+          <t>Implements approved security changes and documents any instances where security procedures are not being followed.</t>
         </is>
       </c>
       <c r="X99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>security procedures, non‑compliance documentation, change implementation, approved changes, audit records</t>
+          <t>security changes, procedure compliance, documentation, implementation, non‑compliance</t>
         </is>
       </c>
       <c r="Z99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -16052,7 +16104,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Audience‑focused Report Drafting</t>
+          <t>Research Report Drafting</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -16083,7 +16135,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>technical writing; audience analysis; research reporting; report drafting; document design</t>
+          <t>technical writing; research reporting; stakeholder communication; document design; drafting</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -16098,15 +16150,19 @@
         </is>
       </c>
       <c r="S100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U100" t="inlineStr"/>
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Research Report Drafting/Report Drafting/Audience‑Focused Report Drafting":3</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -16203,7 +16259,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Data Analysis</t>
+          <t>Research Information Synthesis</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -16234,7 +16290,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>research methodology; information retrieval; statistical analysis; data mining; stored information</t>
+          <t>research methodology; information retrieval; statistical analysis; data mining; synthesis</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -16256,12 +16312,12 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>keep:0, "Data Analysis":3</t>
+          <t>keep:0, "Research Information Synthesis":2, "Data Analysis Synthesis":1</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -16393,7 +16449,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>information retrieval; online databases; digital research tools; data analysis; research software</t>
+          <t>information retrieval; digital research tools; data analysis; research software; utilisation</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -16408,15 +16464,19 @@
         </is>
       </c>
       <c r="S102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T102" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U102" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>keep:2, "Digital Technology Utilisation":1</t>
+          <t>keep:0, "Digital Research Tool Utilisation/Digital Tool Utilisation":3</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
@@ -16433,7 +16493,7 @@
         </is>
       </c>
       <c r="Z102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -16518,7 +16578,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Demonstrates conclusions by explicitly stating assumptions, justifying them, and supporting evidence in analyses.</t>
+          <t>Demonstrates conclusions by explicitly stating assumptions, justifying them, and supporting them with evidence.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -16562,12 +16622,12 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>keep:2, "Assumption and Conclusion Justification":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -16850,7 +16910,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>data retrieval; data formatting; information extraction tools; content mining; information analysis</t>
+          <t>data retrieval; data formatting; information extraction tools; content mining; data analysis</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -17023,16 +17083,16 @@
         <v>1</v>
       </c>
       <c r="T106" t="n">
-        <v>0.9</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>keep:0, "Oral Presentation":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
@@ -17129,12 +17189,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Problem‑solving in Familiar Contexts</t>
+          <t>Problem Solving</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Identifies anticipated issues within routine tasks using established procedures.</t>
+          <t>Identifies and resolves anticipated issues within routine tasks using procedures.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -17160,7 +17220,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>troubleshooting; root cause analysis; process improvement; familiar contexts; problem solving</t>
+          <t>troubleshooting; root cause analysis; process improvement; standard operating procedures; problem solving</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -17175,15 +17235,19 @@
         </is>
       </c>
       <c r="S107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U107" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Foreseeable Problem Solving/Problem Solving":3</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
@@ -17207,9 +17271,13 @@
       </c>
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>generic FS capability "Problem Solving" is implicit in other skills</t>
+        </is>
+      </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
@@ -17280,7 +17348,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Report Review Facilitation</t>
+          <t>Draft Report Review Facilitation</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -17311,7 +17379,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>document review; policy compliance; quality assurance; stakeholder engagement; facilitation</t>
+          <t>document review; stakeholder engagement; quality assurance; facilitation; draft</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -17326,15 +17394,19 @@
         </is>
       </c>
       <c r="S108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U108" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Draft Report Review Facilitation":2</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
@@ -17480,12 +17552,12 @@
         <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Research Report Distribution":1</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -17635,12 +17707,12 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>keep:0, "Research Strategy Identification":3</t>
+          <t>keep:0, "Research Strategy Identification":2, "Research Strategy Confirmation":1</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
@@ -17768,7 +17840,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>information security; data protection; encryption; records management; secure storage</t>
+          <t>information security; data protection; access control; encryption; records management</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -17786,12 +17858,12 @@
         <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Information Storage Management":1, "Information Storage":1</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
@@ -17808,7 +17880,7 @@
         </is>
       </c>
       <c r="Z111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -17888,12 +17960,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Self‑management</t>
+          <t>Self‑management Planning</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Plans and implements tasks to meet organisational requirements and achieve objectives.</t>
+          <t>Plans and implements tasks to meet organisational requirements.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -17934,19 +18006,15 @@
         </is>
       </c>
       <c r="S112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>keep:1, "Self‑management":2</t>
+          <t>keep:2, "Self‑Management Planning":1</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -18048,7 +18116,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Evaluates source credibility by cross‑checking evidence and criteria during hybrid research tasks.</t>
+          <t>Assesses source credibility against evidence and criteria during hybrid research tasks.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -18074,7 +18142,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>information verification; bias assessment; citation analysis; source reliability; source evaluation</t>
+          <t>source reliability; information verification; bias assessment; citation analysis; media literacy</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -18106,7 +18174,7 @@
         </is>
       </c>
       <c r="X113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
@@ -18225,7 +18293,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>thematic analysis; pattern recognition; qualitative research; content coding; theme</t>
+          <t>thematic analysis; pattern recognition; qualitative research; content coding; research methodology</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -18247,12 +18315,12 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>keep:0, "Theme Identification":3</t>
+          <t>keep:0, "Theme Identification":2, "Thematic Pattern Identification":1</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
@@ -18269,7 +18337,7 @@
         </is>
       </c>
       <c r="Z114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -18349,12 +18417,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Report Method Selection</t>
+          <t>Report Format Selection</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Identifies reporting methods that align with the target audience and meet organisational requirements.</t>
+          <t>Identify reporting methods that align with the target audience and meet organisational requirements.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -18380,7 +18448,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>reporting methods; intended audience; organisational requirements; method selection; audience alignment</t>
+          <t>reporting methods; intended audience; organisational requirements; format selection; communication strategy</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -18391,7 +18459,7 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Report Method Selection</t>
+          <t>Report Format Selection</t>
         </is>
       </c>
       <c r="S115" t="b">
@@ -18408,7 +18476,7 @@
       <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Selects reporting methods that suit the target audience and meet organisational requirements independently.</t>
+          <t>Select reporting methods that suit the target audience and meet organisational requirements effectively.</t>
         </is>
       </c>
       <c r="X115" t="b">
@@ -18416,7 +18484,7 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>reporting methods, intended audience, organisational requirements, method selection, audience alignment</t>
+          <t>reporting methods, intended audience, organisational requirements, format selection, communication strategy</t>
         </is>
       </c>
       <c r="Z115" t="b">
@@ -18505,12 +18573,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Barrier Analysis WHS</t>
+          <t>Barrier Identification</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Identifies and reports obstacles to consultation participation following systematic WHS barrier analysis.</t>
+          <t>Identifies barriers to WHS consultation and reports obstacles to participation.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -18551,15 +18619,19 @@
         </is>
       </c>
       <c r="S116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T116" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U116" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>keep:2, "WHS Barrier Identification":1</t>
+          <t>keep:0, "Barrier Identification":3</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
@@ -18696,7 +18768,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>WHS consultation; occupational health and safety; stakeholder engagement; communication channels; consultation method selection</t>
+          <t>WHS consultation; stakeholder engagement; communication channels; consultation methods; selection process</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -18714,12 +18786,12 @@
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "WHS Consultation Method Selection":1</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
@@ -18852,7 +18924,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>occupational health and safety; stakeholder engagement; WHS legislation compliance; safety committee facilitation; WHS consultation</t>
+          <t>occupational health and safety; stakeholder engagement; WHS legislation compliance; safety committee facilitation; consultation</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -18870,12 +18942,12 @@
         <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "WHS Consultation Facilitation":1</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
@@ -19008,7 +19080,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>issue raising; hazard reporting; risk communication; safety meetings; issue escalation</t>
+          <t>work health and safety; hazard reporting; issue raising; safety meetings; issue escalation</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -19026,16 +19098,16 @@
         <v>1</v>
       </c>
       <c r="T119" t="n">
-        <v>0.9</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>keep:1, "WHS Issue Raising":2</t>
+          <t>keep:0, "WHS Issue Raising/Meeting Issue Raising":3</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
@@ -19055,13 +19127,9 @@
         <v>1</v>
       </c>
       <c r="AA119" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>Barrier Analysis WHS (LLM verified, sim=0.67)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="b">
         <v>0</v>
       </c>
@@ -19141,12 +19209,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Outcome Follow-up Coordination</t>
+          <t>Meeting Outcome Coordination</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Follows up post‑meeting actions by tracking outcomes in line with role responsibilities and company policies.</t>
+          <t>Follows up meeting outcomes according to own job role and organisational policies and procedures.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -19172,7 +19240,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>meeting coordination; outcome tracking; stakeholder communication; action item management; follow up meeting</t>
+          <t>meeting coordination; outcome tracking; policy compliance; stakeholder communication; follow up meeting</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -19187,15 +19255,19 @@
         </is>
       </c>
       <c r="S120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120" t="n">
         <v>0.9</v>
       </c>
-      <c r="U120" t="inlineStr"/>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Meeting Outcome Coordination/Meeting Outcome Follow-up Coordination":3</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
@@ -19301,7 +19373,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Plain Language Communication</t>
+          <t>WHS Information Communication</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -19347,15 +19419,19 @@
         </is>
       </c>
       <c r="S121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T121" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U121" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "WHS Information Communication":3</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
@@ -19515,7 +19591,7 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>keep:0, "Duties Rights Responsibilities Communication/Duties Rights Communication":3</t>
+          <t>keep:0, "Duties Rights Responsibilities Communication":3</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
@@ -19617,7 +19693,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Solution Suggestion</t>
+          <t>Barrier Solution Development</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -19648,7 +19724,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>workplace health and safety; suggestion; hazard barrier analysis; safety consultation; corrective action planning</t>
+          <t>workplace health and safety; hazard barrier analysis; safety consultation; corrective action planning; barrier removal solution</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -19670,12 +19746,12 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Suggestion":2, "Suggestion Development":1</t>
+          <t>keep:0, "Barrier Solution Development":3</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
@@ -19781,7 +19857,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>WHS Stakeholder Identification</t>
+          <t>Stakeholder Identification</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -19812,7 +19888,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>occupational health and safety; stakeholder analysis; WHS legislation; compliance documentation; key stakeholders</t>
+          <t>occupational health and safety; stakeholder analysis; WHS legislation; compliance documentation; record key stakeholders</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -19834,12 +19910,12 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>keep:1, "WHS Stakeholder Identification/Stakeholder Identification":2</t>
+          <t>keep:0, "Stakeholder Identification":3</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
@@ -19941,12 +20017,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>WHS Discussion Documentation</t>
+          <t>WHS Discussion Recording</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Documents WHS discussions and disseminates outcomes in line with organisational policies.</t>
+          <t>Records WHS discussions and communicates outcomes in line with organisational policies.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -19972,7 +20048,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>occupational health and safety; policy compliance; recordkeeping; risk communication; whs discussion</t>
+          <t>occupational health and safety; policy compliance; recordkeeping; risk communication; discussion</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -19987,19 +20063,15 @@
         </is>
       </c>
       <c r="S125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>keep:0, "WHS discussion documentation":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
@@ -20008,7 +20080,7 @@
         </is>
       </c>
       <c r="X125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y125" t="inlineStr">
         <is>
@@ -20101,12 +20173,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>WHS Understanding Verification</t>
+          <t>WHS Information Verification</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Participates in confirming personnel understanding of WHS information, instructions and signs.</t>
+          <t>Participates in confirming personnel comprehension of WHS information, instructions and signs.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -20132,7 +20204,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>occupational health and safety; hazard communication; safety compliance; training verification; understanding</t>
+          <t>occupational health and safety; hazard communication; safety compliance; risk assessment; training verification</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -20147,19 +20219,15 @@
         </is>
       </c>
       <c r="S126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>keep:1, "WHS Understanding Verification":2</t>
+          <t>keep:1, "WHS Information Confirmation":1, "WHS Information Understanding":1</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
@@ -20176,7 +20244,7 @@
         </is>
       </c>
       <c r="Z126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -20310,12 +20378,12 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>keep:2, "WHS Obligations Research":1</t>
+          <t>keep:0, "WHS Legislative Review":1, "WHS Legislative Obligations Research":1, "WHS Obligations Investigation":1</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
@@ -20427,7 +20495,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>cognitive</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -20440,15 +20508,15 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>theoretical</t>
+          <t>practical</t>
         </is>
       </c>
       <c r="N128" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>communication methods; required individuals; WHS context; appropriate forms; stakeholder selection</t>
+          <t>communication methods; WHS stakeholders; form selection; appropriate channels; forms of communication</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -20466,7 +20534,7 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -20484,11 +20552,11 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>communication methods, required individuals, WHS context, appropriate forms, stakeholder selection</t>
+          <t>communication methods, WHS stakeholders, form selection, appropriate channels, information delivery</t>
         </is>
       </c>
       <c r="Z128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -20578,7 +20646,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Communicates WHS meeting outcomes to required individuals or parties promptly and clearly, ensuring understanding and appropriate follow‑up.</t>
+          <t>Communicates the WHS-related outcomes of meetings to designated individuals or parties promptly and accurately.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -20600,11 +20668,11 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>WHS outcomes; meeting communication; required individuals; meeting outcomes; outcome dissemination</t>
+          <t>WHS outcomes; meeting communication; stakeholder notification; required individuals; outcome reporting</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -20622,7 +20690,7 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -20632,7 +20700,7 @@
       <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Communicates WHS meeting outcomes to required individuals or parties promptly and clearly, ensuring understanding and appropriate follow‑up.</t>
+          <t>Communicates the WHS-related outcomes of meetings to designated individuals or parties promptly and accurately.</t>
         </is>
       </c>
       <c r="X129" t="b">
@@ -20640,7 +20708,7 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>WHS outcomes, meeting communication, required individuals, stakeholder notification, outcome dissemination</t>
+          <t>WHS outcomes, meeting communication, stakeholder notification, information dissemination, outcome reporting</t>
         </is>
       </c>
       <c r="Z129" t="b">
@@ -20763,7 +20831,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>network security; firewall policies; intrusion prevention; VPN configuration; advanced functions</t>
+          <t>network security; firewall policies; intrusion prevention; advanced firewall functions; Cisco ASA</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -20922,7 +20990,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>network security; configuration management; backup automation; device configuration; change control</t>
+          <t>network security; configuration management; backup automation; device; change control</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -20940,12 +21008,12 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>keep:2, "Device Configuration Backup":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
@@ -21055,7 +21123,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Determines required firewall configurations according to organisational requirements for hybrid environments.</t>
+          <t>Determines required firewall security according to organisational requirements.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -21096,15 +21164,19 @@
         </is>
       </c>
       <c r="S132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T132" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U132" t="inlineStr"/>
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Firewall Security Determination":3</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
@@ -21214,7 +21286,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Configures perimeter network topology to meet specified security requirements.</t>
+          <t>Configures required perimeter topology to meet specified security requirements.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -21376,12 +21448,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Penetration Testing Execution</t>
+          <t>Penetration Testing Verification</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tests penetration and verifies network perimeter compliance with security standards.</t>
+          <t>Tests penetration of network perimeter and verifies compliance with security standards.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -21407,7 +21479,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>cybersecurity; vulnerability assessment; red team operations; Metasploit; penetration testing</t>
+          <t>penetration testing; verification; vulnerability assessment; perimeter validation; cybersecurity</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -21422,15 +21494,19 @@
         </is>
       </c>
       <c r="S134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T134" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U134" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>keep:1, "Penetration Testing Verification":1, "Penetration Testing":1</t>
+          <t>keep:1, "Penetration Testing Verification":2</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
@@ -21566,7 +21642,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>network security; firewall implementation; security appliances; perimeter devices; security policy compliance</t>
+          <t>network security; firewall implementation; security appliances; security policy compliance; perimeter device deployment</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -21703,7 +21779,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Researches perimeter security solutions against organisational requirements in hybrid environments.</t>
+          <t>Researches and identifies perimeter security solutions against organisational requirements in hybrid environments.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -21729,7 +21805,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>network security; firewall; security assessment; perimeter security; intrusion detection</t>
+          <t>network security; firewall; intrusion detection; security assessment; perimeter security</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -21747,12 +21823,12 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>0.9499999999999998</v>
+        <v>0</v>
       </c>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Perimeter Security Options Survey":1, "Perimeter Security Options Investigation":1, "Perimeter Security Identification":1</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
@@ -21914,12 +21990,12 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>keep:1, "Remote Access VPN Configuration":2</t>
+          <t>keep:0, "Remote Access VPN Configuration":3</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
@@ -22059,7 +22135,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>network security; firewall architecture; DMZ segmentation; defense in depth; security perimeter design</t>
+          <t>network security; firewall architecture; DMZ segmentation; defense in depth; perimeter design</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -22077,12 +22153,12 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Security Perimeter Design":1</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
@@ -22351,7 +22427,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Designs and configures perimeter solutions for service continuity during device upgrades in hybrid environments.</t>
+          <t>Designs and configures perimeter solutions to enable service continuity during device upgrades in hybrid environments.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -22399,12 +22475,12 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>keep:0, "Service Continuity Enablement":3</t>
+          <t>keep:0, "Service Continuity Enablement":2, "Service Continuity Design":1</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
@@ -22555,15 +22631,19 @@
         </is>
       </c>
       <c r="S141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T141" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U141" t="inlineStr"/>
+        <v>0.925</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Site‑to‑Site VPN Configuration":2</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
@@ -22730,7 +22810,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>keep:0, "Performance Documentation/Performance Results Documentation":3</t>
+          <t>keep:0, "Functionality Performance Documentation/Performance Results Documentation":3</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
@@ -22840,7 +22920,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Diagnoses and resolves VPN connectivity problems according to network security requirements.</t>
+          <t>Diagnoses and resolves VPN connectivity problems using security policies and troubleshooting protocols.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -23161,12 +23241,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Basic Feature Testing</t>
+          <t>Feature Functionality Testing</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Tests the functionality of basic network security features to confirm they meet defined security requirements.</t>
+          <t>Tests basic firewall and VPN features to ensure they meet defined security requirements.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -23188,11 +23268,11 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>basic feature testing; functionality verification; security requirements; network security requirements; compliance checking</t>
+          <t>basic feature verification; security requirement testing; functional assessment; network device testing; compliance validation</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -23203,14 +23283,14 @@
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Basic Feature Testing</t>
+          <t>Feature Functionality Testing</t>
         </is>
       </c>
       <c r="S145" t="b">
         <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
@@ -23220,19 +23300,19 @@
       <c r="V145" t="inlineStr"/>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Tests the functionality of basic network security features to confirm they meet defined security requirements.</t>
+          <t>Conducts hands‑on tests to verify basic firewall and VPN features meet defined security requirements.</t>
         </is>
       </c>
       <c r="X145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>basic feature testing, functionality verification, security requirements, network testing, compliance checking</t>
+          <t>basic feature verification, security requirement testing, functional assessment, network device testing, compliance validation</t>
         </is>
       </c>
       <c r="Z145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -23305,7 +23385,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Digital Tool Design Understanding</t>
+          <t>Digital Tool Design Recognition</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -23336,7 +23416,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>human-computer interaction; usability; software architecture; design principles; digital tool development</t>
+          <t>human-computer interaction; usability; design principles; digital tool development; recognition</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -23351,15 +23431,19 @@
         </is>
       </c>
       <c r="S146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T146" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U146" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>keep:2, "Digital Tool Design Recognition":1</t>
+          <t>keep:0, "Digital Tool Design Recognition":2, "Digital Tool Design Familiarisation":1</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
@@ -23376,7 +23460,7 @@
         </is>
       </c>
       <c r="Z146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -23454,7 +23538,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Identifies and documents emerging technologies and practices relevant to organisational needs.</t>
+          <t>Identifies and documents emerging technologies and practices, ensuring relevance to organisational needs.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -23480,7 +23564,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>emerging technologies; technology scouting; trend analysis; strategic foresight; technology roadmapping</t>
+          <t>technology scouting; trend analysis; strategic foresight; technology roadmapping; emerging technologies</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -23498,12 +23582,12 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Emerging Technology Identification":1</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
@@ -23646,12 +23730,12 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>keep:2, "Terminology Translation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
@@ -23741,12 +23825,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Information Source Access</t>
+          <t>Information Source Assessment</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Accesses relevant IT industry sources to stay informed on emerging technologies.</t>
+          <t>Accesses relevant IT industry sources to stay updated on emerging technologies.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -23772,7 +23856,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>technology scouting; IT industry trends; information retrieval; emerging tech monitoring; access sources</t>
+          <t>technology scouting; IT industry trends; information retrieval; information source; emerging tech monitoring</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -23787,19 +23871,15 @@
         </is>
       </c>
       <c r="S149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>keep:1, "Information Source Access":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -23924,7 +24004,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>technology trends; digital transformation; emerging technologies; IT industry developments; discussion</t>
+          <t>technology trends; emerging technologies; IT industry developments; discussion; technical communication</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -23942,12 +24022,12 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "IT Industry Discussion":1</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
@@ -24042,7 +24122,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Identifies changes to organisational technologies and practices required based on strategies and documents them.</t>
+          <t>Identifies changes to organisational technologies and practices required based on strategies, documenting them for implementation.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -24095,7 +24175,7 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>keep:2, "Organisational Change Documentation":1</t>
+          <t>keep:1, "Organisational Change Identification":1, "Technology Change Planning":1</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
@@ -24220,7 +24300,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>continuous learning; career development; learning &amp; development; CPD opportunities; recognition</t>
+          <t>continuous learning; career development; learning &amp; development; CPD opportunities; professional development</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -24238,12 +24318,12 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>keep:2, "Professional Development Opportunity Recognition":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
@@ -24333,12 +24413,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Regulatory Compliance Responsibility</t>
+          <t>Regulatory Compliance Awareness</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Takes personal responsibility for complying with applicable laws and regulations by following procedures.</t>
+          <t>Takes personal responsibility to ensure work complies with applicable laws and regulations by following procedures.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -24364,7 +24444,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>legal obligations; governance frameworks; compliance management systems; regulatory responsibility; personal responsibility</t>
+          <t>legal obligations; governance frameworks; audit procedures; compliance management systems; regulatory awareness</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -24379,19 +24459,15 @@
         </is>
       </c>
       <c r="S153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>keep:0, "Regulatory Compliance Responsibility":3</t>
+          <t>keep:0, "Regulatory Compliance":1, "Regulatory Compliance Adherence":1, "Regulatory Compliance Management":1</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
@@ -24512,7 +24588,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>literature review; critical appraisal; academic databases; citation management; information application</t>
+          <t>literature review; critical appraisal; academic databases; citation management; application</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -24534,12 +24610,12 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>keep:0, "Information Application":2, "Information Evaluation":1</t>
+          <t>keep:0, "Information Application":3</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
@@ -24559,9 +24635,13 @@
         <v>1</v>
       </c>
       <c r="AA154" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB154" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>Technical Documentation Interpretation (LLM verified, sim=0.61)</t>
+        </is>
+      </c>
       <c r="AC154" t="b">
         <v>0</v>
       </c>
@@ -24629,12 +24709,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Risk Opportunity Analysis</t>
+          <t>Threat Opportunity Analysis</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Risk and opportunity analysis of emerging technologies regarding organisational impacts.</t>
+          <t>Risk and opportunity analysis of emerging technologies to determine organisational impacts.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -24675,15 +24755,19 @@
         </is>
       </c>
       <c r="S155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T155" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U155" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>keep:1, "Opportunity Threat Analysis":1, "Risk and Opportunity Analysis":1</t>
+          <t>keep:0, "Threat Opportunity Analysis/Opportunity Threat Analysis":3</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
@@ -24703,13 +24787,9 @@
         <v>0</v>
       </c>
       <c r="AA155" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>Technology Impact Evaluation (LLM verified, sim=0.66)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB155" t="inlineStr"/>
       <c r="AC155" t="b">
         <v>0</v>
       </c>
@@ -24808,7 +24888,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>stakeholder engagement; feedback collection; report synthesis; organizational liaison; feedback integration</t>
+          <t>stakeholder engagement; feedback collection; report synthesis; integration; organizational liaison</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -24926,7 +25006,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Develops and documents strategic plans to prepare the organization for emerging technology impacts.</t>
+          <t>Develops and documents strategic approaches to prepare the organization for emerging technology impacts.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -24952,7 +25032,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>technology foresight; scenario planning; change management; digital transformation strategy; emerging technology</t>
+          <t>emerging technology; technology foresight; scenario planning; change management; digital transformation strategy</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -24974,12 +25054,12 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>keep:0, "Strategy Development":2, "Strategic Planning":1</t>
+          <t>keep:0, "Strategy Development":3</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -25221,7 +25301,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Technology Impact Evaluation</t>
+          <t>Emerging Technology Impact Evaluation</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -25267,15 +25347,19 @@
         </is>
       </c>
       <c r="S159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T159" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U159" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>keep:2, "Emerging Technology Impact Evaluation":1</t>
+          <t>keep:1, "Emerging Technology Impact Evaluation":2</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
@@ -25365,12 +25449,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Technology Strategy Planning</t>
+          <t>Emerging Technology Planning</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Implements technology solutions using proven methods on schedule.</t>
+          <t>Designs and executes implementation plans using proven methods to deploy technology solutions on schedule.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -25396,7 +25480,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>implementation roadmap; change management; deployment strategy; stakeholder alignment; technology</t>
+          <t>implementation roadmap; change management; deployment strategy; stakeholder alignment; emerging technology</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -25418,12 +25502,12 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>keep:0, "Technology Strategy Planning/Emerging Technology Strategy Planning":3</t>
+          <t>keep:1, "Emerging Technology Planning/Emerging Technology Strategy Planning":2</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
@@ -25432,7 +25516,7 @@
         </is>
       </c>
       <c r="X160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y160" t="inlineStr">
         <is>
@@ -25572,12 +25656,12 @@
         <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>keep:1, "Abstract Design Creation":1, "Abstract Design":1</t>
+          <t>keep:0, "Abstract Script Design":1, "Abstract Design Creation":1, "Script Development":1</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
@@ -25708,7 +25792,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>algorithm; computational thinking; data structures; complexity analysis; pseudocode</t>
+          <t>computational thinking; data structures; complexity analysis; pseudocode; algorithm</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -25726,7 +25810,7 @@
         <v>1</v>
       </c>
       <c r="T162" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
@@ -25835,7 +25919,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Algorithm Termination Assurance</t>
+          <t>Algorithm Termination Verification</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -25866,7 +25950,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>algorithm analysis; termination proof; formal verification; computational complexity; assurance</t>
+          <t>algorithm analysis; termination proof; formal verification; computational complexity; possible situations</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -25881,15 +25965,19 @@
         </is>
       </c>
       <c r="S163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T163" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U163" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Algorithm Termination Verification":2, "Algorithm Termination Assurance":1</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
@@ -25994,7 +26082,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Identifies automation guidelines and instructions for applicable procedures in system design.</t>
+          <t>Identifies automation guidelines and instructions and identifies applicable procedures for system design.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -26020,7 +26108,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>process automation; interpretation; RPA guidelines; workflow documentation; automation compliance</t>
+          <t>process automation; standard operating procedures; RPA guidelines; automation compliance; interpretation</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -26148,7 +26236,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Identifies scripts' uncovered sections and incorrect implementations, ensuring semantic accuracy.</t>
+          <t>Identifies uncovered sections and incorrect implementations in scripts, ensuring semantic accuracy.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -26192,12 +26280,12 @@
         <v>0</v>
       </c>
       <c r="T165" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Script Semantic Verification":1</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
@@ -26297,7 +26385,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Code Debugging</t>
+          <t>Code Syntax Debugging</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26328,7 +26416,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>debugging; syntax errors; semantic errors; troubleshooting; code</t>
+          <t>debugging; syntax errors; semantic errors; code; troubleshooting</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -26343,19 +26431,15 @@
         </is>
       </c>
       <c r="S166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T166" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>keep:0, "Code Debugging":3</t>
+          <t>keep:1, "Code Error Debugging":1, "Code Syntax Semantic Debugging":1</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
@@ -26455,7 +26539,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Team Collaboration</t>
+          <t>Problem Solving Collaboration</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -26486,7 +26570,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>cross-functional collaboration; stakeholder engagement; hybrid teamwork; perspective gathering; solution quality improvement</t>
+          <t>cross-functional collaboration; stakeholder engagement; perspective gathering; solution quality improvement; problem solving</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -26508,12 +26592,12 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>keep:0, "Team Collaboration":3</t>
+          <t>keep:0, "Problem Solving Collaboration":2, "Team Problem Solving":1</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
@@ -26530,20 +26614,16 @@
         </is>
       </c>
       <c r="Z167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
       </c>
       <c r="AB167" t="inlineStr"/>
       <c r="AC167" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD167" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 1.3 Discuss and establish potential solutions and process id</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
@@ -26617,7 +26697,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Feedback Sign-off</t>
+          <t>Feedback Incorporation</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -26648,7 +26728,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>stakeholder engagement; sign‑off workflow; feedback loop; collaboration tools; hybrid communication</t>
+          <t>stakeholder engagement; sign‑off workflow; feedback loop; incorporation; hybrid communication</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -26670,12 +26750,12 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>keep:0, "Feedback Sign-off":2, "Feedback Incorporation":1</t>
+          <t>keep:0, "Feedback Incorporation":3</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
@@ -26692,7 +26772,7 @@
         </is>
       </c>
       <c r="Z168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -26824,12 +26904,12 @@
         <v>0</v>
       </c>
       <c r="T169" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>keep:1, "Formula Interpretation":1, "Formula Interpretation and Manipulation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
@@ -26964,7 +27044,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>workflow analysis; process mapping; automation assessment; RPA; business process improvement</t>
+          <t>workflow analysis; process mapping; automation assessment; process requiring automation; business process improvement</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -26986,12 +27066,12 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>keep:0, "Process Automation Identification/Process Identification":2, "Automation Requirement Analysis":1</t>
+          <t>keep:0, "Process Identification/Process Automation Identification":3</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
@@ -27008,7 +27088,7 @@
         </is>
       </c>
       <c r="Z170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -27140,12 +27220,12 @@
         <v>0</v>
       </c>
       <c r="T171" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>keep:2, "Script Implementation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
@@ -27245,7 +27325,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Team Solution Discussion</t>
+          <t>Solution Brainstorming</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -27276,7 +27356,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>collaborative ideation; requirements gathering; discussion; solution; remote teamwork</t>
+          <t>collaborative ideation; requirements gathering; problem‑solving facilitation; brainstorming; solution</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -27298,12 +27378,12 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>keep:0, "Team Solution Discussion/Solution Discussion":3</t>
+          <t>keep:1, "Solution Brainstorming":2</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
@@ -27403,12 +27483,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Technical Documentation Analysis</t>
+          <t>Technical Documentation Assessment</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Analyses complex technical documentation to ensure accuracy.</t>
+          <t>Analyses complex technical documents to ensure accuracy.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -27434,7 +27514,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>documentation review; error correction; technical writing standards; quality assurance; content management systems</t>
+          <t>documentation review; error correction; technical writing standards; quality assurance; technical documentation</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -27449,15 +27529,19 @@
         </is>
       </c>
       <c r="S173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T173" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U173" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Technical Documentation Assessment":2, "Technical Documentation Review":1</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
@@ -27474,7 +27558,7 @@
         </is>
       </c>
       <c r="Z173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -27557,7 +27641,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Technical Documentation Creation</t>
+          <t>Internal Documentation Creation</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -27588,7 +27672,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>technical writing; SOP; documentation standards; Confluence; documentation creation</t>
+          <t>technical writing; SOP; documentation standards; internal documentation; Confluence</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -27603,15 +27687,19 @@
         </is>
       </c>
       <c r="S174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T174" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U174" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Internal Documentation Creation":2</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
@@ -27874,7 +27962,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>The worker describes algorithmic solutions for the identified problem using sequence, selection and iteration structures.</t>
+          <t>Explains algorithmic solutions for a problem using sequence, selection, and iteration structures.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -27900,7 +27988,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>algorithmic solution description; sequence structures; selection structures; iteration structures; identified problem</t>
+          <t>algorithmic solution; sequence structure; selection structure; iteration structure; problem description</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -27928,7 +28016,7 @@
       <c r="V176" t="inlineStr"/>
       <c r="W176" t="inlineStr">
         <is>
-          <t>The worker describes algorithmic solutions for the identified problem using sequence, selection and iteration structures.</t>
+          <t>Explains algorithmic solutions for a problem using sequence, selection, and iteration structures.</t>
         </is>
       </c>
       <c r="X176" t="b">
@@ -27936,11 +28024,11 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>algorithmic solution description, sequence structures, selection structures, iteration structures, problem analysis</t>
+          <t>algorithmic solution, sequence structure, selection structure, iteration structure, problem description</t>
         </is>
       </c>
       <c r="Z176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -28023,12 +28111,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Abstract Design Revision</t>
+          <t>Abstract Design Translation</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Reviews the abstract script design, corrects omissions and errors, and translates it into code following organisational guidelines.</t>
+          <t>Reviews abstract designs for omissions and errors, then translates them into code following organisational guidelines.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -28050,11 +28138,11 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>abstract design review; design amendment; error correction; language translation; revision</t>
+          <t>abstract design; design review; error amendment; code translation; chosen language</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -28066,14 +28154,14 @@
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Abstract Design Revision</t>
+          <t>Abstract Design Translation</t>
         </is>
       </c>
       <c r="S177" t="b">
         <v>0</v>
       </c>
       <c r="T177" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
@@ -28083,7 +28171,7 @@
       <c r="V177" t="inlineStr"/>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Reviews the abstract script design, corrects omissions and errors, and translates it into code following organisational guidelines.</t>
+          <t>Reviews abstract designs for omissions and errors, then translates them into code following organisational guidelines.</t>
         </is>
       </c>
       <c r="X177" t="b">
@@ -28091,7 +28179,7 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>abstract design review, design amendment, error correction, language translation, organisational guidelines</t>
+          <t>abstract design, design review, error amendment, code translation, organisational guidelines</t>
         </is>
       </c>
       <c r="Z177" t="b">
@@ -28178,12 +28266,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Problem Confirmation</t>
+          <t>Issue Confirmation</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Confirms identified problems with team members and collaboratively resolves any issues as required.</t>
+          <t>Confirms identified problems with team members and resolves them as required, ensuring shared understanding and agreement.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -28209,7 +28297,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>problem confirmation; team communication; issue resolution; stakeholder engagement; team members</t>
+          <t>problem confirmation; team communication; issue resolution; collaborative verification; team members</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -28220,7 +28308,7 @@
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Problem Confirmation</t>
+          <t>Issue Confirmation</t>
         </is>
       </c>
       <c r="S178" t="b">
@@ -28237,7 +28325,7 @@
       <c r="V178" t="inlineStr"/>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Confirms identified problems with team members and collaboratively resolves any issues as required.</t>
+          <t>Confirms identified problems with team members and resolves them as required, ensuring shared understanding and agreement.</t>
         </is>
       </c>
       <c r="X178" t="b">
@@ -28245,7 +28333,7 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>problem confirmation, team communication, issue resolution, stakeholder engagement, collaborative verification</t>
+          <t>problem confirmation, team communication, issue resolution, collaborative verification, stakeholder alignment</t>
         </is>
       </c>
       <c r="Z178" t="b">
@@ -28332,7 +28420,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Active Listening</t>
+          <t>Active Listening Communication</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -28378,19 +28466,15 @@
         </is>
       </c>
       <c r="S179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T179" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>keep:0, "Active Listening":3</t>
+          <t>keep:1, "Active Listening":1, "Perspective Identification":1</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
@@ -28490,7 +28574,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Incident Response Design</t>
+          <t>Incident Response Procedure Design</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -28521,7 +28605,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>security incident management; audit procedures; playbook development; SOC processes; security design</t>
+          <t>security incident management; audit procedures; playbook development; response procedure; NIST CSF</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -28536,15 +28620,19 @@
         </is>
       </c>
       <c r="S180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T180" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U180" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Incident Response Procedure Design":3</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
@@ -28698,7 +28786,7 @@
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>keep:2, "Security Audit Execution":1</t>
+          <t>keep:2, "Log Analysis":1</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
@@ -28803,7 +28891,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Identifies standard vulnerability types across environments in hybrid network security assessments.</t>
+          <t>Identifies standard vulnerability types across environments during hybrid network security assessments.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -28956,12 +29044,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Penetration Testing</t>
+          <t>Security Audit Execution</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Tests system vulnerabilities using auditing techniques.</t>
+          <t>Tests system vulnerabilities using auditing techniques to exploit them.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -28987,7 +29075,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>ethical hacking; vulnerability assessment; penetration testing; Nmap; exploit development</t>
+          <t>ethical hacking; vulnerability assessment; audit; execution; exploit development</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -29009,12 +29097,12 @@
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>keep:0, "Penetration Testing/Audit and Penetration Testing":3</t>
+          <t>keep:1, "Security Audit Execution":2</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
@@ -29038,7 +29126,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>Security Audit Testing</t>
+          <t>Security Audit Execution</t>
         </is>
       </c>
       <c r="AC183" t="b">
@@ -29118,12 +29206,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk Management Determination</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Designs and determines risk management components based on network security design specifications in hybrid environments.</t>
+          <t>Determines risk management components based on network security design specifications in hybrid environments.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -29149,7 +29237,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>risk management; network security; threat assessment; security architecture; security design specifications</t>
+          <t>risk management; network security; threat assessment; security architecture; compliance standards</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -29171,12 +29259,12 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>keep:0, "Risk Management Planning":3</t>
+          <t>keep:0, "Risk Management Determination":2, "Risk Management Planning":1</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
@@ -29193,14 +29281,14 @@
         </is>
       </c>
       <c r="Z184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA184" t="b">
         <v>1</v>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Threat Model Design (LLM verified, sim=0.71)</t>
         </is>
       </c>
       <c r="AC184" t="b">
@@ -29280,12 +29368,12 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk Management Plan Development</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Determines and documents risk management plans in hybrid environments.</t>
+          <t>Determines, documents and plans risk management plans in hybrid environments according to organisational standards.</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -29329,16 +29417,16 @@
         <v>1</v>
       </c>
       <c r="T185" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.9</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Risk Management Plan Development":3</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
@@ -29438,12 +29526,12 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Security Audit Testing</t>
+          <t>Security Audit Execution</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Tests security controls through penetration testing to reveal vulnerabilities.</t>
+          <t>Tests security controls using penetration testing methods to test vulnerabilities.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -29469,7 +29557,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>penetration testing; vulnerability assessment; audit; Metasploit; risk assessment</t>
+          <t>penetration testing; vulnerability assessment; risk assessment; audit; execution</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -29484,19 +29572,15 @@
         </is>
       </c>
       <c r="S186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T186" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>keep:0, "Security Audit Testing":2, "Security Testing Execution":1</t>
+          <t>keep:2, "Security Testing Execution":1</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
@@ -29596,7 +29680,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Security Controls Evaluation</t>
+          <t>Security Information Evaluation</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -29627,7 +29711,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>risk assessment; threat modeling; security frameworks; countermeasure planning; security controls</t>
+          <t>risk assessment; threat modeling; security frameworks; countermeasure planning; security information</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -29642,15 +29726,19 @@
         </is>
       </c>
       <c r="S187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T187" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U187" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>keep:2, "Security Control Assessment":1</t>
+          <t>keep:0, "Security Information Evaluation":2, "Security Control Planning":1</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
@@ -29781,7 +29869,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>cost estimation; cost analysis; asset valuation; ROI calculation; budgeting</t>
+          <t>cost analysis; asset valuation; ROI calculation; budgeting; estimation</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -29904,12 +29992,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Security Design Planning</t>
+          <t>Network Security Design Planning</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Designs network security planning phase, integrating hybrid architecture with organisational requirements.</t>
+          <t>Designs network security design planning phase for hybrid architecture in line with organisational requirements.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -29950,15 +30038,19 @@
         </is>
       </c>
       <c r="S189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T189" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U189" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Network Security Design Planning":3</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
@@ -30063,7 +30155,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Develops and documents security policies across hybrid environments, technical controls and organizational standards.</t>
+          <t>Develops and documents security policies across hybrid environments.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -30216,7 +30308,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Security Problem Solving</t>
+          <t>Security Troubleshooting</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -30247,7 +30339,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>cybersecurity; incident response; threat intelligence; data aggregation; problem solving</t>
+          <t>cybersecurity; incident response; threat intelligence; SIEM tools; troubleshooting</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -30262,19 +30354,15 @@
         </is>
       </c>
       <c r="S191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T191" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>keep:0, "Security Problem Solving":2, "Security Data Analysis":1</t>
+          <t>keep:2, "Security Analysis":1</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
@@ -30379,7 +30467,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Develops and documents technical information using factual data and industry terminology to plan organisational plans, security policies and breach documentation.</t>
+          <t>Develops and documents technical information with factual data and industry terms for plans, policies, and breach reports.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -30423,12 +30511,12 @@
         <v>0</v>
       </c>
       <c r="T192" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Technical Documentation Writing":1</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
@@ -30532,7 +30620,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Threat Modelling</t>
+          <t>Threat Model Design</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -30563,7 +30651,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>network security; attack surface analysis; STRIDE methodology; security architecture; threat model</t>
+          <t>network security; STRIDE methodology; security architecture; threat model; attack surface analysis</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -30581,16 +30669,16 @@
         <v>1</v>
       </c>
       <c r="T193" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.9</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Threat Model Design":2</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
@@ -30690,12 +30778,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Asset Identification</t>
+          <t>Organisational Asset Identification</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Identifies organisational assets that require protection for network security planning.</t>
+          <t>Identifies all organisational assets that require protection within the network environment.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -30713,15 +30801,15 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>practical</t>
+          <t>theoretical</t>
         </is>
       </c>
       <c r="N194" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>assets requiring protection; critical assets; information resources; data repositories; asset register</t>
+          <t>asset inventory; protection requirements; organisational resources; asset classification; assets requiring protection</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -30732,14 +30820,14 @@
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Asset Identification</t>
+          <t>Organisational Asset Identification</t>
         </is>
       </c>
       <c r="S194" t="b">
         <v>0</v>
       </c>
       <c r="T194" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U194" t="inlineStr">
         <is>
@@ -30749,7 +30837,7 @@
       <c r="V194" t="inlineStr"/>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Identifies and documents organisational assets that require protection to support network security planning.</t>
+          <t>Identifies and documents all organisational assets that require protection within the network environment.</t>
         </is>
       </c>
       <c r="X194" t="b">
@@ -30757,7 +30845,7 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>critical assets, information resources, hardware inventory, data repositories, asset register</t>
+          <t>asset inventory, protection requirements, organisational resources, security scope, asset classification</t>
         </is>
       </c>
       <c r="Z194" t="b">
@@ -30844,12 +30932,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Document Distribution</t>
+          <t>Document Submission Coordination</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Documents security documents for designated personnel, seeks feedback and submits responses appropriately.</t>
+          <t>Submits security documents to designated personnel, solicits feedback, and addresses comments to finalise the documentation.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -30871,11 +30959,11 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>document distribution; feedback solicitation; stakeholder communication; revision handling; document submission</t>
+          <t>document submission; designated personnel; feedback solicitation; comment response; finalisation</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -30886,14 +30974,14 @@
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Document Distribution</t>
+          <t>Document Submission Coordination</t>
         </is>
       </c>
       <c r="S195" t="b">
         <v>0</v>
       </c>
       <c r="T195" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
@@ -30903,19 +30991,19 @@
       <c r="V195" t="inlineStr"/>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Distributes security documents to designated personnel, actively seeks feedback and responds to comments appropriately.</t>
+          <t>Submits security documents to designated personnel, solicits feedback, and addresses comments to finalise the documentation.</t>
         </is>
       </c>
       <c r="X195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>document distribution, feedback solicitation, stakeholder communication, revision handling, security documentation</t>
+          <t>document submission, designated personnel, feedback solicitation, comment response, finalisation</t>
         </is>
       </c>
       <c r="Z195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -31048,12 +31136,12 @@
         <v>0</v>
       </c>
       <c r="T196" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Access Control Configuration":1</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
@@ -31185,7 +31273,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>cloud infrastructure; metrics-driven scaling; infrastructure as code; virtual machine scaling; autoscaling</t>
+          <t>cloud infrastructure; metrics-driven scaling; virtual machine scaling; autoscaling; configuration</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -31314,7 +31402,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Discusses hybrid cloud options while comparing models and services against business requirements.</t>
+          <t>Discusses hybrid cloud options by comparing models and services against business requirements.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -31340,7 +31428,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>cloud computing; service models; cloud solution; Azure; cost-benefit analysis</t>
+          <t>cloud computing; service models; AWS; Azure; cloud solution</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -31358,12 +31446,12 @@
         <v>0</v>
       </c>
       <c r="T198" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Cloud Solution Evaluation":1</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
@@ -31495,7 +31583,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>constructive feedback; communication skills; feedback loop; feedback response; feedback handling</t>
+          <t>active listening; constructive feedback; communication skills; feedback loop; response handling</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -31513,7 +31601,7 @@
         <v>0</v>
       </c>
       <c r="T199" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
@@ -31650,7 +31738,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>cloud database; virtual network; Azure SQL Database; DBaaS; managed deployment</t>
+          <t>deployment; virtual network; Azure SQL Database; DBaaS; managed database</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -31668,12 +31756,12 @@
         <v>0</v>
       </c>
       <c r="T200" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Managed Database Deployment":1</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
@@ -31929,7 +32017,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Routine Task Management</t>
+          <t>Routine Task Planning</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -31975,19 +32063,15 @@
         </is>
       </c>
       <c r="S202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>keep:0, "Routine Task Management":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
@@ -32088,7 +32172,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Scaling Performance Testing</t>
+          <t>Automatic Scaling Testing</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -32134,15 +32218,19 @@
         </is>
       </c>
       <c r="S203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T203" t="n">
-        <v>0</v>
-      </c>
-      <c r="U203" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>keep:0, "Autoscaling Testing":1, "Scaling Testing":1, "Scaling Test":1</t>
+          <t>keep:0, "Automatic Scaling Testing":2, "Autoscaling Testing":1</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
@@ -32248,7 +32336,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Identifies impact of shared security responsibility models in hybrid environments on organisational risk.</t>
+          <t>Identifies impact of shared security responsibility models in hybrid environments on organizational risk.</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -32297,7 +32385,7 @@
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>keep:2, "Security Responsibility Identification":1</t>
+          <t>keep:2, "Security Responsibility Impact Identification":1</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
@@ -32429,7 +32517,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>stakeholder management; documentation; reporting; work; liaison</t>
+          <t>stakeholder management; documentation; reporting; liaison; work communication</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -32456,7 +32544,7 @@
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>keep:0, "Work Communication":2, "Stakeholder Communication":1</t>
+          <t>keep:0, "Work Communication/Work Documentation Communication":2, "Stakeholder Communication":1</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
@@ -32480,7 +32568,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>Documentation Preparation</t>
+          <t>Work Documentation Preparation</t>
         </is>
       </c>
       <c r="AC205" t="b">
@@ -32561,12 +32649,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Storage Allocation Management</t>
+          <t>Storage Allocation</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Defines, adds and expands VM storage to meet business requirements.</t>
+          <t>Defines, adds and expands VM storage volumes to meet business requirements.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -32592,7 +32680,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>virtualization; storage provisioning; capacity planning; hypervisor; storage allocation</t>
+          <t>virtualization; storage provisioning; capacity planning; storage allocation; cloud IaaS</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -32607,15 +32695,19 @@
         </is>
       </c>
       <c r="S206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T206" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U206" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Storage Allocation/Virtual-Machine Storage Allocation":2, "Storage Allocation Configuration":1</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
@@ -32716,7 +32808,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Documentation Preparation</t>
+          <t>Work Documentation Preparation</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -32747,7 +32839,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>technical writing; documentation standards; communication; collaboration tools; user manuals</t>
+          <t>technical writing; documentation standards; version control; user manuals; work documentation</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -32774,7 +32866,7 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>keep:1, "Documentation Preparation":2</t>
+          <t>keep:0, "Work Documentation Preparation/Documentation Preparation":2, "Work Documentation":1</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
@@ -32910,7 +33002,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>hypervisor; virtual machine; OS deployment; virtualization platform; infrastructure as code</t>
+          <t>hypervisor; virtual machine; infrastructure as code; OS deployment; virtualization platform</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -33034,12 +33126,12 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Virtual Network Creation</t>
+          <t>Virtual Network Design</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Creates multi‑tier virtual network that supports core services and enables autoscaling.</t>
+          <t>Creates multi‑tier virtual network to support core services and enable autoscaling.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -33065,7 +33157,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>software-defined networking; multi-tier architecture; cloud networking; autoscaling; virtual network</t>
+          <t>software-defined networking; cloud networking; autoscaling; load balancing; virtual network design</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -33080,19 +33172,15 @@
         </is>
       </c>
       <c r="S209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T209" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>keep:0, "Virtual Network Creation":3</t>
+          <t>keep:0, "Virtual Network Configuration":1, "Virtual Network Creation":1, "Virtual Network Planning":1</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
@@ -33224,7 +33312,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>capacity planning; business requirements analysis; resource allocation; workload definition; workload management tools</t>
+          <t>capacity planning; business requirements analysis; resource allocation; workload management tools; workload definition</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -33352,17 +33440,17 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Security Responsibility Assignment</t>
+          <t>Security Role Allocation</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Identifies and allocates security duties in line with policies, business protocols and job functions.</t>
+          <t>Identifies and assigns security responsibilities based on policies, protocols and specific work functions.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>domain_knowledge</t>
+          <t>cognitive</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -33383,7 +33471,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>security responsibilities; security policies; business protocols; work function; responsibility allocation</t>
+          <t>security policies; business protocols; work function; responsibility assignment; role allocation</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -33394,7 +33482,7 @@
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr">
         <is>
-          <t>Security Responsibility Assignment</t>
+          <t>Security Role Allocation</t>
         </is>
       </c>
       <c r="S211" t="b">
@@ -33411,7 +33499,7 @@
       <c r="V211" t="inlineStr"/>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Identifies and allocates security duties in line with policies, business protocols and job functions.</t>
+          <t>Identifies and assigns security responsibilities based on policies, protocols and specific work functions.</t>
         </is>
       </c>
       <c r="X211" t="b">
@@ -33419,7 +33507,7 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>security responsibilities, security policies, business protocols, work function, responsibility allocation</t>
+          <t>security policies, business protocols, work function, responsibility assignment, role allocation</t>
         </is>
       </c>
       <c r="Z211" t="b">
@@ -33538,7 +33626,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>user creation; group management; identity provisioning; cloud infrastructure; business requirements</t>
+          <t>user creation; group management; identity provisioning; cloud infrastructure; infrastructure management</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -33578,7 +33666,7 @@
         </is>
       </c>
       <c r="Z212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -33662,17 +33750,17 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Documentation Storage</t>
+          <t>Documentation Archiving</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Stores user documentation in designated repositories in line with organisational policies and procedures.</t>
+          <t>The worker saves and stores user documentation in accordance with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>technical</t>
+          <t>domain_knowledge</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -33693,7 +33781,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>user documentation; document storage; organisational policy compliance; record keeping; data archiving</t>
+          <t>document storage; organisational policies; compliance standards; record keeping; archival process</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -33704,7 +33792,7 @@
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr">
         <is>
-          <t>Documentation Storage</t>
+          <t>Documentation Archiving</t>
         </is>
       </c>
       <c r="S213" t="b">
@@ -33721,7 +33809,7 @@
       <c r="V213" t="inlineStr"/>
       <c r="W213" t="inlineStr">
         <is>
-          <t>Stores user documentation in designated repositories in line with organisational policies and procedures.</t>
+          <t>The worker saves and stores user documentation in accordance with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="X213" t="b">
@@ -33729,11 +33817,11 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>document storage, organisational policy compliance, repository management, record keeping, data archiving</t>
+          <t>document storage, organisational policies, compliance standards, record keeping, archival process</t>
         </is>
       </c>
       <c r="Z213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -33870,7 +33958,7 @@
         <v>0</v>
       </c>
       <c r="T214" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr">
@@ -34011,7 +34099,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>Active Directory; LDAP; identity management; access control; directory service administration</t>
+          <t>Active Directory; LDAP; identity management; group policy; directory service administration</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -34139,12 +34227,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Disk Partitioning Scheme Creation</t>
+          <t>Disk Partitioning Scheme Design</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Creates disk partitioning scheme, file systems and virtual memory aligned with business requirements.</t>
+          <t>Creates disk partitioning scheme, file systems, and virtual memory according to business needs.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -34170,7 +34258,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>storage architecture; file system layout; logical volume management; partitioning tools; disk partitioning scheme</t>
+          <t>storage architecture; file system layout; scheme; partitioning tools; disk</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -34197,7 +34285,7 @@
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>keep:0, "Disk Partitioning Scheme Creation":2, "Disk Partitioning Scheme Design":1</t>
+          <t>keep:0, "Disk Partitioning Scheme Design/Disk Partitioning Design":2, "Disk Partitioning Scheme Creation":1</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
@@ -34333,7 +34421,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>e-waste regulations; hazardous waste management; environmental compliance; WEEE directive; asset disposal procedures</t>
+          <t>e-waste regulations; hazardous waste management; environmental compliance; asset disposal procedures; excess equipment</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -34348,15 +34436,19 @@
         </is>
       </c>
       <c r="S217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T217" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U217" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>keep:2, "Equipment Disposal":1</t>
+          <t>keep:1, "e-waste disposal compliance":2</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
@@ -34373,7 +34465,7 @@
         </is>
       </c>
       <c r="Z217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -34496,7 +34588,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>e-waste compliance; asset disposition; recycling procedures; inventory decommissioning; equipment disposal</t>
+          <t>e-waste compliance; asset disposition; equipment disposal; recycling procedures; inventory decommissioning</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -34514,12 +34606,12 @@
         <v>0</v>
       </c>
       <c r="T218" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="U218" t="inlineStr"/>
       <c r="V218" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Equipment Disposal Management":1, "Equipment Disposal Execution":1, "Equipment Disposal Coordination":1</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
@@ -34659,7 +34751,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>network operating system; server application deployment; configuration; system installation; network services (DHCP; DNS; VPN)</t>
+          <t>network operating system; server application deployment; network configuration; system installation; network services (DHCP; DNS; VPN)</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -34787,12 +34879,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Patch Management</t>
+          <t>Patch Management Execution</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Operates patch management to meet security and reliability standards.</t>
+          <t>Operates patch management to maintain operating system and applications in line with security and reliability requirements.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -34818,7 +34910,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>vulnerability remediation; OS and application updates; security compliance; patch deployment tools; reliability requirements</t>
+          <t>vulnerability remediation; OS and application updates; security compliance; patch deployment tools; patch management</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -34833,19 +34925,15 @@
         </is>
       </c>
       <c r="S220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T220" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U220" t="inlineStr"/>
       <c r="V220" t="inlineStr">
         <is>
-          <t>keep:1, "Patch Management":2</t>
+          <t>keep:2, "System Patch Deployment":1</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
@@ -34950,7 +35038,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Security Access Management</t>
+          <t>User Access Management</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -34981,7 +35069,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>identity and access management; role‑based access control; network security policies; user provisioning; authentication/authorization tools</t>
+          <t>identity and access management; role‑based access control; user provisioning; authentication/authorization tools; network access</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -34996,15 +35084,19 @@
         </is>
       </c>
       <c r="S221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T221" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U221" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "User Access Management":2</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
@@ -35021,7 +35113,7 @@
         </is>
       </c>
       <c r="Z221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -35268,7 +35360,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Server Documentation Preparation</t>
+          <t>Server Documentation</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -35299,7 +35391,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>configuration management; change management; technical writing; system administration; server</t>
+          <t>configuration management; change management; technical writing; system administration; server administration</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -35314,15 +35406,19 @@
         </is>
       </c>
       <c r="S223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T223" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U223" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>keep:2, "Server Configuration Documentation":1</t>
+          <t>keep:1, "Server Documentation":2</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
@@ -35432,7 +35528,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Prepares server installations by identifying organisational needs and installing appropriate applications and features.</t>
+          <t>Prepares server installations by identifying organisational needs and identifying appropriate applications and features.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -35476,12 +35572,12 @@
         <v>0</v>
       </c>
       <c r="T224" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Server Installation Preparation":1</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
@@ -35590,7 +35686,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Server Testing</t>
+          <t>Server Performance Testing</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -35636,19 +35732,15 @@
         </is>
       </c>
       <c r="S225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T225" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
-          <t>keep:0, "Server Testing":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
@@ -35784,7 +35876,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>IT infrastructure; network diagnostics; system administration; hardware failure; server troubleshooting</t>
+          <t>IT infrastructure; system administration; hardware failure; server troubleshooting; server management</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -35916,12 +36008,12 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Stakeholder Communication</t>
+          <t>Stakeholder Communication Planning</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Advises stakeholders by arranging site access and advising users of deployment downtime expectations.</t>
+          <t>Advises users of deployment downtime while arranging site access for stakeholders.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -35962,19 +36054,15 @@
         </is>
       </c>
       <c r="S227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T227" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U227" t="inlineStr"/>
       <c r="V227" t="inlineStr">
         <is>
-          <t>keep:0, "Stakeholder Communication":2, "User Communication":1</t>
+          <t>keep:0, "Stakeholder Communication Arrangement":1, "Stakeholder Communication":1, "Stakeholder Communication Advisement":1</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
@@ -36110,7 +36198,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>operating system policies; login scripts; environment variables; configuration management; user environment</t>
+          <t>operating system policies; login scripts; user environment; environment variables; configuration management</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -36242,12 +36330,12 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Connectivity Device Reconfiguration</t>
+          <t>Connectivity Reconfiguration</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Reconnects and reconfigures connectivity devices, setting links to ensure proper server communication.</t>
+          <t>Reconnects and reconfigures network connectivity devices to ensure optimal server communication and performance.</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -36273,7 +36361,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>connectivity devices; network links; device settings; reconfiguration; server communication</t>
+          <t>network devices; connectivity settings; configuration changes; hardware reconnection; connectivity devices</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -36284,7 +36372,7 @@
       <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Connectivity Device Reconfiguration</t>
+          <t>Connectivity Reconfiguration</t>
         </is>
       </c>
       <c r="S229" t="b">
@@ -36301,7 +36389,7 @@
       <c r="V229" t="inlineStr"/>
       <c r="W229" t="inlineStr">
         <is>
-          <t>Re-establishes and adjusts connectivity devices, configuring settings and links to ensure proper server communication.</t>
+          <t>Re-establishes and adjusts network connectivity devices to ensure optimal server communication and performance.</t>
         </is>
       </c>
       <c r="X229" t="b">
@@ -36309,7 +36397,7 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>connectivity devices, network links, device settings, cabling, server communication</t>
+          <t>network devices, connectivity settings, server links, configuration changes, hardware reconnection</t>
         </is>
       </c>
       <c r="Z229" t="b">
@@ -36401,12 +36489,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Server Performance Review</t>
+          <t>Performance Feedback Management</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Seeks and responds to server performance feedback from designated personnel to optimise operations.</t>
+          <t>Seeks server performance feedback from required personnel and responds to improve operation.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -36428,11 +36516,11 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>server performance feedback; personnel input; performance evaluation; response actions; operational optimisation</t>
+          <t>server performance feedback; stakeholder input; response actions; performance monitoring; required personnel</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -36443,14 +36531,14 @@
       <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr">
         <is>
-          <t>Server Performance Review</t>
+          <t>Performance Feedback Management</t>
         </is>
       </c>
       <c r="S230" t="b">
         <v>0</v>
       </c>
       <c r="T230" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U230" t="inlineStr">
         <is>
@@ -36460,7 +36548,7 @@
       <c r="V230" t="inlineStr"/>
       <c r="W230" t="inlineStr">
         <is>
-          <t>Actively solicit, evaluate, and act on server performance feedback from designated personnel to optimise operations.</t>
+          <t>Collects server performance feedback from required personnel and implements appropriate responses to improve operation.</t>
         </is>
       </c>
       <c r="X230" t="b">
@@ -36468,11 +36556,11 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>server performance feedback, personnel input, performance evaluation, response actions, operational optimisation</t>
+          <t>server performance feedback, stakeholder input, response actions, performance monitoring, communication</t>
         </is>
       </c>
       <c r="Z230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -36545,7 +36633,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Communication Tool Identification</t>
+          <t>Communication Technology Identification</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -36576,7 +36664,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>remote collaboration; communication platforms; virtual team tools; video conferencing; digital workflow</t>
+          <t>remote collaboration; communication platforms; virtual team tools; video conferencing; technology</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -36598,12 +36686,12 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>keep:0, "Communication Tool Identification":2, "Collaborative Technology Identification":1</t>
+          <t>keep:0, "Communication Tools Identification/Communication Technology Identification":3</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
@@ -36620,7 +36708,7 @@
         </is>
       </c>
       <c r="Z231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -36693,12 +36781,12 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Virtual Team Protocol Development</t>
+          <t>Virtual Team Conflict Mediation</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Resolution of differing viewpoints in remote teams by mediation techniques during virtual meetings.</t>
+          <t>Mediates differing viewpoints in remote teams using mediation techniques during virtual meetings.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -36724,7 +36812,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>virtual collaboration; conflict resolution; mediation techniques; remote team communication; virtual protocols</t>
+          <t>virtual collaboration; conflict resolution; mediation techniques; remote team communication; conflicting perspectives</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -36742,16 +36830,16 @@
         <v>1</v>
       </c>
       <c r="T232" t="n">
-        <v>0.875</v>
+        <v>0.9</v>
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>keep:1, "Virtual Team Protocol Development":2</t>
+          <t>keep:0, "Virtual Team Conflict Mediation":3</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
@@ -36841,12 +36929,12 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Cyber Security Protocol Creation</t>
+          <t>Cyber Security Protocol Development</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Develops cyber security protocols in accordance with organisational cyber security procedures to safeguard information assets.</t>
+          <t>Develops cyber security protocols in accordance with organisational procedures to safeguard information assets.</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -36872,7 +36960,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>risk assessment; security policy; cyber security protocol; incident response; access control</t>
+          <t>security protocols; security policy; compliance standards; incident response; access control</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -36887,15 +36975,19 @@
         </is>
       </c>
       <c r="S233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T233" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U233" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>keep:2, "Cyber Security Protocol Development":1</t>
+          <t>keep:1, "Cyber Security Protocol Development":2</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
@@ -37134,7 +37226,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Seeks feedback from team members to improve communication processes.</t>
+          <t>Seeks feedback from relevant personnel on team communication practices to improve communication processes.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -37277,7 +37369,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Knowledge Sharing Protocol Development</t>
+          <t>Knowledge Sharing According to Policy</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -37308,7 +37400,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>knowledge sharing; protocol development; knowledge management; team collaboration; knowledge base platforms</t>
+          <t>knowledge sharing; knowledge management; information governance; corporate policy compliance; team collaboration</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -37323,19 +37415,15 @@
         </is>
       </c>
       <c r="S236" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T236" t="n">
         <v>0.9</v>
       </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+      <c r="U236" t="inlineStr"/>
       <c r="V236" t="inlineStr">
         <is>
-          <t>keep:1, "Knowledge Sharing Protocol Development":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
@@ -37425,7 +37513,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Oral Communication</t>
+          <t>Oral Communication Facilitation</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -37456,7 +37544,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>active listening; questioning techniques; oral communication; presentation skills; feedback collection</t>
+          <t>active listening; questioning techniques; presentation skills; oral communication; facilitation</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -37471,19 +37559,15 @@
         </is>
       </c>
       <c r="S237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T237" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U237" t="inlineStr"/>
       <c r="V237" t="inlineStr">
         <is>
-          <t>keep:1, "Oral Communication":2</t>
+          <t>keep:1, "Oral Communication Presentation":1, "Oral Communication":1</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
@@ -37577,7 +37661,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Problem Solving</t>
+          <t>Virtual Team Problem Solving</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -37608,7 +37692,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>problem solving; remote teamwork; rapid decision‑making; experiential learning; situational awareness</t>
+          <t>virtual collaboration; remote teamwork; problem solving; experiential learning; situational awareness</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -37635,7 +37719,7 @@
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>keep:1, "Problem Solving":2</t>
+          <t>keep:0, "Virtual Team Problem Solving":2, "Virtual Team Problem‑Solving":1</t>
         </is>
       </c>
       <c r="W238" t="inlineStr">
@@ -37659,13 +37743,9 @@
       </c>
       <c r="AB238" t="inlineStr"/>
       <c r="AC238" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>generic FS capability "Problem Solving" is implicit in other skills</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD238" t="inlineStr"/>
       <c r="AE238" t="b">
         <v>0</v>
       </c>
@@ -37734,7 +37814,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Reviews virtual collaboration protocols to support effective team compliance.</t>
+          <t>Reviews virtual collaboration protocols to support teams working collaboratively in virtual environments.</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -37778,12 +37858,12 @@
         <v>0</v>
       </c>
       <c r="T239" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Protocol Compliance Review":1</t>
         </is>
       </c>
       <c r="W239" t="inlineStr">
@@ -37803,9 +37883,13 @@
         <v>0</v>
       </c>
       <c r="AA239" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB239" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>Virtual Collaboration Compliance Monitoring (LLM verified, sim=0.80)</t>
+        </is>
+      </c>
       <c r="AC239" t="b">
         <v>0</v>
       </c>
@@ -37873,12 +37957,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Protocol Improvement Recommendation</t>
+          <t>Protocol Improvement Determination</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Determines improvements to virtual work processes and protocol enhancements for future projects.</t>
+          <t>Determines improvements to future work protocols in virtual environments.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -37904,7 +37988,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>virtual collaboration; workflow optimization; remote work protocols; process improvement; recommendation</t>
+          <t>virtual collaboration; workflow optimization; remote work protocols; process improvement; digital SOP tools</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -37919,15 +38003,19 @@
         </is>
       </c>
       <c r="S240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T240" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U240" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>keep:2, "Protocol Improvement Determination":1</t>
+          <t>keep:0, "Protocol Improvement Determination/Work Protocol Improvement Determination":2, "Protocol Improvement Recommendation":1</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
@@ -37944,7 +38032,7 @@
         </is>
       </c>
       <c r="Z240" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -38017,7 +38105,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Role and Responsibility Definition</t>
+          <t>Team Role Definition</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -38048,7 +38136,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>definition; team communication protocols; role assignment; responsibility matrix; organizational roles</t>
+          <t>RACI matrix; team communication protocols; role assignment; team role definition; organizational roles</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -38063,15 +38151,19 @@
         </is>
       </c>
       <c r="S241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T241" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U241" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Team Role Definition":3</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
@@ -38161,12 +38253,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Teamwork Coordination</t>
+          <t>Group Interaction Coordination</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Collaborates to facilitate group interaction and communication to achieve shared outcomes.</t>
+          <t>Facilitates group interaction to achieve shared outcomes.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -38192,7 +38284,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>collaboration; group dynamics; facilitation; communication; teamwork</t>
+          <t>collaboration; group dynamics; facilitation; communication; interaction</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -38207,15 +38299,19 @@
         </is>
       </c>
       <c r="S242" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T242" t="n">
-        <v>0</v>
-      </c>
-      <c r="U242" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>keep:0, "Collaboration Facilitation":1, "Group Interaction Facilitation":1, "Team Collaboration":1</t>
+          <t>keep:0, "Group Interaction Coordination":3</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
@@ -38305,7 +38401,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Virtual Collaboration Compliance Review</t>
+          <t>Virtual Collaboration Compliance Monitoring</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -38351,19 +38447,15 @@
         </is>
       </c>
       <c r="S243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T243" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U243" t="inlineStr"/>
       <c r="V243" t="inlineStr">
         <is>
-          <t>keep:0, "Virtual Collaboration Compliance Review/Collaboration Compliance Review":2, "Protocol Compliance Review":1</t>
+          <t>keep:2, "Collaboration Protocol Compliance Review":1</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
@@ -38383,13 +38475,9 @@
         <v>0</v>
       </c>
       <c r="AA243" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>Protocol Compliance Review (LLM verified, sim=0.80)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB243" t="inlineStr"/>
       <c r="AC243" t="b">
         <v>0</v>
       </c>
@@ -38462,7 +38550,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Develops collaborative virtual knowledge‑sharing protocols in line with task details and team goals.</t>
+          <t>Develops collaborative virtual knowledge‑sharing protocols based on task details and team goals.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -38488,7 +38576,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>knowledge management; virtual collaboration; protocol design; knowledge sharing; remote teamwork</t>
+          <t>knowledge management; virtual collaboration; protocol design; remote teamwork; knowledge sharing</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -38749,7 +38837,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Data Protection Monitoring</t>
+          <t>Technology Monitoring</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -38780,7 +38868,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>cybersecurity; intrusion detection; incident response; data compliance; data protection</t>
+          <t>cybersecurity; intrusion detection; incident response; SIEM; technology monitoring</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -38795,15 +38883,19 @@
         </is>
       </c>
       <c r="S246" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T246" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U246" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>keep:2, "Data Security Monitoring":1</t>
+          <t>keep:1, "Technology Monitoring":2</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
@@ -38928,7 +39020,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>cryptography; key management; enterprise security; encryption; TLS/SSL</t>
+          <t>encryption; cryptography; key management; enterprise security; TLS/SSL</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -38950,12 +39042,12 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Implementation":3</t>
+          <t>keep:0, "Encryption Implementation":2, "Encryption Deployment":1</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
@@ -39098,12 +39190,12 @@
         <v>0</v>
       </c>
       <c r="T248" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U248" t="inlineStr"/>
       <c r="V248" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Encryption Implementation Strategy Planning":1</t>
         </is>
       </c>
       <c r="W248" t="inlineStr">
@@ -39202,7 +39294,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Determines function and performance of encryption tools in operational settings.</t>
+          <t>Determines function and performance of encryption tools by measuring performance metrics in operational settings.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -39228,7 +39320,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>cryptography; encryption algorithms; performance benchmarking; security analysis; OpenSSL</t>
+          <t>cryptography; encryption algorithms; performance benchmarking; security analysis; encryption technologies</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -39243,15 +39335,19 @@
         </is>
       </c>
       <c r="S249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T249" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U249" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Encryption Technology Performance Assessment/Encryption Performance Assessment":3</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
@@ -39268,7 +39364,7 @@
         </is>
       </c>
       <c r="Z249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -39345,12 +39441,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Encryption Standards Knowledge</t>
+          <t>Encryption Standards Understanding</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Uses AES, DES, and other symmetric algorithms to secure data protection schemes.</t>
+          <t>AES, DES, and other symmetric algorithms for secure data protection schemes.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -39391,15 +39487,19 @@
         </is>
       </c>
       <c r="S250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T250" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U250" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Encryption Standards Understanding":2, "Encryption Standards Review":1</t>
         </is>
       </c>
       <c r="W250" t="inlineStr">
@@ -39493,7 +39593,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Encryption Implementation Evaluation</t>
+          <t>Encryption Technologies Evaluation</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -39524,7 +39624,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>cryptography; encryption standards; key management; encryption technologies; compliance</t>
+          <t>cryptography; encryption standards; key management; security assessment; encryption technologies</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
@@ -39546,12 +39646,12 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Implementation Evaluation":3</t>
+          <t>keep:1, "Encryption Technologies Evaluation/Encryption Implementation Evaluation":2</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
@@ -39954,7 +40054,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Reports encryption analysis and submits notification to affected users and staff of incident impacts.</t>
+          <t>Reports encryption analysis and submits notifications to affected users and staff of incident impacts.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -40007,7 +40107,7 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Analysis Reporting":3</t>
+          <t>keep:0, "Encryption Analysis Reporting/Encryption Technologies Reporting":3</t>
         </is>
       </c>
       <c r="W254" t="inlineStr">
@@ -40158,12 +40258,12 @@
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Plan Creation":2, "Encryption Implementation Planning":1</t>
+          <t>keep:0, "Encryption Plan Creation":3</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
@@ -40261,12 +40361,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Security Requirements Analysis</t>
+          <t>Security Requirements Identification</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Identifies enterprise data security needs in relation to network architecture and organisational requirements.</t>
+          <t>Identifies enterprise data security needs by reviewing network architecture and organisational requirements.</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -40292,7 +40392,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>cybersecurity; risk assessment; network security; data protection; compliance governance</t>
+          <t>cybersecurity; risk assessment; network security; data protection; enterprise data security</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -40307,15 +40407,19 @@
         </is>
       </c>
       <c r="S256" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T256" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U256" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>keep:2, "Security Requirements Identification":1</t>
+          <t>keep:0, "Security Requirements Identification":3</t>
         </is>
       </c>
       <c r="W256" t="inlineStr">
@@ -40332,7 +40436,7 @@
         </is>
       </c>
       <c r="Z256" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -40440,7 +40544,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>communication channels; role‑based messaging; collaboration tools; information flow; mode of communication</t>
+          <t>communication channels; stakeholder management; role‑based messaging; collaboration tools; mode of communication</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
@@ -40458,7 +40562,7 @@
         <v>1</v>
       </c>
       <c r="T257" t="n">
-        <v>0.9</v>
+        <v>0.925</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -40467,7 +40571,7 @@
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>keep:0, "Communication Coordination":2, "Communication Determination":1</t>
+          <t>keep:0, "Communication Coordination/Team Communication Coordination":2, "Communication Determination":1</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
@@ -40566,7 +40670,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Prepares workplace documentation that incorporates an evaluation of technical information using specialised, cohesive language.</t>
+          <t>Creates workplace documents using specialized, cohesive language to present technical data.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -40713,7 +40817,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Connectivity and Security Troubleshooting</t>
+          <t>Security Issue Troubleshooting</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -40744,7 +40848,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>network security; connectivity troubleshooting; security protocols; firewall configuration; debugging</t>
+          <t>network security; incident response; connectivity troubleshooting; security protocols; firewall configuration</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
@@ -40766,12 +40870,12 @@
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>keep:0, "Connectivity and Security Troubleshooting":2, "Network Issue Troubleshooting":1</t>
+          <t>keep:0, "Security Issues Troubleshooting/Security Issue Troubleshooting":3</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
@@ -40788,7 +40892,7 @@
         </is>
       </c>
       <c r="Z259" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -40896,7 +41000,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>encryption technologies; role-based access control; security policy analysis; user responsibility mapping; user impact</t>
+          <t>encryption technologies; role-based access control; security policy analysis; user responsibility mapping; impact analysis</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
@@ -40918,12 +41022,12 @@
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>keep:0, "User Impact Analysis":3</t>
+          <t>keep:0, "User Impact Analysis":2, "User Impact Documentation":1</t>
         </is>
       </c>
       <c r="W260" t="inlineStr">
@@ -41017,12 +41121,12 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Encryption Feedback Response</t>
+          <t>Encryption Feedback Management</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Plans and seeks feedback on encryption plans from required personnel to satisfy organisational needs.</t>
+          <t>Actively solicit and address feedback on encryption plans from relevant personnel to meet organisational requirements.</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -41044,11 +41148,11 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>encryption feedback; plan review; stakeholder input; response handling; proposed encryption plan</t>
+          <t>encryption plan feedback; personnel consultation; response handling; feedback integration; proposed encryption plan</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
@@ -41059,14 +41163,14 @@
       <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr">
         <is>
-          <t>Encryption Feedback Response</t>
+          <t>Encryption Feedback Management</t>
         </is>
       </c>
       <c r="S261" t="b">
         <v>0</v>
       </c>
       <c r="T261" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
@@ -41076,15 +41180,15 @@
       <c r="V261" t="inlineStr"/>
       <c r="W261" t="inlineStr">
         <is>
-          <t>Collects and addresses feedback on encryption plans from required personnel to satisfy organisational needs.</t>
+          <t>Actively solicit and address feedback on encryption plans from relevant personnel to meet organisational requirements.</t>
         </is>
       </c>
       <c r="X261" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>encryption feedback, plan review, stakeholder input, organisational needs, response handling</t>
+          <t>encryption plan feedback, personnel consultation, organisational needs, response handling, feedback integration</t>
         </is>
       </c>
       <c r="Z261" t="b">
@@ -41170,7 +41274,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Documents encryption problems and compromises and submits them to the organisational help desk support.</t>
+          <t>Records encryption issues and compromises and submits the documentation to the organisational help desk support.</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -41196,7 +41300,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>encryption issues; compromise documentation; help desk submission; incident reporting; security logging</t>
+          <t>encryption issues; compromise documentation; help desk submission; incident reporting; reporting</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
@@ -41224,19 +41328,19 @@
       <c r="V262" t="inlineStr"/>
       <c r="W262" t="inlineStr">
         <is>
-          <t>Records encryption problems and compromises and forwards detailed reports to the organisation's help desk support.</t>
+          <t>Records encryption issues and compromises and submits the documentation to the organisational help desk support.</t>
         </is>
       </c>
       <c r="X262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>encryption issues, compromise documentation, help desk submission, incident reporting, security logging</t>
+          <t>encryption issues, compromise documentation, help desk submission, incident reporting, security communication</t>
         </is>
       </c>
       <c r="Z262" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>

--- a/vet_skills_refined.xlsx
+++ b/vet_skills_refined.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>VPN; tunneling protocols; key exchange; ipsec; configuration</t>
+          <t>VPN; ipsec; tunneling protocols; key exchange; configuration</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>standard operating procedures; troubleshooting; problem solving; adaptive response; changing contexts</t>
+          <t>standard operating procedures; troubleshooting; changing contexts; process initiation; problem solving</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>keep:0, "Problem Response Initiation":2, "Standard Procedure Initiation":1</t>
+          <t>keep:0, "Problem Response Initiation/Problem Procedure Initiation":3</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Creates and applies router audit rules, then runs and monitors asset security compliance.</t>
+          <t>Creates and applies router audit rules, then monitors assets for security compliance.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1112,19 +1112,15 @@
         </is>
       </c>
       <c r="S4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0.95</v>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>keep:1, "Network Router Auditing":2</t>
+          <t>keep:2, "Network Router Auditing":1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1144,9 +1140,13 @@
         <v>1</v>
       </c>
       <c r="AA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Security Monitoring Implementation (LLM verified, sim=0.74)</t>
+        </is>
+      </c>
       <c r="AC4" t="b">
         <v>0</v>
       </c>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Security Procedures Planning</t>
+          <t>Work Brief Confirmation</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Confirms work briefs and tasks against organisational security policies.</t>
+          <t>Confirms work briefs and tasks in line with organisational security policies.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>risk assessment; security policy compliance; procedural documentation; procedures; access control planning</t>
+          <t>risk assessment; security policy compliance; procedural documentation; access control planning; work brief</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1271,16 +1271,16 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>MIS re-refinement: Structure Rule 1 — tail 'Procedures' is not an action-as-noun; rewrite to end in an action.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>keep:0, "Security Procedures Planning/Security Procedure Planning":2, "Work Brief Confirmation":1</t>
+          <t>keep:0, "Security Procedures Planning":1, "Work Brief Confirmation":1, "Security Procedure Confirmation":1</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 1.1 Confirm work brief and tasks according to organisational</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Structure Rule 1 — tail 'Procedures' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Industry Regulation Reading</t>
+          <t>Industry Regulations Interpretation</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Collects, interprets and analyses current industry regulations from multiple sources to ensure compliance.</t>
+          <t>Gathers and interprets current industry regulations from multiple sources to ensure compliance.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>reading; regulatory compliance; policy interpretation; industry standards; legal research</t>
+          <t>regulatory compliance; policy interpretation; industry standards; legal research; governance frameworks</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>keep:0, "Industry Regulation Reading":2, "Industry Regulations Analysis":1</t>
+          <t>keep:0, "Industry Regulations Interpretation":2, "Industry Regulations Analysis":1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="Z6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -1587,12 +1587,12 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>keep:2, "Risk Identification Planning":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>VPN; network security; encryption; firewall; configuration</t>
+          <t>VPN; network security; encryption; remote access; configuration</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>System Settings Documentation Development</t>
+          <t>Security Documentation Development</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>system configuration; compliance; policy management; access control; system settings</t>
+          <t>system configuration; compliance; policy management; access control; audit trail</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1892,19 +1892,15 @@
         </is>
       </c>
       <c r="S9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>keep:1, "System Settings Documentation Development/System Documentation Development":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1921,7 +1917,7 @@
         </is>
       </c>
       <c r="Z9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -2007,7 +2003,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Runs and monitors asset security monitoring tools to address threats.</t>
+          <t>Runs asset security monitoring tools to monitor threats.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2051,12 +2047,12 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>keep:0, "Asset Security Monitoring Execution":1, "Asset Security Monitoring":1, "Asset Security Monitoring Implementation":1</t>
+          <t>keep:1, "Asset Security Monitoring":1, "Asset Security Monitoring Implementation":1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -2076,13 +2072,9 @@
         <v>0</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Network Router Auditing (LLM verified, sim=0.74)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="b">
         <v>0</v>
       </c>
@@ -2163,7 +2155,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Identifies and manages work‑related risks independently.</t>
+          <t>Identifies and manages work‑related risks independently while following personal security procedures.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2189,7 +2181,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>risk assessment; security procedures; personal accountability; risk mitigation; self‑management</t>
+          <t>risk assessment; information security; security procedures; personal accountability; self-management</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2211,12 +2203,12 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>keep:0, "Security Task Self‑Management":2, "Security Task Management":1</t>
+          <t>keep:0, "Security Tasks Self‑Management/Security Task Self‑Management":3</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2345,7 +2337,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>system analysis; functional specification; feature identification; specialist systems; function identification</t>
+          <t>system analysis; functional specification; function; feature identification; specialist systems</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2372,7 +2364,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>keep:0, "Specialist System Function Identification":2, "Technology Feature Identification":1</t>
+          <t>keep:1, "Specialist System Function Identification/Specialist System Identification":2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2470,12 +2462,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Network Fault Rectification</t>
+          <t>Network Fault Troubleshooting</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tests remote access server to rectify any faults.</t>
+          <t>Tests remote access server and rectifies faults.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2501,7 +2493,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>network diagnostics; remote server access; fault isolation; TCP/IP troubleshooting; rectification</t>
+          <t>network diagnostics; fault isolation; TCP/IP troubleshooting; remote access server; network monitoring tools</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2523,12 +2515,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>keep:0, "Network Fault Rectification":2, "Network Fault Troubleshooting":1</t>
+          <t>keep:0, "Network Fault Troubleshooting":3</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2626,7 +2618,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Site-to-site VPN User Authentication</t>
+          <t>VPN User Authentication</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2657,7 +2649,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>SSL/TLS; RADIUS; MFA; site-to-site; user authentication</t>
+          <t>IPsec; SSL/TLS; RADIUS; MFA; user authentication</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2672,19 +2664,15 @@
         </is>
       </c>
       <c r="S14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>keep:1, "Site-to-Site VPN User Authentication":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2813,7 +2801,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>penetration testing; network security assessment; vulnerability scanning; risk assessment; network router testing</t>
+          <t>penetration testing; network security assessment; vulnerability scanning; network router testing; security policies</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2938,12 +2926,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Technical Report Writing</t>
+          <t>Technical Documentation Preparation</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Prepares technical reports using prescribed templates to meet organisational documentation standards.</t>
+          <t>Prepares technical documentation using prescribed templates to meet organisational documentation standards.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2969,7 +2957,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>technical documentation; report formatting; organizational standards; template compliance; writing</t>
+          <t>technical documentation; report formatting; organizational standards; word processing tools; template compliance</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2996,7 +2984,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>keep:0, "Technical Report Writing":3</t>
+          <t>keep:0, "Technical Documentation Preparation":3</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -3013,7 +3001,7 @@
         </is>
       </c>
       <c r="Z16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -3098,12 +3086,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Network Component Sourcing</t>
+          <t>Network Component Procurement</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sources appropriate network hardware, software and tools, then confirms each component is serviceable before deployment.</t>
+          <t>Sources required network configuration hardware, software and tools and confirms each component is serviceable before deployment.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3125,11 +3113,11 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>network hardware selection; software tool acquisition; component serviceability verification; network component sourcing; equipment readiness assessment</t>
+          <t>network hardware sourcing; software acquisition; tool procurement; component serviceability verification; network configuration hardware</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3141,14 +3129,14 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Network Component Sourcing</t>
+          <t>Network Component Procurement</t>
         </is>
       </c>
       <c r="S17" t="b">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3158,7 +3146,7 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Selects appropriate network hardware, software and tools, then verifies each component is serviceable before deployment.</t>
+          <t>Sources required network configuration hardware, software and tools and verifies each component is serviceable before deployment.</t>
         </is>
       </c>
       <c r="X17" t="b">
@@ -3166,7 +3154,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>network hardware selection, software tool acquisition, component serviceability verification, VPN configuration resources, equipment readiness assessment</t>
+          <t>network hardware sourcing, software acquisition, tool procurement, component serviceability verification, configuration resources</t>
         </is>
       </c>
       <c r="Z17" t="b">
@@ -3278,7 +3266,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3300,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3434,7 +3422,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>router console installation; management console access; router management console; network device configuration; console authentication</t>
+          <t>router console installation; management interface; access credentials; configuration tool; router management console</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3462,7 +3450,7 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Installs the router management console and accesses it to configure and monitor network settings.</t>
+          <t>Installs the router management console and accesses it using appropriate credentials to configure the device.</t>
         </is>
       </c>
       <c r="X19" t="b">
@@ -3470,7 +3458,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>router console installation, management console access, network device configuration, router interface setup, console authentication</t>
+          <t>router console installation, management interface, access credentials, configuration tool, network device</t>
         </is>
       </c>
       <c r="Z19" t="b">
@@ -3586,7 +3574,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>access control; identity and access management; security policy design; risk assessment; authentication</t>
+          <t>authentication; access control; identity and access management; security policy design; risk assessment</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3604,12 +3592,12 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Authentication Controls Planning":1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3707,12 +3695,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Authentication System Development</t>
+          <t>Authentication Documentation Development</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Develops and documents authentication system designs and protocols to meet specified requirements.</t>
+          <t>Creates and records authentication system designs and protocols to meet specified requirements.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3738,7 +3726,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>identity management; security protocols; access control; IAM; authentication system</t>
+          <t>authentication; identity management; security protocols; access control; IAM</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3765,7 +3753,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>keep:0, "Authentication System Development/Authentication System Documentation Development":2, "Authentication Documentation":1</t>
+          <t>keep:1, "Authentication Documentation Development":2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3774,7 +3762,7 @@
         </is>
       </c>
       <c r="X21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -3863,12 +3851,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Authentication Failure Identification</t>
+          <t>Authentication Failure Problem Solving</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Demonstrates intuitive analysis to identify authentication failures, generate solutions for security incidents, and define problem scope.</t>
+          <t>Demonstrates intuitive analysis to identify authentication failures, identify security incidents, and generate problem scope.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3894,7 +3882,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>security incidents; access control; incident response; identity management; authentication failure</t>
+          <t>security incidents; access control; identity management; authentication; failure</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3909,19 +3897,15 @@
         </is>
       </c>
       <c r="S22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>keep:0, "Authentication Failure Identification":2, "Authentication Failure Analysis":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -4019,12 +4003,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Authentication Requirements Analysis</t>
+          <t>Authentication Requirements Determination</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Plans and determines user and organizational authentication requirements per security plan.</t>
+          <t>Determines user and organisational authentication requirements according to the security plan.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4050,7 +4034,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>access control; identity and access management; authentication protocols; security policy; risk assessment</t>
+          <t>access control; identity and access management; authentication protocols; security policy; authentication requirements</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -4065,15 +4049,19 @@
         </is>
       </c>
       <c r="S23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U23" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Authentication Requirements Determination":2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -4090,7 +4078,7 @@
         </is>
       </c>
       <c r="Z23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -4180,7 +4168,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Creates required authentication realm and reuses it per system and organisational policies.</t>
+          <t>Creates authentication realms and reuses them per system and organisational policies.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4224,12 +4212,12 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>keep:2, "Authentication System Configuration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -4332,7 +4320,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Submits required documentation and responds promptly to feedback from personnel.</t>
+          <t>Submits required documents in response to feedback from required personnel.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4381,7 +4369,7 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>keep:2, "Feedback Response Management":1</t>
+          <t>keep:2, "Feedback Coordination":1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -4484,7 +4472,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Determines, documents, monitors and reports security monitoring and incident response procedures in line with the organization’s security plan.</t>
+          <t>Determines, documents and monitors security monitoring and incident response procedures in accordance with the organization’s security plan.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4636,7 +4624,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Reviews authentication systems against user security and quality of service requirements.</t>
+          <t>Reviews authentication systems to ensure security controls meet user requirements and service quality standards.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4685,7 +4673,7 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>keep:1, "Security Monitoring Determination":1, "Authentication System Monitoring Implementation":1</t>
+          <t>keep:1, "Authentication System Review":1, "Authentication Monitoring Implementation":1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4783,12 +4771,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Authentication Process Determination</t>
+          <t>Authentication Process Alignment</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Determines authentication and authorisation steps in accordance with organisational security policies.</t>
+          <t>Determines authentication and authorisation steps according to organisational security policies.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4836,12 +4824,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>keep:0, "Authentication Authorisation Determination/Authentication Process Determination":3</t>
+          <t>keep:0, "Authentication Process Alignment":2, "Authentication Process Determination":1</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4970,7 +4958,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>protocol compliance; information security; policy adherence; access control; self-management</t>
+          <t>self-management; protocol compliance; information security; policy adherence; access control</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4988,12 +4976,12 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.9166666666666666</v>
+        <v>0</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Role Self‑Management":1, "Security Protocol Following":1, "Protocol Self‑Management":1</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -5091,7 +5079,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Technical Data Analysis</t>
+          <t>Technical Data Interpretation</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -5122,7 +5110,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>technical data; data analysis; requirements engineering; technical specifications; engineering standards</t>
+          <t>data interpretation; data analysis; requirements engineering; technical specifications; engineering standards</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -5137,19 +5125,15 @@
         </is>
       </c>
       <c r="S30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>keep:1, "Technical Data Analysis":2</t>
+          <t>keep:2, "Technical Data Analysis":1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -5305,7 +5289,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>keep:0, "User Attribute Determination":2, "User Attribute Configuration":1</t>
+          <t>keep:0, "User Attribute Determination/User Attributes Determination":2, "User Attribute Configuration":1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -5403,12 +5387,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Permission Data Management</t>
+          <t>Permission Recordkeeping</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Records and securely stores permission and configuration information in line with authentication system requirements.</t>
+          <t>Records and securely stores permission and configuration information in accordance with authentication system requirements.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5434,7 +5418,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>permission records; configuration information; secure storage; authentication system; data management</t>
+          <t>permission records; configuration data; secure storage; authentication system; recordkeeping</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -5445,7 +5429,7 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Permission Data Management</t>
+          <t>Permission Recordkeeping</t>
         </is>
       </c>
       <c r="S32" t="b">
@@ -5462,7 +5446,7 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Records and securely stores permission and configuration information in line with authentication system requirements.</t>
+          <t>Records and securely stores permission and configuration information in accordance with authentication system requirements.</t>
         </is>
       </c>
       <c r="X32" t="b">
@@ -5470,7 +5454,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>permission records, configuration information, secure storage, authentication system, data management</t>
+          <t>permission records, configuration data, secure storage, authentication system, recordkeeping</t>
         </is>
       </c>
       <c r="Z32" t="b">
@@ -5552,12 +5536,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Item Manipulation Incorporation</t>
+          <t>Item Manipulation Scripting</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Incorporates scripts to manipulate data items, automating transformations within chosen language.</t>
+          <t>Incorporates scripts to manipulate data items, automating transformations within the chosen language.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5583,7 +5567,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>data transformation; automation; Python; PowerShell; item manipulation</t>
+          <t>data transformation; Python; PowerShell; item manipulation; scripting language</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5605,12 +5589,12 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>keep:0, "Item Manipulation Incorporation":2, "Item Manipulation Scripting":1</t>
+          <t>keep:0, "Item Manipulation Scripting":3</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -5705,7 +5689,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>IDE Identification</t>
+          <t>IDE Selection</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5736,7 +5720,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>development environment; code editor; language support; software development tools; IDE</t>
+          <t>development environment; toolchain evaluation; language support; software development tools; IDE selection</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5758,12 +5742,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>keep:0, "IDE Identification":2, "IDE Selection":1</t>
+          <t>keep:0, "IDE Selection":3</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5889,7 +5873,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>code comments; technical documentation; script standards; internal documentation; software development procedures</t>
+          <t>code comments; technical documentation; script standards; internal documentation; version control</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5912,7 +5896,7 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>keep:1, "Script Documentation":1, "Internal Documentation Creation":1</t>
+          <t>keep:1, "Script Documentation":1, "Script Documentation Creation":1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -6007,7 +5991,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pseudo Code Review</t>
+          <t>Pseudo Code Logic Correction</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -6065,7 +6049,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>keep:0, "Pseudo Code Review":2, "Logic Correction":1</t>
+          <t>keep:0, "Pseudo Code Logic Correction":2, "Pseudo Code Logic Review":1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -6169,7 +6153,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Identifies communication protocols and underlying object model in the chosen scripting language.</t>
+          <t>Identifies communication protocols and underlying object model of the chosen scripting language.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -6213,16 +6197,16 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>keep:0, "Protocol Model Identification/Protocol Object Model Identification":3</t>
+          <t>keep:1, "Protocol Object Model Identification":2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -6322,7 +6306,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Creates pseudocode and describes script logic to support development and debugging.</t>
+          <t>Creates detailed pseudocode and describes script logic to support development and debugging.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -6366,12 +6350,12 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>keep:2, "Pseudocode Development":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -6497,7 +6481,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>code review; troubleshooting; script documentation; debugging; version control</t>
+          <t>debugging; code review; troubleshooting; script documentation; version control</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -6803,7 +6787,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>pseudo-code; scripting languages; code conversion; basic syntax; script translation</t>
+          <t>pseudo-code; scripting languages; code conversion; basic syntax; translation</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -6830,7 +6814,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>keep:0, "Script Translation":2, "Pseudo Code Translation":1</t>
+          <t>keep:0, "Script Translation":2, "Pseudo Code Translation Implementation":1</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6934,7 +6918,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Identifies main characteristics of scripting languages for appropriate selection.</t>
+          <t>Identifies key characteristics of scripting languages for appropriate selection.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -7087,7 +7071,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Identifies required software outcomes in line with user needs and functional specifications.</t>
+          <t>Identifies required software outcomes.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -7136,7 +7120,7 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>keep:2, "Software Application Requirements Analysis":1</t>
+          <t>keep:2, "Software Application Outcomes Identification":1</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -7438,7 +7422,7 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>keep:1, "Stakeholder Expectation Discussion":1, "Stakeholder Expectation Review":1</t>
+          <t>keep:1, "Software Application Expectation Discussion":1, "Stakeholder Expectations Discussion":1</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -7538,7 +7522,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Systematic analysis to identify and evaluate scripting language texts and pseudo‑code in hybrid environments.</t>
+          <t>Identifies and evaluates scripting language texts and pseudo‑code in hybrid environments.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -7564,7 +7548,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>algorithmic analysis; scripting languages; pseudo‑code evaluation; logical reasoning; systematic problem solving</t>
+          <t>systematic; scripting languages; pseudo‑code evaluation; logical reasoning; problem solving</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -7582,12 +7566,12 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Scripting Problem Solving":1</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -7682,7 +7666,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Technical Documentation Interpretation</t>
+          <t>Technical Reading Comprehension</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7713,7 +7697,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>technical documentation; requirements analysis; information extraction; interpretation; comprehension strategies</t>
+          <t>technical documentation; requirements analysis; information extraction; comprehension strategies; reading</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -7728,19 +7712,15 @@
         </is>
       </c>
       <c r="S47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>keep:0, "Technical Documentation Interpretation":2, "Technical Documentation Comprehension":1</t>
+          <t>keep:1, "Technical Documentation Interpretation":1, "Technical Documentation Reading":1</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -7890,7 +7870,7 @@
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>keep:2, "Benefits Identification":1</t>
+          <t>keep:2, "Benefits Documentation":1</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -7910,13 +7890,9 @@
         <v>1</v>
       </c>
       <c r="AA48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>Challenges Documentation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="b">
         <v>0</v>
       </c>
@@ -8021,7 +7997,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>cloud adoption; business requirements; cloud governance; migration challenges; challenges of adopting</t>
+          <t>cloud adoption; business requirements; cloud governance; migration challenges; document challenges</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -8039,7 +8015,7 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0.95</v>
+        <v>0.925</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -8068,9 +8044,13 @@
         <v>1</v>
       </c>
       <c r="AA49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Benefits Documentation</t>
+        </is>
+      </c>
       <c r="AC49" t="b">
         <v>0</v>
       </c>
@@ -8144,7 +8124,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Cloud Service Platform Selection</t>
+          <t>Cloud Service Selection</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -8175,7 +8155,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>cloud vendor evaluation; service model comparison; cost‑benefit analysis; scalability and compliance; cloud platform selection</t>
+          <t>cloud vendor evaluation; service model comparison; cost‑benefit analysis; scalability and compliance; cloud service selection</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -8190,19 +8170,15 @@
         </is>
       </c>
       <c r="S50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>keep:0, "Cloud Service Platform Selection":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -8298,12 +8274,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Cloud Solutions Evaluation</t>
+          <t>Cloud Solution Evaluation</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Finalises cloud solution assessments, seeks stakeholder feedback, and responds to improvements accordingly.</t>
+          <t>Finalises cloud solution assessments, seeks evaluation feedback, and responds accordingly.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -8329,7 +8305,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>cloud computing; solution assessment; cloud solutions; cost analysis; service level agreement</t>
+          <t>cloud computing; solution assessment; vendor comparison; cost analysis; service level agreement</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -8344,19 +8320,15 @@
         </is>
       </c>
       <c r="S51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>keep:0, "cloud solutions evaluation/Cloud Solutions Services Evaluation/Cloud Solutions Evaluation":3</t>
+          <t>keep:2, "Cloud Solutions Evaluation":1</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -8373,7 +8345,7 @@
         </is>
       </c>
       <c r="Z51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -8457,7 +8429,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Discusses cloud and hybrid cost models, articulating pros and cons to inform deployment decisions.</t>
+          <t>Discusses cloud and hybrid cost models, articulating pros/cons to inform deployment decisions.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -8483,7 +8455,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>cloud computing; total cost of ownership; hybrid cloud; cost‑benefit analysis; cost model</t>
+          <t>cloud computing; total cost of ownership; hybrid cloud; cost‑benefit analysis; cost model comparison</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -8501,12 +8473,12 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Cost Model Comparison":1</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -8602,7 +8574,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Evaluation Document Management</t>
+          <t>Evaluation Document Lodging</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -8633,7 +8605,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>evaluation document; document control; records management; versioning; compliance filing</t>
+          <t>document control; records management; versioning; lodging; compliance filing</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -8660,7 +8632,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>keep:0, "Evaluation Document Management":3</t>
+          <t>keep:0, "Evaluation Document Lodging":3</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -8756,12 +8728,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Cloud Deployment Model Research</t>
+          <t>Cloud Deployment Model Researching</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Researches and identifies emerging cloud deployment models to inform technology strategy.</t>
+          <t>Researches and identifies new cloud deployment models to inform technology strategy.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -8787,7 +8759,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>cloud computing; deployment models; multi‑cloud architecture; edge computing; research</t>
+          <t>cloud deployment models; cloud computing; deployment models; multi‑cloud architecture; edge computing</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -8809,12 +8781,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>keep:0, "Cloud Deployment Model Research/Emerging Cloud Model Research/Emerging Deployment Model Research":3</t>
+          <t>keep:0, "Cloud Deployment Model Researching":2, "Emerging Cloud Model Identification":1</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -8915,7 +8887,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Communicates evaluation results to designated staff through concise briefings.</t>
+          <t>Communicates evaluation results to designated staff through concise reports or briefings.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -9249,7 +9221,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>verbal communication; active listening; concise feedback; interpersonal communication; feedback handling</t>
+          <t>verbal communication; active listening; concise feedback; interpersonal communication; oral feedback handling</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -9267,12 +9239,12 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Oral Feedback Handling":1</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -9372,7 +9344,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Organisational Policy Identification</t>
+          <t>Policy Identification</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -9430,7 +9402,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>keep:0, "Organisational Policy Identification":3</t>
+          <t>keep:0, "Policy Identification/Organisational Policy Identification":3</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -9526,7 +9498,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Report Writing</t>
+          <t>Documentation Writing</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -9572,15 +9544,19 @@
         </is>
       </c>
       <c r="S59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U59" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>keep:2, "Documentation Writing":1</t>
+          <t>keep:1, "Documentation Writing":2</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -9876,19 +9852,15 @@
         </is>
       </c>
       <c r="S61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>keep:1, "Self‑Management Decision‑Making":2</t>
+          <t>keep:2, "Decision Making":1</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -9989,7 +9961,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Applies cloud solution total cost of ownership to business requirements.</t>
+          <t>Applies total cost of ownership for cloud solution to business requirements.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -10042,7 +10014,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>keep:0, "Total Cost Ownership Analysis/Ownership Cost Analysis":3</t>
+          <t>keep:0, "Ownership Cost Analysis/Total Ownership Cost Analysis":3</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -10143,7 +10115,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Identifies and confirms business and industry technology terminology, characteristics and concepts for cloud solutions evaluation.</t>
+          <t>Identifies business and industry technology terminology, characteristics and concepts for cloud solution reviews.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -10169,7 +10141,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>business terminology; industry terminology; technology concepts; technology terminology; terminology verification</t>
+          <t>technology terminology; industry concepts; business characteristics; industry technology terminology; terminology validation</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -10197,15 +10169,15 @@
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Identifies and confirms business and industry technology terminology, characteristics and concepts for cloud solutions evaluation.</t>
+          <t>Identifies and validates business and industry technology terminology, characteristics and concepts for cloud solution reviews.</t>
         </is>
       </c>
       <c r="X63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>business terminology, industry terminology, technology concepts, cloud computing terms, terminology verification</t>
+          <t>technology terminology, industry concepts, business characteristics, cloud computing, terminology validation</t>
         </is>
       </c>
       <c r="Z63" t="b">
@@ -10288,17 +10260,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Cloud Service Assessment</t>
+          <t>Cloud Platform Assessment</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Identifies cloud service platforms and delivery models, reviewing their capabilities against specific business requirements.</t>
+          <t>Identifies and reviews capabilities and characteristics of cloud service platforms and delivery models against business requirements.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>technical</t>
+          <t>cognitive</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -10319,7 +10291,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>cloud platforms; delivery models; business requirements; service characteristics; cloud deployment models</t>
+          <t>cloud platforms; service capabilities; delivery models; business requirements; capability assessment</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -10330,7 +10302,7 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Cloud Service Assessment</t>
+          <t>Cloud Platform Assessment</t>
         </is>
       </c>
       <c r="S64" t="b">
@@ -10347,19 +10319,19 @@
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Analyzes cloud service platforms and delivery models, matching their capabilities to specific business requirements.</t>
+          <t>Identifies and reviews capabilities and characteristics of cloud service platforms and delivery models against business requirements.</t>
         </is>
       </c>
       <c r="X64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>cloud platforms, delivery models, business requirements, capability review, service characteristics</t>
+          <t>cloud platforms, service capabilities, delivery models, business requirements, capability assessment</t>
         </is>
       </c>
       <c r="Z64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -10474,7 +10446,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>business continuity; risk assessment; critical function identification; impact analysis; business resilience</t>
+          <t>risk assessment; critical function identification; impact analysis; business resilience; business continuity</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -10492,12 +10464,12 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>keep:2, "Business Continuity Impact Assessment":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -10607,7 +10579,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Prepares comprehensive contingency documentation detailing evaluations and strategies in prescribed language and formats.</t>
+          <t>Prepares comprehensive contingency plans in prescribed language and formats.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -10680,9 +10652,13 @@
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 2.2 Evaluate and document risk minimisation alternatives aga</t>
+        </is>
+      </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
@@ -10757,7 +10733,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Critical Data Software Identification</t>
+          <t>Critical Data Identification</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -10806,16 +10782,16 @@
         <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0.9</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>keep:1, "Critical Data Software Identification/Critical Data Identification":2</t>
+          <t>keep:0, "Critical Data Identification/Critical Data Software Identification/Critical Data/Software Identification":3</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -10921,7 +10897,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Develops comprehensive disaster recovery plans, documents them, and submits them to designated stakeholders.</t>
+          <t>Develops comprehensive disaster recovery plans, documents them, and submits them to designated personnel.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -11230,7 +11206,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>System Data Interpretation</t>
+          <t>System Data Analysis</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -11261,7 +11237,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>quantitative analysis; financial data reporting; technical system metrics; data visualization; data interpretation</t>
+          <t>quantitative analysis; financial data reporting; technical system metrics; data visualization; numerical data</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -11283,12 +11259,12 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>keep:0, "System Data Interpretation":3</t>
+          <t>keep:0, "System Data Analysis":2, "System Data Interpretation":1</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -11394,7 +11370,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Gathers and analyses data, seeks feedback, and plans improvements to plans and processes in hybrid settings.</t>
+          <t>Gathers and analyses data, seeks feedback, and plans improvements to processes in hybrid settings.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -11420,7 +11396,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>data analysis; feedback loops; continuous improvement; process optimization; problem solving</t>
+          <t>data analysis; continuous improvement; process optimization; problem solving; feedback loops</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -11602,7 +11578,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>keep:0, "Regulatory Requirements Identification/Regulatory Requirement Identification":3</t>
+          <t>keep:0, "Regulatory Requirements Identification/Regulatory Compliance Identification":3</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -11708,7 +11684,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Evaluates risk‑minimisation options against organisational cost limits and documents findings in hybrid projects.</t>
+          <t>Evaluates risk‑minimisation options, documents findings, and ensures choices meet organisational cost limits in hybrid projects.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -11734,7 +11710,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>risk assessment; cost‑benefit analysis; mitigation strategies; alternatives; minimisation</t>
+          <t>risk assessment; cost‑benefit analysis; mitigation strategies; risk register; risk minimisation alternatives</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -11862,12 +11838,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>System Threat Analysis</t>
+          <t>System Threat Identification</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Identifies and documents internal and external system threats through hybrid risk threat analysis.</t>
+          <t>Identifies and documents internal and external system threats.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -11915,12 +11891,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>keep:0, "System Threat Analysis/Threat Analysis":2, "Threat Identification":1</t>
+          <t>keep:0, "System Threat Identification":3</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -12026,7 +12002,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Documents feedback from relevant parties, seeks their input, and submits responses in hybrid settings.</t>
+          <t>Documents feedback, seeks input from relevant parties, and submits responses in hybrid settings.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -12070,12 +12046,12 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Feedback Management":1</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -12181,7 +12157,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Demonstrates priorities across flexible hybrid teams to achieve efficient outcomes.</t>
+          <t>Demonstrates strategic planning of priorities across flexible hybrid teams to achieve efficient outcomes.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -12207,7 +12183,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>roadmap development; priority alignment; outcome measurement; performance governance; strategic planning</t>
+          <t>strategic planning; roadmap development; priority alignment; outcome measurement; performance governance</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -12331,12 +12307,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Collaboration Facilitation</t>
+          <t>Working Relationships Facilitation</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Maintains team collaboration by employing communication tools and strategies.</t>
+          <t>Uses communication tools and strategies to maintain working relationships.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -12362,7 +12338,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>communication tools; relationship building; collaboration platforms; interpersonal dynamics; effective working relationships</t>
+          <t>communication tools; relationship building; facilitation techniques; interpersonal dynamics; working relationships</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -12389,7 +12365,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>keep:1, "Collaboration Facilitation":2</t>
+          <t>keep:0, "Working Relationships Facilitation":2, "Collaboration Facilitation":1</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -12521,7 +12497,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>oral communication; active listening; questioning techniques; industry terminology; audience analysis</t>
+          <t>active listening; questioning techniques; industry terminology; audience analysis; oral communication</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -12548,7 +12524,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>keep:0, "Audience Oral Communication/Oral Communication":3</t>
+          <t>keep:0, "Oral Communication":3</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -12649,7 +12625,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Technical Specification Analysis</t>
+          <t>Technical Specification Research</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -12680,7 +12656,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>technical documentation; specification analysis; information retrieval; engineering standards; data extraction</t>
+          <t>technical documentation; specification analysis; information retrieval; data extraction; research</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -12695,19 +12671,15 @@
         </is>
       </c>
       <c r="S79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr">
         <is>
-          <t>keep:0, "Technical Specification Analysis":3</t>
+          <t>keep:0, "Technical Specification Analysis":1, "Technical Specification Researching":1, "Technical Specification Review":1</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -12724,7 +12696,7 @@
         </is>
       </c>
       <c r="Z79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12813,7 +12785,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Assesses the potential impact of business risks and threats on ICT systems to inform mitigation planning.</t>
+          <t>Independently evaluates how business risks and threats could affect ICT systems to inform mitigation planning.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -12831,7 +12803,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>practical</t>
+          <t>theoretical</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12839,7 +12811,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>risk impact assessment; business risk; ICT systems; threat evaluation; mitigation planning</t>
+          <t>ICT risk assessment; business risk impact; threat analysis; impact assessment; impact modelling</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -12867,7 +12839,7 @@
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
         <is>
-          <t>Assesses the potential impact of business risks and threats on ICT systems to inform mitigation planning.</t>
+          <t>Independently evaluates how business risks and threats could affect ICT systems to inform mitigation planning.</t>
         </is>
       </c>
       <c r="X80" t="b">
@@ -12875,11 +12847,11 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>risk impact assessment, business risk, ICT systems, threat evaluation, mitigation planning</t>
+          <t>ICT risk assessment, business risk impact, threat analysis, system vulnerability evaluation, impact modelling</t>
         </is>
       </c>
       <c r="Z80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12963,12 +12935,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Procedure Compliance Review</t>
+          <t>Operational Procedure Review</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Independently reviews industry standard procedures and checks that required risk safeguards and contingency plans are in place.</t>
+          <t>Independently reviews industry‑standard operational procedures and checks that required risk safeguards and contingency plans are in place.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -12994,7 +12966,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>industry standards; operational procedures; risk safeguards; contingency plans; compliance verification</t>
+          <t>industry standard procedures; risk safeguards; contingency plans; compliance verification; operational review</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -13005,7 +12977,7 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Procedure Compliance Review</t>
+          <t>Operational Procedure Review</t>
         </is>
       </c>
       <c r="S81" t="b">
@@ -13022,7 +12994,7 @@
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr">
         <is>
-          <t>Independently reviews industry standard procedures and verifies that required risk safeguards and contingency plans are implemented.</t>
+          <t>Independently reviews industry‑standard operational procedures and verifies that required risk safeguards and contingency plans are implemented.</t>
         </is>
       </c>
       <c r="X81" t="b">
@@ -13030,7 +13002,7 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>industry standards, operational procedures, risk safeguards, contingency plans, compliance verification</t>
+          <t>industry standard procedures, risk safeguards, contingency plans, compliance verification, operational review</t>
         </is>
       </c>
       <c r="Z81" t="b">
@@ -13123,7 +13095,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Identifies required cut‑over criteria and secures final sign‑off from stakeholders for task completion.</t>
+          <t>Independently defines cut‑over criteria and secures final sign‑off for the disaster recovery task.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -13149,7 +13121,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>cut‑over criteria plan; cut‑over criteria; sign‑off process; task completion; stakeholder approval</t>
+          <t>cut‑over criteria; sign‑off process; task approval; recovery planning; final task sign off</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -13178,7 +13150,7 @@
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr">
         <is>
-          <t>Identifies required cut‑over criteria and secures final sign‑off from stakeholders for task completion.</t>
+          <t>Independently defines cut‑over criteria and secures final sign‑off for the disaster recovery task.</t>
         </is>
       </c>
       <c r="X82" t="b">
@@ -13186,7 +13158,7 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>cut‑over criteria, sign‑off process, task completion, stakeholder approval, documentation requirements</t>
+          <t>cut‑over criteria, sign‑off process, task approval, stakeholder validation, recovery planning</t>
         </is>
       </c>
       <c r="Z82" t="b">
@@ -13288,7 +13260,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Prepares and reports comprehensive audit findings and presents recommendations to stakeholders through formal presentations.</t>
+          <t>Prepares comprehensive audit reports and presents recommendations to stakeholders through formal presentations.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -13452,7 +13424,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Recommends changes to decision‑makers for approval.</t>
+          <t>Recommends changes and obtains approval.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -13478,7 +13450,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>stakeholder management; approval workflow; change management process; recommended changes approval; communication coordination</t>
+          <t>stakeholder management; approval workflow; change management process; governance compliance; change approval</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -13500,12 +13472,12 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>keep:1, "Change Approval Obtaining":2</t>
+          <t>keep:0, "Change Approval Obtaining":3</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -13615,12 +13587,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Encryption Facility Implementation</t>
+          <t>Encryption Facility Deployment</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Investigates built‑in and third‑party encryption tools, then implements them to secure data systems.</t>
+          <t>Investigates built‑in and third‑party encryption tools and implements them to secure data systems.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -13646,7 +13618,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>cryptography; AES; PKI; data protection; encryption facility</t>
+          <t>cryptography; key management; AES; PKI; encryption facility</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -13661,19 +13633,15 @@
         </is>
       </c>
       <c r="S85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Facility Implementation/Encryption Facilities Implementation":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -13814,7 +13782,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>information security; data classification; access control; confidentiality policy; file categorisation</t>
+          <t>information security; data classification; access control; security labeling; file security categorisation</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -13841,7 +13809,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>keep:0, "File Security Categorisation Development":2, "File Security Categorisation":1</t>
+          <t>keep:1, "File Security Categorisation Development":2</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
@@ -13956,7 +13924,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Checks password strength with utilities, reviews organisational guidelines for password complexity, and tightens complexity requirements as required.</t>
+          <t>Checks password strength with required utilities and reviews organisational guidelines for password complexity, tightening requirements as needed, also reviews password guidelines within other internal departments.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -13982,7 +13950,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>password complexity; authentication security; IT policy compliance; password strength utilities; password enforcement</t>
+          <t>password complexity; authentication security; IT policy compliance; password strength utilities; enforcement</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -14168,12 +14136,12 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>keep:0, "Problem Solving":2, "Problem Solving Analysis":1</t>
+          <t>keep:0, "Problem Solving":3</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -14292,7 +14260,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Reviews system logs and audit reports across hybrid environments to identify security threats.</t>
+          <t>Reviews system logs and audit reports across hybrid environments to identify and report security threats.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -14336,12 +14304,12 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr">
         <is>
-          <t>keep:2, "Log Threat Identification":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -14451,12 +14419,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>System Security Procedure Evaluation</t>
+          <t>Security Procedure Evaluation</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Evaluates system security procedures across on‑site and remote environments and reports findings in formal reports.</t>
+          <t>Evaluates system security procedures across on‑site and remote environments, reporting findings in formal reports.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -14497,19 +14465,15 @@
         </is>
       </c>
       <c r="S90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr">
         <is>
-          <t>keep:0, "System Security Procedure Evaluation":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -14624,7 +14588,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Creates actionable security adherence recommendations.</t>
+          <t>Creates actionable security adherence recommendations in line with policies.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -14650,7 +14614,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>compliance; risk assessment; security policy; governance; recommendation</t>
+          <t>compliance; risk assessment; security policy; governance; security recommendation</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -14668,12 +14632,12 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
-          <t>keep:2, "Security Adherence Recommendation Development":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -14951,7 +14915,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Task Prioritisation</t>
+          <t>Self‑task Prioritisation</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -14982,7 +14946,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>time management; task sequencing; workload planning; prioritisation techniques; self-management</t>
+          <t>time management; task sequencing; workload planning; prioritisation techniques; self‑management</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -14997,19 +14961,15 @@
         </is>
       </c>
       <c r="S93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>keep:0, "Task Prioritisation":2, "Workload Prioritisation":1</t>
+          <t>keep:0, "Task Prioritisation":1, "Workload Prioritisation":1, "Workload Management":1</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -15124,7 +15084,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Creates detailed technical documents outlining information, requirements, and recommendations for workplace projects.</t>
+          <t>Prepares detailed technical documents outlining information, requirements, and recommendations for workplace projects.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -15168,12 +15128,12 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>keep:1, "Complex Documentation Writing":1, "Security Documentation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
@@ -15182,7 +15142,7 @@
         </is>
       </c>
       <c r="X94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
@@ -15292,7 +15252,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Continuously monitors ICT systems, records identified security threats, for response planning.</t>
+          <t>Continuously monitors ICT systems, records identified security threats in threat registers for response planning.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -15345,7 +15305,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>keep:0, "Threat Monitoring":3</t>
+          <t>keep:0, "Security Threat Monitoring/Threat Monitoring":3</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -15460,7 +15420,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Creates user accounts by accessing ICT systems in accordance with organisational procedures and settings according to security policies.</t>
+          <t>Creates accounts by accessing ICT systems following procedures and creating settings to meet security policies.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -15619,7 +15579,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Virus Checking Implementation</t>
+          <t>Virus Scanning Implementation</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -15650,7 +15610,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>malware detection; antivirus software; file integrity checking; signature‑based scanning; virus checking</t>
+          <t>malware detection; antivirus software; file integrity checking; signature‑based scanning; virus scanning</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -15665,19 +15625,15 @@
         </is>
       </c>
       <c r="S97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>keep:0, "Virus Checking Implementation":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -15787,12 +15743,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Legal Notice Auditing</t>
+          <t>Legal Notice Compliance</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>The worker checks that log‑on legal notices are aligned with organisational standards and checks for legislative compliance breaches.</t>
+          <t>Checks and aligns log‑on legal notices and system settings with organisational and legislative requirements.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -15814,11 +15770,11 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>legal notice; organisational requirements; legislation compliance; audit checks; auditing</t>
+          <t>legal notice verification; compliance checking; legislation alignment; legislation compliance breaches; log‑on display</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -15830,14 +15786,14 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Legal Notice Auditing</t>
+          <t>Legal Notice Compliance</t>
         </is>
       </c>
       <c r="S98" t="b">
         <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -15847,7 +15803,7 @@
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr">
         <is>
-          <t>The worker verifies that log‑on legal notices meet organisational standards and monitors for legislative compliance breaches.</t>
+          <t>Reviews and verifies that log‑on legal notices and system settings meet organisational and legislative requirements.</t>
         </is>
       </c>
       <c r="X98" t="b">
@@ -15855,7 +15811,7 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>legal notice, log on screen, organisational requirements, legislation compliance, audit checks</t>
+          <t>legal notice verification, compliance checking, legislation alignment, organisational requirements, log‑on display</t>
         </is>
       </c>
       <c r="Z98" t="b">
@@ -15952,12 +15908,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Security Procedure Implementation</t>
+          <t>Security Procedure Enforcement</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Implements approved security changes and documents any instances where security procedures are not being followed.</t>
+          <t>Documents non‑compliance with security procedures and implements approved security changes to ensure system integrity.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -15979,11 +15935,11 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>security procedures; security changes; procedure compliance; documentation; non‑compliance</t>
+          <t>compliance documentation; non‑compliance reporting; change implementation; security procedures; security enforcement</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -15995,14 +15951,14 @@
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Security Procedure Implementation</t>
+          <t>Security Procedure Enforcement</t>
         </is>
       </c>
       <c r="S99" t="b">
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -16012,15 +15968,15 @@
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Implements approved security changes and documents any instances where security procedures are not being followed.</t>
+          <t>Documents non‑compliance with security procedures and implements approved security changes to maintain system integrity.</t>
         </is>
       </c>
       <c r="X99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>security changes, procedure compliance, documentation, implementation, non‑compliance</t>
+          <t>compliance documentation, non‑compliance reporting, change implementation, security procedures, audit records</t>
         </is>
       </c>
       <c r="Z99" t="b">
@@ -16135,7 +16091,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>technical writing; research reporting; stakeholder communication; document design; drafting</t>
+          <t>technical writing; audience analysis; research reporting; stakeholder communication; document design</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -16153,7 +16109,7 @@
         <v>1</v>
       </c>
       <c r="T100" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -16162,7 +16118,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>keep:0, "Research Report Drafting/Report Drafting/Audience‑Focused Report Drafting":3</t>
+          <t>keep:0, "Research Report Drafting":3</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -16179,7 +16135,7 @@
         </is>
       </c>
       <c r="Z100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -16259,7 +16215,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Research Information Synthesis</t>
+          <t>Research Information Analysis</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -16290,7 +16246,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>research methodology; information retrieval; statistical analysis; data mining; synthesis</t>
+          <t>research methodology; information retrieval; statistical analysis; data mining; research strategy</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -16312,12 +16268,12 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>keep:0, "Research Information Synthesis":2, "Data Analysis Synthesis":1</t>
+          <t>keep:0, "Research Information Analysis/Information Analysis":3</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -16423,7 +16379,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Leverages digital tools' core functions to research and analyse information for research tasks.</t>
+          <t>Uses digital tools' core functions to research and analyse information for research tasks.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -16467,16 +16423,16 @@
         <v>1</v>
       </c>
       <c r="T102" t="n">
-        <v>0.9</v>
+        <v>0.925</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>keep:0, "Digital Research Tool Utilisation/Digital Tool Utilisation":3</t>
+          <t>keep:1, "Digital Research Tool Utilisation":2</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
@@ -16578,7 +16534,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Demonstrates conclusions by explicitly stating assumptions, justifying them, and supporting them with evidence.</t>
+          <t>Demonstrates conclusions by explicitly stating assumptions, justifying them, and supporting them with evidence in analyses.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -16910,7 +16866,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>data retrieval; data formatting; information extraction tools; content mining; data analysis</t>
+          <t>data retrieval; data formatting; information extraction tools; content mining; information analysis</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -17065,7 +17021,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>oral presentation; public speaking; audience analysis; persuasive communication; presentation design</t>
+          <t>public speaking; audience analysis; persuasive communication; presentation design; oral presentation</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -17083,16 +17039,16 @@
         <v>1</v>
       </c>
       <c r="T106" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.875</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Oral Presentation Delivery":2</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
@@ -17242,12 +17198,12 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>keep:0, "Foreseeable Problem Solving/Problem Solving":3</t>
+          <t>keep:0, "Problem Solving/Familiar Context Problem Solving":2, "Familiar Context Problem‑Solving":1</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
@@ -17348,12 +17304,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Draft Report Review Facilitation</t>
+          <t>Report Review Facilitation</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Facilitates team draft report review, ensuring compliance with organisational policies and procedures.</t>
+          <t>Facilitates team review of draft report, ensuring compliance with organisational policies and procedures.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -17379,7 +17335,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>document review; stakeholder engagement; quality assurance; facilitation; draft</t>
+          <t>document review; policy compliance; quality assurance; stakeholder engagement; facilitation</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -17394,19 +17350,15 @@
         </is>
       </c>
       <c r="S108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
-          <t>keep:1, "Draft Report Review Facilitation":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
@@ -17552,12 +17504,12 @@
         <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>keep:2, "Research Report Distribution":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -17659,7 +17611,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Identifies and researches strategies, ensuring alignment with objectives across hybrid environments.</t>
+          <t>Identifies research strategies, ensuring alignment with objectives across hybrid environments.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -17685,7 +17637,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>literature review; information retrieval; research design; relevance assessment; information research strategy</t>
+          <t>literature review; information retrieval; research design; relevance assessment; research strategy</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -17707,12 +17659,12 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>keep:0, "Research Strategy Identification":2, "Research Strategy Confirmation":1</t>
+          <t>keep:0, "Research Strategy Identification":3</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
@@ -17809,7 +17761,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Secure Information Storage</t>
+          <t>Research Information Storing</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -17840,7 +17792,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>information security; data protection; access control; encryption; records management</t>
+          <t>information security; data protection; access control; records management; research information</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -17855,15 +17807,19 @@
         </is>
       </c>
       <c r="S111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="U111" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>keep:1, "Information Storage Management":1, "Information Storage":1</t>
+          <t>keep:1, "Research Information Storing/Secure Information Storing":2</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
@@ -17880,7 +17836,7 @@
         </is>
       </c>
       <c r="Z111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -17965,7 +17921,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Plans and implements tasks to meet organisational requirements.</t>
+          <t>Plans, organizes, and executes tasks to meet organisational requirements and achieve objectives.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -18014,7 +17970,7 @@
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>keep:2, "Self‑Management Planning":1</t>
+          <t>keep:2, "Task Planning":1</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -18116,7 +18072,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Assesses source credibility against evidence and criteria during hybrid research tasks.</t>
+          <t>Assesses source credibility by cross‑checking evidence and criteria during hybrid research tasks.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -18142,7 +18098,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>source reliability; information verification; bias assessment; citation analysis; media literacy</t>
+          <t>reliability; source; information verification; bias assessment; citation analysis</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -18320,7 +18276,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>keep:0, "Theme Identification":2, "Thematic Pattern Identification":1</t>
+          <t>keep:1, "Theme Identification":2</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
@@ -18417,12 +18373,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Report Format Selection</t>
+          <t>Reporting Method Selection</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Identify reporting methods that align with the target audience and meet organisational requirements.</t>
+          <t>Identifies reporting methods that align with the target audience and organisational requirements, and reports on each output.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -18444,11 +18400,11 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>reporting methods; intended audience; organisational requirements; format selection; communication strategy</t>
+          <t>reporting methods; target audience; organisational requirements; research output; method selection</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -18459,14 +18415,14 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Report Format Selection</t>
+          <t>Reporting Method Selection</t>
         </is>
       </c>
       <c r="S115" t="b">
         <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -18476,7 +18432,7 @@
       <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Select reporting methods that suit the target audience and meet organisational requirements effectively.</t>
+          <t>Select reporting methods that suit the target audience and meet organisational requirements for each research output.</t>
         </is>
       </c>
       <c r="X115" t="b">
@@ -18484,7 +18440,7 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>reporting methods, intended audience, organisational requirements, format selection, communication strategy</t>
+          <t>reporting methods, target audience, organisational requirements, research output, method selection</t>
         </is>
       </c>
       <c r="Z115" t="b">
@@ -18573,7 +18529,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Barrier Identification</t>
+          <t>WHS Barrier Identification</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -18626,12 +18582,12 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>keep:0, "Barrier Identification":3</t>
+          <t>keep:0, "WHS Barrier Identification":2, "WHS Barrier Analysis":1</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
@@ -18893,7 +18849,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Consultation Process Facilitation</t>
+          <t>WHS Consultation Facilitation</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -18924,7 +18880,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>occupational health and safety; stakeholder engagement; WHS legislation compliance; safety committee facilitation; consultation</t>
+          <t>occupational health and safety; stakeholder engagement; WHS legislation compliance; risk management; WHS consultation</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -18939,15 +18895,19 @@
         </is>
       </c>
       <c r="S118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U118" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>keep:2, "WHS Consultation Facilitation":1</t>
+          <t>keep:1, "WHS Consultation Facilitation":2</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
@@ -18967,9 +18927,13 @@
         <v>1</v>
       </c>
       <c r="AA118" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB118" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>Duties Rights Responsibilities Communication (LLM verified, sim=0.68)</t>
+        </is>
+      </c>
       <c r="AC118" t="b">
         <v>0</v>
       </c>
@@ -19080,7 +19044,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>work health and safety; hazard reporting; issue raising; safety meetings; issue escalation</t>
+          <t>work health and safety; hazard reporting; safety meetings; issue escalation; WHS issue raising</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -19098,7 +19062,7 @@
         <v>1</v>
       </c>
       <c r="T119" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -19107,7 +19071,7 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>keep:0, "WHS Issue Raising/Meeting Issue Raising":3</t>
+          <t>keep:0, "WHS Issue Raising/WHS Issues Raising":3</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
@@ -19209,12 +19173,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Meeting Outcome Coordination</t>
+          <t>Meeting Outcome Follow-up Coordination</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Follows up meeting outcomes according to own job role and organisational policies and procedures.</t>
+          <t>Follows up post‑meeting actions by tracking outcomes in line with role responsibilities and company policies.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -19240,7 +19204,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>meeting coordination; outcome tracking; policy compliance; stakeholder communication; follow up meeting</t>
+          <t>meeting coordination; outcome tracking; follow-up; stakeholder communication; action item management</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -19262,12 +19226,12 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>keep:0, "Meeting Outcome Coordination/Meeting Outcome Follow-up Coordination":3</t>
+          <t>keep:1, "Meeting Outcome Follow-up Coordination":2</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
@@ -19426,12 +19390,12 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>keep:0, "WHS Information Communication":3</t>
+          <t>keep:1, "WHS Information Communication/WHS Information Plain-Language Communication":2</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
@@ -19693,12 +19657,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Barrier Solution Development</t>
+          <t>Suggestion Development</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Makes actionable suggestions to eliminate barriers, enhancing workplace health and safety consultations.</t>
+          <t>Makes suggestions to remove barriers, enhancing workplace health and safety consultations.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -19724,7 +19688,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>workplace health and safety; hazard barrier analysis; safety consultation; corrective action planning; barrier removal solution</t>
+          <t>workplace health and safety; hazard barrier analysis; safety consultation; corrective action planning; suggestion development</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -19751,7 +19715,7 @@
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>keep:0, "Barrier Solution Development":3</t>
+          <t>keep:0, "Barrier Removal Suggestion Development/Suggestion Development":3</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
@@ -19857,7 +19821,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Stakeholder Identification</t>
+          <t>WHS Stakeholder Identification</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -19888,7 +19852,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>occupational health and safety; stakeholder analysis; WHS legislation; compliance documentation; record key stakeholders</t>
+          <t>occupational health and safety; stakeholder analysis; WHS legislation; compliance documentation; key stakeholders</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -19915,7 +19879,7 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>keep:0, "Stakeholder Identification":3</t>
+          <t>keep:0, "WHS Stakeholder Identification/Stakeholder Identification":3</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
@@ -20048,7 +20012,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>occupational health and safety; policy compliance; recordkeeping; risk communication; discussion</t>
+          <t>occupational health and safety; policy compliance; recordkeeping; discussion; risk communication</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -20066,12 +20030,12 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "WHS Discussion Documentation":1</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
@@ -20227,7 +20191,7 @@
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>keep:1, "WHS Information Confirmation":1, "WHS Information Understanding":1</t>
+          <t>keep:2, "WHS Understanding Verification":1</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
@@ -20329,7 +20293,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>WHS Legislative Research</t>
+          <t>WHS Obligations Researching</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -20360,7 +20324,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>occupational health and safety legislation; compliance analysis; risk assessment; consultation and communication processes; regulatory research tools</t>
+          <t>occupational health and safety legislation; compliance analysis; consultation and communication processes; whs obligations; researching whs information</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -20375,15 +20339,19 @@
         </is>
       </c>
       <c r="S127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>keep:0, "WHS Legislative Review":1, "WHS Legislative Obligations Research":1, "WHS Obligations Investigation":1</t>
+          <t>keep:1, "WHS Obligations Researching":2</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
@@ -20400,7 +20368,7 @@
         </is>
       </c>
       <c r="Z127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -20485,7 +20453,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Communication Form Selection</t>
+          <t>Communication Form Identification</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -20495,7 +20463,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>technical</t>
+          <t>cognitive</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -20508,15 +20476,15 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>practical</t>
+          <t>theoretical</t>
         </is>
       </c>
       <c r="N128" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>communication methods; WHS stakeholders; form selection; appropriate channels; forms of communication</t>
+          <t>communication methods; required individuals; WHS stakeholders; appropriate forms; communication selection</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -20527,14 +20495,14 @@
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Communication Form Selection</t>
+          <t>Communication Form Identification</t>
         </is>
       </c>
       <c r="S128" t="b">
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -20552,11 +20520,11 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>communication methods, WHS stakeholders, form selection, appropriate channels, information delivery</t>
+          <t>communication methods, required individuals, WHS stakeholders, appropriate forms, communication selection</t>
         </is>
       </c>
       <c r="Z128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -20646,7 +20614,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Communicates the WHS-related outcomes of meetings to designated individuals or parties promptly and accurately.</t>
+          <t>Communicates WHS meeting outcomes to relevant individuals and parties promptly and accurately.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -20668,11 +20636,11 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>WHS outcomes; meeting communication; stakeholder notification; required individuals; outcome reporting</t>
+          <t>WHS outcomes; meeting results; required individuals; communication channels; stakeholder notification</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -20690,7 +20658,7 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -20700,7 +20668,7 @@
       <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Communicates the WHS-related outcomes of meetings to designated individuals or parties promptly and accurately.</t>
+          <t>Communicates WHS meeting outcomes to relevant individuals and parties promptly and accurately.</t>
         </is>
       </c>
       <c r="X129" t="b">
@@ -20708,11 +20676,11 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>WHS outcomes, meeting communication, stakeholder notification, information dissemination, outcome reporting</t>
+          <t>WHS outcomes, meeting results, required individuals, communication channels, stakeholder notification</t>
         </is>
       </c>
       <c r="Z129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -20831,7 +20799,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>network security; firewall policies; intrusion prevention; advanced firewall functions; Cisco ASA</t>
+          <t>network security; firewall policies; intrusion prevention; VPN configuration; advanced firewall functions</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -20959,7 +20927,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Device Configuration Backup</t>
+          <t>Device Configuration Backuping</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -20990,7 +20958,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>network security; configuration management; backup automation; device; change control</t>
+          <t>network security; configuration management; backup automation; device configuration; change control</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -21005,15 +20973,19 @@
         </is>
       </c>
       <c r="S131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U131" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: Structure Rule 1 — tail 'Backup' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Device Configuration Backup":2</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
@@ -21041,9 +21013,13 @@
       </c>
       <c r="AD131" t="inlineStr"/>
       <c r="AE131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF131" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>Structure Rule 1 — tail 'Backup' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -21123,7 +21099,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Determines required firewall security according to organisational requirements.</t>
+          <t>Determines required firewall configurations according to organisational requirements for hybrid environments.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -21167,16 +21143,16 @@
         <v>1</v>
       </c>
       <c r="T132" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>keep:0, "Firewall Security Determination":3</t>
+          <t>keep:1, "Firewall Security Determination":2</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
@@ -21286,7 +21262,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Configures required perimeter topology to meet specified security requirements.</t>
+          <t>Configures perimeter network topology to meet specified security requirements.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -21312,7 +21288,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>perimeter security; VLAN segmentation; firewall configuration; network architecture; perimeter topology</t>
+          <t>perimeter topology; perimeter security; VLAN segmentation; firewall configuration; network architecture</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -21334,12 +21310,12 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>keep:0, "Perimeter Topology Configuration":3</t>
+          <t>keep:1, "Perimeter Topology Configuration":2</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
@@ -21448,12 +21424,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Penetration Testing Verification</t>
+          <t>Penetration Testing</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tests penetration of network perimeter and verifies compliance with security standards.</t>
+          <t>Tests penetration of network perimeter and verifies compliance with security requirements.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -21479,7 +21455,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>penetration testing; verification; vulnerability assessment; perimeter validation; cybersecurity</t>
+          <t>cybersecurity; vulnerability assessment; perimeter validation; penetration testing; testing</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -21506,7 +21482,7 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>keep:1, "Penetration Testing Verification":2</t>
+          <t>keep:1, "Penetration Testing":2</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
@@ -21774,12 +21750,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Perimeter Security Research</t>
+          <t>Perimeter Security Options Identification</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Researches and identifies perimeter security solutions against organisational requirements in hybrid environments.</t>
+          <t>Researches and identifies perimeter security options against organisational requirements in hybrid environments.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -21805,7 +21781,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>network security; firewall; intrusion detection; security assessment; perimeter security</t>
+          <t>network security; firewall; intrusion detection; perimeter security; security options</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -21820,15 +21796,19 @@
         </is>
       </c>
       <c r="S136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>keep:0, "Perimeter Security Options Survey":1, "Perimeter Security Options Investigation":1, "Perimeter Security Identification":1</t>
+          <t>keep:0, "Perimeter Security Identification/Perimeter Security Options Identification":3</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
@@ -22109,7 +22089,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Designs hybrid security perimeters with organisational requirements and operational constraints.</t>
+          <t>Designs hybrid security perimeters according to organisational requirements and operational constraints.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -22135,7 +22115,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>network security; firewall architecture; DMZ segmentation; defense in depth; perimeter design</t>
+          <t>network security; firewall architecture; DMZ segmentation; perimeter design; security perimeter</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -22153,12 +22133,12 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>keep:2, "Security Perimeter Design":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
@@ -22268,7 +22248,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Identifies organisational and industry security threats according to policies and procedures in hybrid environments.</t>
+          <t>Identifies organisational and industry security threats in hybrid environments according to policies and procedures.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -22312,12 +22292,12 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>keep:2, "Security Threat Identification":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
@@ -22422,12 +22402,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Service Continuity Enablement</t>
+          <t>Service Continuity Design</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Designs and configures perimeter solutions to enable service continuity during device upgrades in hybrid environments.</t>
+          <t>Designs and configures perimeter solutions for service continuity during device upgrades in hybrid environments.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -22453,7 +22433,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>perimeter security; high availability; disaster recovery; configuration management; service continuity</t>
+          <t>perimeter security; high availability; disaster recovery; configuration management; service continuity design</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -22480,7 +22460,7 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>keep:0, "Service Continuity Enablement":2, "Service Continuity Design":1</t>
+          <t>keep:0, "Service Continuity Design":2, "Service Continuity Configuration":1</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
@@ -22590,7 +22570,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Configures network perimeter devices for site‑to‑site VPN tunnels.</t>
+          <t>Configures perimeter devices for site‑to‑site VPN tunnels.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -22631,19 +22611,15 @@
         </is>
       </c>
       <c r="S141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>keep:1, "Site‑to‑Site VPN Configuration":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
@@ -22805,12 +22781,12 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>keep:0, "Functionality Performance Documentation/Performance Results Documentation":3</t>
+          <t>keep:1, "Performance Results Documentation":2</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
@@ -22920,7 +22896,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Diagnoses and resolves VPN connectivity problems using security policies and troubleshooting protocols.</t>
+          <t>Diagnoses and resolves VPN connectivity problems.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -23246,7 +23222,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Tests basic firewall and VPN features to ensure they meet defined security requirements.</t>
+          <t>Tests basic firewall and VPN features to ensure they meet defined network security requirements.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -23272,7 +23248,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>basic feature verification; security requirement testing; functional assessment; network device testing; compliance validation</t>
+          <t>basic feature verification; network security requirements; functional testing; functionality; compliance assessment</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -23300,7 +23276,7 @@
       <c r="V145" t="inlineStr"/>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Conducts hands‑on tests to verify basic firewall and VPN features meet defined security requirements.</t>
+          <t>Conducts practical tests to verify basic firewall and VPN features meet defined network security requirements.</t>
         </is>
       </c>
       <c r="X145" t="b">
@@ -23308,11 +23284,11 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>basic feature verification, security requirement testing, functional assessment, network device testing, compliance validation</t>
+          <t>basic feature verification, network security requirements, functional testing, perimeter devices, compliance assessment</t>
         </is>
       </c>
       <c r="Z145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -23385,7 +23361,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Digital Tool Design Recognition</t>
+          <t>Digital Tool Design Understanding</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -23416,7 +23392,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>human-computer interaction; usability; design principles; digital tool development; recognition</t>
+          <t>human-computer interaction; usability; software architecture; design principles; digital tool development</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -23431,19 +23407,15 @@
         </is>
       </c>
       <c r="S146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T146" t="n">
         <v>0.9</v>
       </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+      <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>keep:0, "Digital Tool Design Recognition":2, "Digital Tool Design Familiarisation":1</t>
+          <t>keep:2, "Digital Tool Principles Understanding":1</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
@@ -23460,7 +23432,7 @@
         </is>
       </c>
       <c r="Z146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -23564,7 +23536,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>technology scouting; trend analysis; strategic foresight; technology roadmapping; emerging technologies</t>
+          <t>emerging technologies; technology scouting; trend analysis; strategic foresight; technology roadmapping</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -23607,17 +23579,17 @@
         <v>1</v>
       </c>
       <c r="AA147" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB147" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>Information Source Assessment (LLM verified, sim=0.67)</t>
+        </is>
+      </c>
       <c r="AC147" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>FS implicit in PCs — covered by: 1.2 Identify and document emerging technologies and practice</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
@@ -23874,12 +23846,12 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Information Source Assessment":1</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -23899,17 +23871,17 @@
         <v>1</v>
       </c>
       <c r="AA149" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>Emerging Technology Identification (LLM verified, sim=0.67)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD149" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>FS implicit in PCs — covered by: 1.1 Access sources of information on emerging technologies a</t>
+        </is>
+      </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
@@ -24004,7 +23976,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>technology trends; emerging technologies; IT industry developments; discussion; technical communication</t>
+          <t>technology trends; digital transformation; emerging technologies; IT industry developments; discussion</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -24122,7 +24094,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Identifies changes to organisational technologies and practices required based on strategies, documenting them for implementation.</t>
+          <t>Identifies changes to organisational technologies and practices required based on strategies and documents them.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -24148,7 +24120,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>change management; technology adoption; process redesign; strategic roadmap; organisational change</t>
+          <t>change management; technology adoption; strategic roadmap; stakeholder analysis; organisational change</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -24166,7 +24138,7 @@
         <v>1</v>
       </c>
       <c r="T151" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
@@ -24175,7 +24147,7 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>keep:1, "Organisational Change Identification":1, "Technology Change Planning":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
@@ -24269,7 +24241,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Professional Development Recognition</t>
+          <t>Professional Development Opportunity Recognition</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -24300,7 +24272,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>continuous learning; career development; learning &amp; development; CPD opportunities; professional development</t>
+          <t>continuous learning; career development; learning &amp; development; CPD opportunities; recognition</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -24315,15 +24287,19 @@
         </is>
       </c>
       <c r="S152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U152" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Professional Development Opportunity Recognition":2</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
@@ -24413,7 +24389,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Regulatory Compliance Awareness</t>
+          <t>Regulatory Compliance Management</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -24444,7 +24420,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>legal obligations; governance frameworks; audit procedures; compliance management systems; regulatory awareness</t>
+          <t>legal obligations; governance frameworks; audit procedures; compliance management systems; regulatory responsibilities</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -24459,15 +24435,19 @@
         </is>
       </c>
       <c r="S153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T153" t="n">
-        <v>0</v>
-      </c>
-      <c r="U153" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: Structure Rule 4 — tail 'Adherence' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>keep:0, "Regulatory Compliance":1, "Regulatory Compliance Adherence":1, "Regulatory Compliance Management":1</t>
+          <t>keep:0, "Regulatory Compliance Adherence":3</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
@@ -24495,9 +24475,13 @@
       </c>
       <c r="AD153" t="inlineStr"/>
       <c r="AE153" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF153" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Adherence' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -24562,7 +24546,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Investigates, evaluates, and applies data from complex technical texts to inform outcomes.</t>
+          <t>Investigates, evaluates, and applies data from complex technical texts.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -24588,7 +24572,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>literature review; critical appraisal; academic databases; citation management; application</t>
+          <t>literature review; critical appraisal; academic databases; citation management; information application</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -24635,13 +24619,9 @@
         <v>1</v>
       </c>
       <c r="AA154" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>Technical Documentation Interpretation (LLM verified, sim=0.61)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="b">
         <v>0</v>
       </c>
@@ -24709,12 +24689,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Threat Opportunity Analysis</t>
+          <t>Risk Opportunity Analysis</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Risk and opportunity analysis of emerging technologies to determine organisational impacts.</t>
+          <t>Risk and opportunity analysis of emerging technologies to identify organisational impacts.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -24755,19 +24735,15 @@
         </is>
       </c>
       <c r="S155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>keep:0, "Threat Opportunity Analysis/Opportunity Threat Analysis":3</t>
+          <t>keep:2, "Risk Opportunity Analysis":1</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
@@ -24888,7 +24864,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>stakeholder engagement; feedback collection; report synthesis; integration; organizational liaison</t>
+          <t>stakeholder engagement; feedback collection; report synthesis; organizational liaison; feedback integration</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -24903,15 +24879,19 @@
         </is>
       </c>
       <c r="S156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T156" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="U156" t="inlineStr"/>
+        <v>0.925</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Stakeholder Feedback Integration/Organisational Feedback Integration":2</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
@@ -25032,7 +25012,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>emerging technology; technology foresight; scenario planning; change management; digital transformation strategy</t>
+          <t>technology foresight; scenario planning; change management; digital transformation strategy; emerging technology</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -25184,7 +25164,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>technical manuals; engineering drawings; specification sheets; diagram analysis; interpretation</t>
+          <t>technical manuals; engineering drawings; specification sheets; diagram analysis; documentation interpretation</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -25350,7 +25330,7 @@
         <v>1</v>
       </c>
       <c r="T159" t="n">
-        <v>0.9</v>
+        <v>0.925</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
@@ -25359,7 +25339,7 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>keep:1, "Emerging Technology Impact Evaluation":2</t>
+          <t>keep:1, "Emerging Technology Impact Evaluation/Technology Impact Evaluation":2</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
@@ -25449,12 +25429,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Emerging Technology Planning</t>
+          <t>Technology Implementation Planning</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Designs and executes implementation plans using proven methods to deploy technology solutions on schedule.</t>
+          <t>Implementation plans using proven methods to technology solutions on schedule.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -25480,7 +25460,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>implementation roadmap; change management; deployment strategy; stakeholder alignment; emerging technology</t>
+          <t>implementation roadmap; change management; deployment strategy; stakeholder alignment; technology</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -25495,19 +25475,15 @@
         </is>
       </c>
       <c r="S160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>keep:1, "Emerging Technology Planning/Emerging Technology Strategy Planning":2</t>
+          <t>keep:2, "Technology Strategy Development":1</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
@@ -25516,7 +25492,7 @@
         </is>
       </c>
       <c r="X160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y160" t="inlineStr">
         <is>
@@ -25656,12 +25632,12 @@
         <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>keep:0, "Abstract Script Design":1, "Abstract Design Creation":1, "Script Development":1</t>
+          <t>keep:2, "Script Abstract Design":1</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
@@ -25977,7 +25953,7 @@
       </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>keep:0, "Algorithm Termination Verification":2, "Algorithm Termination Assurance":1</t>
+          <t>keep:1, "Algorithm Termination Verification":2</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
@@ -26077,12 +26053,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Automation Guideline Interpretation</t>
+          <t>Automation Guidelines Identification</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Identifies automation guidelines and instructions and identifies applicable procedures for system design.</t>
+          <t>Identifies automation guidelines and instructions applicable to system design.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -26108,7 +26084,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>process automation; standard operating procedures; RPA guidelines; automation compliance; interpretation</t>
+          <t>process automation; automation guidelines; RPA guidelines; workflow documentation; automation compliance</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -26123,15 +26099,19 @@
         </is>
       </c>
       <c r="S164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T164" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U164" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>keep:2, "Automation Guideline Identification":1</t>
+          <t>keep:1, "Automation Guidelines Identification":2</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
@@ -26236,7 +26216,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Identifies uncovered sections and incorrect implementations in scripts, ensuring semantic accuracy.</t>
+          <t>Identifies scripts' uncovered sections and incorrect implementations, ensuring semantic accuracy.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -26280,12 +26260,12 @@
         <v>0</v>
       </c>
       <c r="T165" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>keep:2, "Script Semantic Verification":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
@@ -26385,7 +26365,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Code Syntax Debugging</t>
+          <t>Code Debugging</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -26431,15 +26411,19 @@
         </is>
       </c>
       <c r="S166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T166" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U166" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>keep:1, "Code Error Debugging":1, "Code Syntax Semantic Debugging":1</t>
+          <t>keep:0, "Code Debugging":2, "Script Debugging":1</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
@@ -26539,7 +26523,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Problem Solving Collaboration</t>
+          <t>Collaborative Problem Solving</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -26570,7 +26554,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>cross-functional collaboration; stakeholder engagement; perspective gathering; solution quality improvement; problem solving</t>
+          <t>cross-functional collaboration; stakeholder engagement; hybrid teamwork; perspective gathering; problem solving</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -26585,19 +26569,15 @@
         </is>
       </c>
       <c r="S167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T167" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>keep:0, "Problem Solving Collaboration":2, "Team Problem Solving":1</t>
+          <t>keep:2, "Problem Solving Collaboration":1</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
@@ -26904,12 +26884,12 @@
         <v>0</v>
       </c>
       <c r="T169" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Numerical Formula Analysis":1</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
@@ -27044,7 +27024,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>workflow analysis; process mapping; automation assessment; process requiring automation; business process improvement</t>
+          <t>workflow analysis; process mapping; automation assessment; RPA; process requiring automation</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -27066,12 +27046,12 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>keep:0, "Process Identification/Process Automation Identification":3</t>
+          <t>keep:1, "Process Automation Identification":2</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
@@ -27325,7 +27305,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Solution Brainstorming</t>
+          <t>Solution Discussion</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -27356,7 +27336,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>collaborative ideation; requirements gathering; problem‑solving facilitation; brainstorming; solution</t>
+          <t>collaborative ideation; requirements gathering; problem‑solving facilitation; discussion; solution</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -27383,7 +27363,7 @@
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>keep:1, "Solution Brainstorming":2</t>
+          <t>keep:1, "Solution Discussion/Team Solution Discussion":2</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
@@ -27483,12 +27463,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Technical Documentation Assessment</t>
+          <t>Technical Documentation Analysis</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Analyses complex technical documents to ensure accuracy.</t>
+          <t>Analyses complex technical documentation to amend inconsistencies and errors.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -27514,7 +27494,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>documentation review; error correction; technical writing standards; quality assurance; technical documentation</t>
+          <t>documentation review; error correction; technical writing standards; quality assurance; content management systems</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -27529,19 +27509,15 @@
         </is>
       </c>
       <c r="S173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T173" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>keep:0, "Technical Documentation Assessment":2, "Technical Documentation Review":1</t>
+          <t>keep:2, "Technical Documentation Review":1</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
@@ -27558,7 +27534,7 @@
         </is>
       </c>
       <c r="Z173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -27641,12 +27617,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Internal Documentation Creation</t>
+          <t>Technical Documentation Creation</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Creates internal technical documents following organisational guidelines and policies to ensure consistency.</t>
+          <t>Produces internal technical documents following organisational guidelines and policies to ensure consistency.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -27672,7 +27648,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>technical writing; SOP; documentation standards; internal documentation; Confluence</t>
+          <t>technical writing; knowledge base; SOP; documentation standards; Confluence</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -27687,19 +27663,15 @@
         </is>
       </c>
       <c r="S174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T174" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>keep:1, "Internal Documentation Creation":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
@@ -27708,7 +27680,7 @@
         </is>
       </c>
       <c r="X174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y174" t="inlineStr">
         <is>
@@ -27716,7 +27688,7 @@
         </is>
       </c>
       <c r="Z174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -27852,12 +27824,12 @@
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>keep:0, "Documentation Preparation":3</t>
+          <t>keep:1, "Documentation Preparation":2</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
@@ -27962,7 +27934,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Explains algorithmic solutions for a problem using sequence, selection, and iteration structures.</t>
+          <t>Describes algorithmic solutions for identified problems using sequence, selection, and iteration structures.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -28016,7 +27988,7 @@
       <c r="V176" t="inlineStr"/>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Explains algorithmic solutions for a problem using sequence, selection, and iteration structures.</t>
+          <t>Describes algorithmic solutions for identified problems using sequence, selection, and iteration structures.</t>
         </is>
       </c>
       <c r="X176" t="b">
@@ -28111,17 +28083,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Abstract Design Translation</t>
+          <t>Abstract Design Revision</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Reviews abstract designs for omissions and errors, then translates them into code following organisational guidelines.</t>
+          <t>Reviews abstract designs, corrects omissions and errors, and translates them into code following organisational guidelines.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>technical</t>
+          <t>cognitive</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -28142,7 +28114,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>abstract design; design review; error amendment; code translation; chosen language</t>
+          <t>abstract design; design revision; organisational guidelines; language translation; design errors</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -28154,7 +28126,7 @@
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Abstract Design Translation</t>
+          <t>Abstract Design Revision</t>
         </is>
       </c>
       <c r="S177" t="b">
@@ -28171,7 +28143,7 @@
       <c r="V177" t="inlineStr"/>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Reviews abstract designs for omissions and errors, then translates them into code following organisational guidelines.</t>
+          <t>Reviews abstract designs, corrects omissions and errors, and translates them into code following organisational guidelines.</t>
         </is>
       </c>
       <c r="X177" t="b">
@@ -28179,7 +28151,7 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>abstract design, design review, error amendment, code translation, organisational guidelines</t>
+          <t>abstract design, design omissions, design errors, organisational guidelines, language translation</t>
         </is>
       </c>
       <c r="Z177" t="b">
@@ -28266,12 +28238,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Issue Confirmation</t>
+          <t>Problem Confirmation</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Confirms identified problems with team members and resolves them as required, ensuring shared understanding and agreement.</t>
+          <t>Confirms identified problems with team members and resolves any issues as required, ensuring shared understanding.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -28281,11 +28253,11 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>APPLY</t>
+          <t>ASSIST</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -28293,11 +28265,11 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>problem confirmation; team communication; issue resolution; collaborative verification; team members</t>
+          <t>problem confirmation; team communication; issue resolution; stakeholder engagement; team members</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -28308,14 +28280,14 @@
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Issue Confirmation</t>
+          <t>Problem Confirmation</t>
         </is>
       </c>
       <c r="S178" t="b">
         <v>0</v>
       </c>
       <c r="T178" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="U178" t="inlineStr">
         <is>
@@ -28325,7 +28297,7 @@
       <c r="V178" t="inlineStr"/>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Confirms identified problems with team members and resolves them as required, ensuring shared understanding and agreement.</t>
+          <t>Confirms identified problems with team members and resolves any issues as required, ensuring shared understanding.</t>
         </is>
       </c>
       <c r="X178" t="b">
@@ -28333,7 +28305,7 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>problem confirmation, team communication, issue resolution, collaborative verification, stakeholder alignment</t>
+          <t>problem confirmation, team communication, issue resolution, stakeholder engagement, collaborative verification</t>
         </is>
       </c>
       <c r="Z178" t="b">
@@ -28420,12 +28392,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Active Listening Communication</t>
+          <t>Perspective Identification</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Identifies diverse viewpoints using active listening, observation, and targeted questioning during interactions.</t>
+          <t>Identifies diverse viewpoints by using active listening, observation, and targeted questioning during interactions.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -28451,7 +28423,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>active listening; questioning techniques; observational skills; perspective taking; interpersonal communication</t>
+          <t>active listening; questioning techniques; observational skills; perspective taking; different perspectives</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -28466,15 +28438,19 @@
         </is>
       </c>
       <c r="S179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T179" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U179" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>keep:1, "Active Listening":1, "Perspective Identification":1</t>
+          <t>keep:0, "Perspective Identification":2, "Active Listening":1</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
@@ -28491,7 +28467,7 @@
         </is>
       </c>
       <c r="Z179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -28605,7 +28581,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>security incident management; audit procedures; playbook development; response procedure; NIST CSF</t>
+          <t>security incident management; audit procedures; playbook development; SOC processes; NIST CSF</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -28627,12 +28603,12 @@
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Procedure Design":3</t>
+          <t>keep:1, "Incident Response Procedure Design/Incident Response Design":2</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
@@ -28649,7 +28625,7 @@
         </is>
       </c>
       <c r="Z180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -28737,7 +28713,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Applies logging analysis techniques to interpret system logs, identify issues, and support decision-making.</t>
+          <t>Logging analysis techniques.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -28781,12 +28757,12 @@
         <v>0</v>
       </c>
       <c r="T181" t="n">
-        <v>0.95</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>keep:2, "Log Analysis":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
@@ -28795,7 +28771,7 @@
         </is>
       </c>
       <c r="X181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y181" t="inlineStr">
         <is>
@@ -28891,7 +28867,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Identifies standard vulnerability types across environments during hybrid network security assessments.</t>
+          <t>Identifies standard vulnerability types across environments.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -28917,7 +28893,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>vulnerability scanning; network vulnerability; NIST standards; penetration testing; risk assessment</t>
+          <t>vulnerability scanning; NIST standards; penetration testing; risk assessment; network vulnerability</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -29044,12 +29020,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Security Audit Execution</t>
+          <t>Penetration Testing Execution</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Tests system vulnerabilities using auditing techniques to exploit them.</t>
+          <t>Tests system vulnerabilities using auditing techniques.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -29075,7 +29051,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>ethical hacking; vulnerability assessment; audit; execution; exploit development</t>
+          <t>ethical hacking; vulnerability assessment; Metasploit; Nmap; penetration testing</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -29090,19 +29066,15 @@
         </is>
       </c>
       <c r="S183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T183" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>keep:1, "Security Audit Execution":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
@@ -29206,12 +29178,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Risk Management Determination</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Determines risk management components based on network security design specifications in hybrid environments.</t>
+          <t>Identifies and defines risk management components based on network security design specifications in hybrid environments.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -29237,7 +29209,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>risk management; network security; threat assessment; security architecture; compliance standards</t>
+          <t>risk management; network security; threat assessment; security architecture; security design specifications</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -29264,7 +29236,7 @@
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>keep:0, "Risk Management Determination":2, "Risk Management Planning":1</t>
+          <t>keep:0, "Risk Management Planning":2, "Risk Management Determination":1</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
@@ -29273,7 +29245,7 @@
         </is>
       </c>
       <c r="X184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y184" t="inlineStr">
         <is>
@@ -29281,14 +29253,14 @@
         </is>
       </c>
       <c r="Z184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA184" t="b">
         <v>1</v>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>Threat Model Design (LLM verified, sim=0.71)</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="AC184" t="b">
@@ -29368,7 +29340,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Risk Management Plan Development</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -29417,16 +29389,16 @@
         <v>1</v>
       </c>
       <c r="T185" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>keep:0, "Risk Management Plan Development":3</t>
+          <t>keep:1, "Risk Management Plan Development":1, "Risk Management Plan Documentation":1</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
@@ -29531,7 +29503,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Tests security controls using penetration testing methods to test vulnerabilities.</t>
+          <t>Tests security audits using penetration testing methods to test vulnerabilities.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -29557,7 +29529,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>penetration testing; vulnerability assessment; risk assessment; audit; execution</t>
+          <t>penetration testing; vulnerability assessment; audit execution; Metasploit; risk assessment</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -29580,7 +29552,7 @@
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>keep:2, "Security Testing Execution":1</t>
+          <t>keep:2, "Security Audit Testing Execution":1</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
@@ -29680,7 +29652,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Security Information Evaluation</t>
+          <t>Security Controls Evaluation</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -29711,7 +29683,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>risk assessment; threat modeling; security frameworks; countermeasure planning; security information</t>
+          <t>risk assessment; security frameworks; countermeasure planning; compliance auditing; security controls</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -29726,19 +29698,15 @@
         </is>
       </c>
       <c r="S187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T187" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>keep:0, "Security Information Evaluation":2, "Security Control Planning":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
@@ -29869,7 +29837,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>cost analysis; asset valuation; ROI calculation; budgeting; estimation</t>
+          <t>cost estimation; cost analysis; asset valuation; ROI calculation; budgeting</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -29997,7 +29965,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Designs network security design planning phase for hybrid architecture in line with organisational requirements.</t>
+          <t>Designs network security design planning phase, incorporating hybrid architecture with organisational requirements.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -30045,12 +30013,12 @@
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>keep:0, "Network Security Design Planning":3</t>
+          <t>keep:1, "Network Security Design Planning":2</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
@@ -30155,7 +30123,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Develops and documents security policies across hybrid environments.</t>
+          <t>Develops and documents security policies across hybrid environments, ensuring technical controls meet organizational standards.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -30362,7 +30330,7 @@
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>keep:2, "Security Analysis":1</t>
+          <t>keep:1, "Security Analysis":1, "Security Problem Solving":1</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
@@ -30467,7 +30435,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Develops and documents technical information with factual data and industry terms for plans, policies, and breach reports.</t>
+          <t>Develops technical content with factual data and industry terminology, documents organisational plans and security policies, and plans breach response actions.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -30511,12 +30479,12 @@
         <v>0</v>
       </c>
       <c r="T192" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>keep:2, "Technical Documentation Writing":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
@@ -30620,7 +30588,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Threat Model Design</t>
+          <t>Threat Modelling</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -30651,7 +30619,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>network security; STRIDE methodology; security architecture; threat model; attack surface analysis</t>
+          <t>network security; attack surface analysis; STRIDE methodology; security architecture; threat model</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -30669,16 +30637,16 @@
         <v>1</v>
       </c>
       <c r="T193" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>postprocess: spelling/redundancy</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>keep:1, "Threat Model Design":2</t>
+          <t>keep:2, "Threat Model Design":1</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
@@ -30778,12 +30746,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Organisational Asset Identification</t>
+          <t>Asset Identification</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Identifies all organisational assets that require protection within the network environment.</t>
+          <t>Identifies organisational assets requiring protection for security design and risk management.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -30801,7 +30769,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>theoretical</t>
+          <t>practical</t>
         </is>
       </c>
       <c r="N194" t="n">
@@ -30809,7 +30777,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>asset inventory; protection requirements; organisational resources; asset classification; assets requiring protection</t>
+          <t>organisational assets; protection requirements; asset inventory; assets requiring protection; criticality assessment</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -30820,7 +30788,7 @@
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Organisational Asset Identification</t>
+          <t>Asset Identification</t>
         </is>
       </c>
       <c r="S194" t="b">
@@ -30837,7 +30805,7 @@
       <c r="V194" t="inlineStr"/>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Identifies and documents all organisational assets that require protection within the network environment.</t>
+          <t>Identifies and records organisational assets requiring protection to support security design and risk management.</t>
         </is>
       </c>
       <c r="X194" t="b">
@@ -30845,7 +30813,7 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>asset inventory, protection requirements, organisational resources, security scope, asset classification</t>
+          <t>organisational assets, protection requirements, asset inventory, security scope, criticality assessment</t>
         </is>
       </c>
       <c r="Z194" t="b">
@@ -30932,12 +30900,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Document Submission Coordination</t>
+          <t>Document Submission</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Submits security documents to designated personnel, solicits feedback, and addresses comments to finalise the documentation.</t>
+          <t>Submits security documents to designated personnel, solicits feedback, and incorporates responses appropriately.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -30963,7 +30931,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>document submission; designated personnel; feedback solicitation; comment response; finalisation</t>
+          <t>document distribution; feedback solicitation; response handling; stakeholder communication; document submission</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -30974,7 +30942,7 @@
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Document Submission Coordination</t>
+          <t>Document Submission</t>
         </is>
       </c>
       <c r="S195" t="b">
@@ -30991,7 +30959,7 @@
       <c r="V195" t="inlineStr"/>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Submits security documents to designated personnel, solicits feedback, and addresses comments to finalise the documentation.</t>
+          <t>Submits security documents to designated personnel, solicits feedback, and incorporates responses appropriately.</t>
         </is>
       </c>
       <c r="X195" t="b">
@@ -30999,11 +30967,11 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>document submission, designated personnel, feedback solicitation, comment response, finalisation</t>
+          <t>document distribution, feedback solicitation, response handling, stakeholder communication, revision management</t>
         </is>
       </c>
       <c r="Z195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -31273,7 +31241,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>cloud infrastructure; metrics-driven scaling; virtual machine scaling; autoscaling; configuration</t>
+          <t>autoscaling; configuration; metrics-driven scaling; infrastructure as code; virtual machine scaling</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -31291,12 +31259,12 @@
         <v>0</v>
       </c>
       <c r="T197" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Autoscaling Configuration":1</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
@@ -31402,7 +31370,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Discusses hybrid cloud options by comparing models and services against business requirements.</t>
+          <t>Compares hybrid cloud options and discusses models and services against business requirements.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -31428,7 +31396,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>cloud computing; service models; AWS; Azure; cloud solution</t>
+          <t>cloud computing; service models; cloud solution; cost-benefit analysis; Azure</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -31446,12 +31414,12 @@
         <v>0</v>
       </c>
       <c r="T198" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>keep:2, "Cloud Solution Evaluation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
@@ -31583,7 +31551,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>active listening; constructive feedback; communication skills; feedback loop; response handling</t>
+          <t>active listening; constructive feedback; feedback loop; feedback response; feedback handling</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -31601,12 +31569,12 @@
         <v>0</v>
       </c>
       <c r="T199" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>keep:2, "Feedback Handling":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
@@ -31738,7 +31706,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>deployment; virtual network; Azure SQL Database; DBaaS; managed database</t>
+          <t>managed database; virtual network; Azure SQL Database; infrastructure as code; DBaaS</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -31756,12 +31724,12 @@
         <v>0</v>
       </c>
       <c r="T200" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>keep:2, "Managed Database Deployment":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
@@ -32022,7 +31990,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Plans and implements daily workload, deciding task order and timing, with limited collaboration.</t>
+          <t>Plans routine tasks and implements workload sequencing, timing and limited collaboration.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -32048,7 +32016,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>task sequencing; workload scheduling; operational workflow; collaboration coordination; routine tasks</t>
+          <t>routine tasks; task sequencing; workload scheduling; operational workflow; collaboration coordination</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -32203,7 +32171,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>load testing; auto‑scaling; performance monitoring; scalability analysis; cloud infrastructure</t>
+          <t>load testing; auto‑scaling; performance monitoring; scalability analysis; automatic scaling</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -32230,7 +32198,7 @@
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>keep:0, "Automatic Scaling Testing":2, "Autoscaling Testing":1</t>
+          <t>keep:1, "Automatic Scaling Testing":2</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
@@ -32247,7 +32215,7 @@
         </is>
       </c>
       <c r="Z203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -32380,12 +32348,12 @@
         <v>0</v>
       </c>
       <c r="T204" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>keep:2, "Security Responsibility Impact Identification":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
@@ -32517,7 +32485,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>stakeholder management; documentation; reporting; liaison; work communication</t>
+          <t>stakeholder management; documentation; reporting; work; liaison</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -32544,7 +32512,7 @@
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>keep:0, "Work Communication/Work Documentation Communication":2, "Stakeholder Communication":1</t>
+          <t>keep:0, "Work Communication/Work Documentation Communication":2, "Work Communication Coordination":1</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
@@ -32568,7 +32536,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>Work Documentation Preparation</t>
+          <t>Technical Documentation Preparation</t>
         </is>
       </c>
       <c r="AC205" t="b">
@@ -32654,7 +32622,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Defines, adds and expands VM storage volumes to meet business requirements.</t>
+          <t>Defines, adds and expands VM storage to meet business requirements.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -32680,7 +32648,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>virtualization; storage provisioning; capacity planning; storage allocation; cloud IaaS</t>
+          <t>virtualization; storage provisioning; capacity planning; storage allocation; hypervisor</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -32702,12 +32670,12 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>keep:0, "Storage Allocation/Virtual-Machine Storage Allocation":2, "Storage Allocation Configuration":1</t>
+          <t>keep:0, "Storage Allocation":3</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
@@ -32808,7 +32776,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Work Documentation Preparation</t>
+          <t>Technical Documentation Preparation</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -32839,7 +32807,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>technical writing; documentation standards; version control; user manuals; work documentation</t>
+          <t>technical writing; documentation standards; version control; collaboration tools; user manuals</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -32854,19 +32822,15 @@
         </is>
       </c>
       <c r="S207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T207" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>keep:0, "Work Documentation Preparation/Documentation Preparation":2, "Work Documentation":1</t>
+          <t>keep:2, "Documentation Preparation":1</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
@@ -32883,7 +32847,7 @@
         </is>
       </c>
       <c r="Z207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -33002,7 +32966,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>hypervisor; virtual machine; infrastructure as code; OS deployment; virtualization platform</t>
+          <t>virtual machine; hypervisor; infrastructure as code; OS deployment; virtualization platform</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -33126,7 +33090,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Virtual Network Design</t>
+          <t>Virtual Network Creation</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -33157,7 +33121,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>software-defined networking; cloud networking; autoscaling; load balancing; virtual network design</t>
+          <t>software-defined networking; multi-tier architecture; cloud networking; autoscaling; virtual network</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -33172,15 +33136,19 @@
         </is>
       </c>
       <c r="S209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T209" t="n">
-        <v>0</v>
-      </c>
-      <c r="U209" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>keep:0, "Virtual Network Configuration":1, "Virtual Network Creation":1, "Virtual Network Planning":1</t>
+          <t>keep:0, "Virtual Network Creation":2, "Virtual Network Deployment":1</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
@@ -33312,7 +33280,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>capacity planning; business requirements analysis; resource allocation; workload management tools; workload definition</t>
+          <t>capacity planning; business requirements analysis; resource allocation; workload definition; workload management tools</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -33440,17 +33408,17 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Security Role Allocation</t>
+          <t>Security Responsibility Assignment</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Identifies and assigns security responsibilities based on policies, protocols and specific work functions.</t>
+          <t>Identifies and allocates security responsibilities based on policies, business protocols and specific work functions.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>cognitive</t>
+          <t>domain_knowledge</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -33467,11 +33435,11 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>security policies; business protocols; work function; responsibility assignment; role allocation</t>
+          <t>security responsibilities; security policies; business protocols; work function; assignment</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -33482,14 +33450,14 @@
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr">
         <is>
-          <t>Security Role Allocation</t>
+          <t>Security Responsibility Assignment</t>
         </is>
       </c>
       <c r="S211" t="b">
         <v>0</v>
       </c>
       <c r="T211" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
@@ -33499,7 +33467,7 @@
       <c r="V211" t="inlineStr"/>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Identifies and assigns security responsibilities based on policies, protocols and specific work functions.</t>
+          <t>Identifies and allocates security responsibilities based on policies, business protocols and specific work functions.</t>
         </is>
       </c>
       <c r="X211" t="b">
@@ -33507,7 +33475,7 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>security policies, business protocols, work function, responsibility assignment, role allocation</t>
+          <t>security responsibilities, security policies, business protocols, work function, assignment</t>
         </is>
       </c>
       <c r="Z211" t="b">
@@ -33595,12 +33563,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Infrastructure Identity Provisioning</t>
+          <t>Identity Provisioning</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Creates users and groups to manage cloud infrastructure in line with business requirements.</t>
+          <t>Creates user accounts and groups to manage cloud infrastructure according to business requirements.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -33622,11 +33590,11 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>user creation; group management; identity provisioning; cloud infrastructure; infrastructure management</t>
+          <t>user account creation; group configuration; infrastructure management; provisioning; identity</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -33637,14 +33605,14 @@
       <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr">
         <is>
-          <t>Infrastructure Identity Provisioning</t>
+          <t>Identity Provisioning</t>
         </is>
       </c>
       <c r="S212" t="b">
         <v>0</v>
       </c>
       <c r="T212" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
@@ -33654,7 +33622,7 @@
       <c r="V212" t="inlineStr"/>
       <c r="W212" t="inlineStr">
         <is>
-          <t>Creates and configures users and groups to manage cloud infrastructure in line with business requirements.</t>
+          <t>Creates and configures user accounts and groups to manage cloud infrastructure according to business requirements.</t>
         </is>
       </c>
       <c r="X212" t="b">
@@ -33662,7 +33630,7 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>user creation, group management, identity provisioning, cloud infrastructure, business requirements</t>
+          <t>user account creation, group configuration, infrastructure management, business requirements, cloud environment</t>
         </is>
       </c>
       <c r="Z212" t="b">
@@ -33755,12 +33723,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>The worker saves and stores user documentation in accordance with organisational policies and procedures.</t>
+          <t>Stores user documentation in designated repositories following organisational policies and procedures.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>domain_knowledge</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -33781,7 +33749,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>document storage; organisational policies; compliance standards; record keeping; archival process</t>
+          <t>user documentation; document storage; organisational policies; archiving process; file management</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -33809,7 +33777,7 @@
       <c r="V213" t="inlineStr"/>
       <c r="W213" t="inlineStr">
         <is>
-          <t>The worker saves and stores user documentation in accordance with organisational policies and procedures.</t>
+          <t>Stores user documentation in designated repositories following organisational policies and procedures.</t>
         </is>
       </c>
       <c r="X213" t="b">
@@ -33817,11 +33785,11 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>document storage, organisational policies, compliance standards, record keeping, archival process</t>
+          <t>document storage, organisational policies, archiving process, compliance standards, file management</t>
         </is>
       </c>
       <c r="Z213" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -34068,7 +34036,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Directory Service Administration</t>
+          <t>Directory Service Configuration</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -34099,7 +34067,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>Active Directory; LDAP; identity management; group policy; directory service administration</t>
+          <t>Active Directory; LDAP; identity management; directory service; configuration</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -34114,15 +34082,19 @@
         </is>
       </c>
       <c r="S215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T215" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U215" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>keep:2, "Directory Service Configuration":1</t>
+          <t>keep:1, "Directory Service Configuration/Network Directory Service Configuration":2</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
@@ -34142,9 +34114,13 @@
         <v>1</v>
       </c>
       <c r="AA215" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB215" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>Network Service Configuration (LLM verified, sim=0.64)</t>
+        </is>
+      </c>
       <c r="AC215" t="b">
         <v>0</v>
       </c>
@@ -34227,12 +34203,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Disk Partitioning Scheme Design</t>
+          <t>Disk Partitioning Design</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Creates disk partitioning scheme, file systems, and virtual memory according to business needs.</t>
+          <t>Creates disk partitioning scheme, file systems, and virtual memory according to business requirements.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -34258,7 +34234,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>storage architecture; file system layout; scheme; partitioning tools; disk</t>
+          <t>storage architecture; file system layout; logical volume management; partitioning tools; disk design</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -34273,19 +34249,15 @@
         </is>
       </c>
       <c r="S216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T216" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr">
         <is>
-          <t>keep:0, "Disk Partitioning Scheme Design/Disk Partitioning Design":2, "Disk Partitioning Scheme Creation":1</t>
+          <t>keep:2, "Disk Partitioning Scheme Development":1</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
@@ -34390,7 +34362,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>E-waste Disposal Compliance</t>
+          <t>Equipment Disposal</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -34421,7 +34393,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>e-waste regulations; hazardous waste management; environmental compliance; asset disposal procedures; excess equipment</t>
+          <t>e-waste regulations; hazardous waste management; environmental compliance; asset disposal procedures; equipment</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -34448,7 +34420,7 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>keep:1, "e-waste disposal compliance":2</t>
+          <t>keep:0, "Equipment Disposal":2, "e-waste Disposal":1</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
@@ -34468,21 +34440,25 @@
         <v>1</v>
       </c>
       <c r="AA217" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB217" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>Equipment Disposal Coordination</t>
+        </is>
+      </c>
       <c r="AC217" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FS implicit in PCs — covered by: 5.3 Dispose of excess equipment according to organisational </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD217" t="inlineStr"/>
       <c r="AE217" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF217" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>Structure Rule 1 — tail 'Disposal' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -34606,12 +34582,12 @@
         <v>0</v>
       </c>
       <c r="T218" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="U218" t="inlineStr"/>
       <c r="V218" t="inlineStr">
         <is>
-          <t>keep:0, "Equipment Disposal Management":1, "Equipment Disposal Execution":1, "Equipment Disposal Coordination":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
@@ -34631,17 +34607,17 @@
         <v>1</v>
       </c>
       <c r="AA218" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>E-waste Disposal Compliance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB218" t="inlineStr"/>
       <c r="AC218" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD218" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FS implicit in PCs — covered by: 5.3 Dispose of excess equipment according to organisational </t>
+        </is>
+      </c>
       <c r="AE218" t="b">
         <v>0</v>
       </c>
@@ -34751,7 +34727,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>network operating system; server application deployment; network configuration; system installation; network services (DHCP; DNS; VPN)</t>
+          <t>network operating system; server application deployment; configuration; system installation; network services (DHCP; DNS; VPN)</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -34910,7 +34886,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>vulnerability remediation; OS and application updates; security compliance; patch deployment tools; patch management</t>
+          <t>vulnerability remediation; OS and application updates; configuration management; patch deployment tools; patch management</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -34933,7 +34909,7 @@
       <c r="U220" t="inlineStr"/>
       <c r="V220" t="inlineStr">
         <is>
-          <t>keep:2, "System Patch Deployment":1</t>
+          <t>keep:1, "Patch Management":1, "Operating System Application Patching":1</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
@@ -35043,7 +35019,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Creates and manages user security and network permissions according to organisational policies.</t>
+          <t>Creates and manages user security and network permissions in line with organisational policies.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -35069,7 +35045,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>identity and access management; role‑based access control; user provisioning; authentication/authorization tools; network access</t>
+          <t>identity and access management; role‑based access control; network security policies; user provisioning; network access</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -35091,12 +35067,12 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>keep:1, "User Access Management":2</t>
+          <t>keep:0, "User Access Management":3</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
@@ -35360,7 +35336,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Server Documentation</t>
+          <t>Server Documentation Preparation</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -35391,7 +35367,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>configuration management; change management; technical writing; system administration; server administration</t>
+          <t>configuration management; change management; technical writing; system administration; server</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -35406,19 +35382,15 @@
         </is>
       </c>
       <c r="S223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T223" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
-          <t>keep:1, "Server Documentation":2</t>
+          <t>keep:2, "Server Configuration Documentation":1</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
@@ -35528,7 +35500,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Prepares server installations by identifying organisational needs and identifying appropriate applications and features.</t>
+          <t>Prepares server installations by identifying organisational needs and required applications and features.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -35554,7 +35526,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>server deployment; application requirements; infrastructure planning; capacity sizing; server installation</t>
+          <t>server deployment; application requirements; infrastructure planning; capacity sizing; installation</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -35572,12 +35544,12 @@
         <v>0</v>
       </c>
       <c r="T224" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
-          <t>keep:2, "Server Installation Preparation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
@@ -35735,12 +35707,12 @@
         <v>0</v>
       </c>
       <c r="T225" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Server Testing":1</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
@@ -35876,7 +35848,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>IT infrastructure; system administration; hardware failure; server troubleshooting; server management</t>
+          <t>IT infrastructure; network diagnostics; system administration; event log analysis; server troubleshooting</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -36013,7 +35985,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Advises users of deployment downtime while arranging site access for stakeholders.</t>
+          <t>Arranges stakeholder communications by arranging site access and advising users of deployment downtime.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -36057,12 +36029,12 @@
         <v>0</v>
       </c>
       <c r="T227" t="n">
-        <v>0</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U227" t="inlineStr"/>
       <c r="V227" t="inlineStr">
         <is>
-          <t>keep:0, "Stakeholder Communication Arrangement":1, "Stakeholder Communication":1, "Stakeholder Communication Advisement":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
@@ -36198,7 +36170,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>operating system policies; login scripts; user environment; environment variables; configuration management</t>
+          <t>operating system policies; login scripts; environment variables; configuration management; user environment</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -36330,12 +36302,12 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Connectivity Reconfiguration</t>
+          <t>Connectivity Device Reconfiguration</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Reconnects and reconfigures network connectivity devices to ensure optimal server communication and performance.</t>
+          <t>Reconnects and reconfigures network connectivity devices to ensure proper server communication and functionality.</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -36361,7 +36333,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>network devices; connectivity settings; configuration changes; hardware reconnection; connectivity devices</t>
+          <t>network devices; connectivity configuration; server integration; device settings; reconfiguration</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -36372,7 +36344,7 @@
       <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Connectivity Reconfiguration</t>
+          <t>Connectivity Device Reconfiguration</t>
         </is>
       </c>
       <c r="S229" t="b">
@@ -36389,7 +36361,7 @@
       <c r="V229" t="inlineStr"/>
       <c r="W229" t="inlineStr">
         <is>
-          <t>Re-establishes and adjusts network connectivity devices to ensure optimal server communication and performance.</t>
+          <t>Re-establishes and adjusts network connectivity devices to ensure proper server communication and functionality.</t>
         </is>
       </c>
       <c r="X229" t="b">
@@ -36397,7 +36369,7 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>network devices, connectivity settings, server links, configuration changes, hardware reconnection</t>
+          <t>network devices, connectivity configuration, server integration, cable management, device settings</t>
         </is>
       </c>
       <c r="Z229" t="b">
@@ -36520,7 +36492,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>server performance feedback; stakeholder input; response actions; performance monitoring; required personnel</t>
+          <t>server performance feedback; stakeholder input; response actions; performance monitoring; communication</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -36560,7 +36532,7 @@
         </is>
       </c>
       <c r="Z230" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -36633,7 +36605,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Communication Technology Identification</t>
+          <t>Collaboration Technology Identification</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -36691,7 +36663,7 @@
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>keep:0, "Communication Tools Identification/Communication Technology Identification":3</t>
+          <t>keep:0, "Collaboration Technology Identification/Collaborative Technology Identification/Communication Technology Identification":3</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
@@ -36929,7 +36901,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Cyber Security Protocol Development</t>
+          <t>Cyber Security Protocol Creation</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -36960,7 +36932,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>security protocols; security policy; compliance standards; incident response; access control</t>
+          <t>risk assessment; security policy; cyber security protocol; incident response; access control</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -36975,19 +36947,15 @@
         </is>
       </c>
       <c r="S233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T233" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U233" t="inlineStr"/>
       <c r="V233" t="inlineStr">
         <is>
-          <t>keep:1, "Cyber Security Protocol Development":2</t>
+          <t>keep:2, "Cyber Security Protocol Development":1</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
@@ -37226,7 +37194,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Seeks feedback from relevant personnel on team communication practices to improve communication processes.</t>
+          <t>Seeks feedback from team members to improve communication processes.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -37275,7 +37243,7 @@
       <c r="U235" t="inlineStr"/>
       <c r="V235" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Team Communication Feedback Solicitation":1</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
@@ -37369,7 +37337,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Knowledge Sharing According to Policy</t>
+          <t>Policy Knowledge Sharing</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -37400,7 +37368,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>knowledge sharing; knowledge management; information governance; corporate policy compliance; team collaboration</t>
+          <t>knowledge management; information governance; team collaboration; knowledge base platforms; knowledge sharing</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -37415,12 +37383,16 @@
         </is>
       </c>
       <c r="S236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T236" t="n">
         <v>0.9</v>
       </c>
-      <c r="U236" t="inlineStr"/>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>MIS re-refinement: Structure Rule 5 — tail 'Policy' is a pure object; append an action-as-noun describing what is done to it.</t>
+        </is>
+      </c>
       <c r="V236" t="inlineStr">
         <is>
           <t>keep:3</t>
@@ -37451,9 +37423,13 @@
       </c>
       <c r="AD236" t="inlineStr"/>
       <c r="AE236" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF236" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>Structure Rule 5 — tail 'Policy' is a pure object; append an action-as-noun describing what is done to it.</t>
+        </is>
+      </c>
       <c r="AG236" t="b">
         <v>0</v>
       </c>
@@ -37567,7 +37543,7 @@
       <c r="U237" t="inlineStr"/>
       <c r="V237" t="inlineStr">
         <is>
-          <t>keep:1, "Oral Communication Presentation":1, "Oral Communication":1</t>
+          <t>keep:2, "Oral Communication":1</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
@@ -37661,7 +37637,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Virtual Team Problem Solving</t>
+          <t>Problem Solving</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -37692,7 +37668,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>virtual collaboration; remote teamwork; problem solving; experiential learning; situational awareness</t>
+          <t>problem solving; rapid decision‑making; experiential learning; situational awareness; remote teamwork</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -37714,12 +37690,12 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>keep:0, "Virtual Team Problem Solving":2, "Virtual Team Problem‑Solving":1</t>
+          <t>keep:0, "Problem Solving/Virtual Team Problem Solving":3</t>
         </is>
       </c>
       <c r="W238" t="inlineStr">
@@ -37743,9 +37719,13 @@
       </c>
       <c r="AB238" t="inlineStr"/>
       <c r="AC238" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD238" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>generic FS capability "Problem Solving" is implicit in other skills</t>
+        </is>
+      </c>
       <c r="AE238" t="b">
         <v>0</v>
       </c>
@@ -37814,7 +37794,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Reviews virtual collaboration protocols to support teams working collaboratively in virtual environments.</t>
+          <t>Reviews virtual collaboration protocols to ensure compliance and supports effective team collaboration.</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -37858,12 +37838,12 @@
         <v>0</v>
       </c>
       <c r="T239" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr">
         <is>
-          <t>keep:2, "Protocol Compliance Review":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W239" t="inlineStr">
@@ -37883,13 +37863,9 @@
         <v>0</v>
       </c>
       <c r="AA239" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>Virtual Collaboration Compliance Monitoring (LLM verified, sim=0.80)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB239" t="inlineStr"/>
       <c r="AC239" t="b">
         <v>0</v>
       </c>
@@ -37957,12 +37933,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Protocol Improvement Determination</t>
+          <t>Protocol Improvement Recommendation</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Determines improvements to future work protocols in virtual environments.</t>
+          <t>Determines improvements to virtual work processes and protocol enhancements for future projects.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -37988,7 +37964,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>virtual collaboration; workflow optimization; remote work protocols; process improvement; digital SOP tools</t>
+          <t>virtual collaboration; workflow optimization; remote work protocols; process improvement; recommendation</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -38003,19 +37979,15 @@
         </is>
       </c>
       <c r="S240" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T240" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U240" t="inlineStr"/>
       <c r="V240" t="inlineStr">
         <is>
-          <t>keep:0, "Protocol Improvement Determination/Work Protocol Improvement Determination":2, "Protocol Improvement Recommendation":1</t>
+          <t>keep:1, "Protocol Improvement Determination":1, "Future Work Protocol Recommendation":1</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
@@ -38032,7 +38004,7 @@
         </is>
       </c>
       <c r="Z240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -38105,7 +38077,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Team Role Definition</t>
+          <t>Role and Responsibility Definition</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -38136,7 +38108,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>RACI matrix; team communication protocols; role assignment; team role definition; organizational roles</t>
+          <t>RACI matrix; team communication protocols; role assignment; responsibility matrix; organizational roles</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -38151,19 +38123,15 @@
         </is>
       </c>
       <c r="S241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T241" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U241" t="inlineStr"/>
       <c r="V241" t="inlineStr">
         <is>
-          <t>keep:0, "Team Role Definition":3</t>
+          <t>keep:1, "Team Roles Determination":1, "Team Role Definition":1</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
@@ -38180,7 +38148,7 @@
         </is>
       </c>
       <c r="Z241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -38253,12 +38221,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Group Interaction Coordination</t>
+          <t>Team Coordination</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Facilitates group interaction to achieve shared outcomes.</t>
+          <t>Facilitates group interaction and collaborates on tasks and communication to achieve shared outcomes.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -38284,7 +38252,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>collaboration; group dynamics; facilitation; communication; interaction</t>
+          <t>collaboration; group dynamics; facilitation; communication; team</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -38302,7 +38270,7 @@
         <v>1</v>
       </c>
       <c r="T242" t="n">
-        <v>0.9</v>
+        <v>0.9066666666666667</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
@@ -38311,7 +38279,7 @@
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>keep:0, "Group Interaction Coordination":3</t>
+          <t>keep:0, "Team Interaction Coordination/Team Coordination":3</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
@@ -38401,7 +38369,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Virtual Collaboration Compliance Monitoring</t>
+          <t>Virtual Collaboration Compliance Review</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -38432,7 +38400,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>remote teamwork; compliance auditing; virtual workspace protocols; digital collaboration tools; policy enforcement</t>
+          <t>remote teamwork; compliance auditing; virtual workspace protocols; team communication protocols; policy enforcement</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
@@ -38447,15 +38415,19 @@
         </is>
       </c>
       <c r="S243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T243" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U243" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>keep:2, "Collaboration Protocol Compliance Review":1</t>
+          <t>keep:0, "Virtual Collaboration Compliance Review":3</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
@@ -38472,12 +38444,16 @@
         </is>
       </c>
       <c r="Z243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA243" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB243" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>Protocol Compliance Review (LLM verified, sim=0.80)</t>
+        </is>
+      </c>
       <c r="AC243" t="b">
         <v>0</v>
       </c>
@@ -38550,7 +38526,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Develops collaborative virtual knowledge‑sharing protocols based on task details and team goals.</t>
+          <t>Develops collaborative virtual knowledge‑sharing protocols in line with task details and team goals.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -38720,7 +38696,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>remote collaboration; cyber security; virtual work policies; digital communication standards; team protocols</t>
+          <t>remote collaboration; cyber security; virtual work policies; team protocols; online teamwork tools</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
@@ -38738,12 +38714,12 @@
         <v>0</v>
       </c>
       <c r="T245" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U245" t="inlineStr"/>
       <c r="V245" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Team Protocol Identification":1</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
@@ -38837,7 +38813,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Technology Monitoring</t>
+          <t>Data Protection Monitoring</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -38868,7 +38844,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>cybersecurity; intrusion detection; incident response; SIEM; technology monitoring</t>
+          <t>cybersecurity; intrusion detection; incident response; data protection; data compliance</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -38883,19 +38859,15 @@
         </is>
       </c>
       <c r="S246" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T246" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U246" t="inlineStr"/>
       <c r="V246" t="inlineStr">
         <is>
-          <t>keep:1, "Technology Monitoring":2</t>
+          <t>keep:2, "Data Protection Monitoring":1</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
@@ -39020,7 +38992,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>encryption; cryptography; key management; enterprise security; TLS/SSL</t>
+          <t>cryptography; key management; enterprise security; encryption; TLS/SSL</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -39042,12 +39014,12 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Implementation":2, "Encryption Deployment":1</t>
+          <t>keep:0, "Encryption Implementation":3</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
@@ -39141,7 +39113,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Encryption Implementation Planning</t>
+          <t>Encryption Implementation Strategy Planning</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -39172,7 +39144,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>cryptography; key management; security policy; encryption standards; implementation roadmap</t>
+          <t>cryptography; security policy; encryption standards; implementation roadmap; encryption implementation strategy</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -39187,15 +39159,19 @@
         </is>
       </c>
       <c r="S248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T248" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="U248" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>keep:2, "Encryption Implementation Strategy Planning":1</t>
+          <t>keep:0, "Encryption Implementation Strategy Planning":3</t>
         </is>
       </c>
       <c r="W248" t="inlineStr">
@@ -39212,12 +39188,16 @@
         </is>
       </c>
       <c r="Z248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA248" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB248" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>Encryption Plan Creation (LLM verified, sim=0.74)</t>
+        </is>
+      </c>
       <c r="AC248" t="b">
         <v>0</v>
       </c>
@@ -39294,7 +39274,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Determines function and performance of encryption tools by measuring performance metrics in operational settings.</t>
+          <t>Determines encryption tools by measuring performance metrics in operational settings.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -39320,7 +39300,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>cryptography; encryption algorithms; performance benchmarking; security analysis; encryption technologies</t>
+          <t>cryptography; encryption algorithms; performance benchmarking; security analysis; OpenSSL</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -39335,19 +39315,15 @@
         </is>
       </c>
       <c r="S249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T249" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="U249" t="inlineStr"/>
       <c r="V249" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Technology Performance Assessment/Encryption Performance Assessment":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
@@ -39364,7 +39340,7 @@
         </is>
       </c>
       <c r="Z249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -39441,7 +39417,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Encryption Standards Understanding</t>
+          <t>Encryption Standards Familiarisation</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -39490,16 +39466,16 @@
         <v>1</v>
       </c>
       <c r="T250" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>MIS re-refinement: Structure Rule 4 — tail 'Knowledge' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
         </is>
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Standards Understanding":2, "Encryption Standards Review":1</t>
+          <t>keep:0, "Encryption Standards Understanding":1, "Encryption Standards Familiarisation":1, "Encryption Technologies Review":1</t>
         </is>
       </c>
       <c r="W250" t="inlineStr">
@@ -39527,9 +39503,13 @@
       </c>
       <c r="AD250" t="inlineStr"/>
       <c r="AE250" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF250" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Knowledge' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AG250" t="b">
         <v>0</v>
       </c>
@@ -39593,7 +39573,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Encryption Technologies Evaluation</t>
+          <t>Encryption Implementation Evaluation</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -39624,7 +39604,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>cryptography; encryption standards; key management; security assessment; encryption technologies</t>
+          <t>cryptography; encryption standards; key management; encryption technologies; compliance</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
@@ -39646,12 +39626,12 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>keep:1, "Encryption Technologies Evaluation/Encryption Implementation Evaluation":2</t>
+          <t>keep:0, "Encryption Technology Implementation Evaluation/Encryption Implementation Evaluation":3</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
@@ -39745,7 +39725,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Feedback Solicitation</t>
+          <t>User Feedback Solicitation</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -39803,7 +39783,7 @@
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>keep:0, "Feedback Solicitation":3</t>
+          <t>keep:0, "User Feedback Solicitation":3</t>
         </is>
       </c>
       <c r="W252" t="inlineStr">
@@ -39897,7 +39877,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Protocol Compliance</t>
+          <t>Protocol Following</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -39950,12 +39930,12 @@
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t>MIS re-refinement: Structure Rule 4 — tail 'Compliance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>keep:0, "Protocol Compliance":3</t>
+          <t>keep:0, "Protocol Compliance":2, "Protocol Following":1</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
@@ -39983,9 +39963,13 @@
       </c>
       <c r="AD253" t="inlineStr"/>
       <c r="AE253" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF253" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>Structure Rule 4 — tail 'Compliance' is a state/quality word; rewrite to [Object] + [Action-as-Noun].</t>
+        </is>
+      </c>
       <c r="AG253" t="b">
         <v>0</v>
       </c>
@@ -40049,12 +40033,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Encryption Analysis Reporting</t>
+          <t>Encryption Impact Reporting</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Reports encryption analysis and submits notifications to affected users and staff of incident impacts.</t>
+          <t>Reports encryption analysis and submits user impact information to affected users and organisational personnel.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -40080,7 +40064,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>encryption technologies; encryption analysis; security reporting; stakeholder communication; risk assessment</t>
+          <t>impact; encryption analysis; security reporting; stakeholder communication; risk assessment</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
@@ -40107,7 +40091,7 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Analysis Reporting/Encryption Technologies Reporting":3</t>
+          <t>keep:0, "Encryption Impact Reporting/Encryption Technologies Reporting/Encryption Technology Reporting":3</t>
         </is>
       </c>
       <c r="W254" t="inlineStr">
@@ -40127,13 +40111,9 @@
         <v>1</v>
       </c>
       <c r="AA254" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>User Impact Analysis (LLM verified, sim=0.75)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB254" t="inlineStr"/>
       <c r="AC254" t="b">
         <v>0</v>
       </c>
@@ -40263,7 +40243,7 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>keep:0, "Encryption Plan Creation":3</t>
+          <t>keep:0, "Encryption Implementation Plan Creation/Encryption Plan Creation":3</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
@@ -40283,13 +40263,9 @@
         <v>1</v>
       </c>
       <c r="AA255" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>Encryption Implementation Planning (LLM verified, sim=0.74)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB255" t="inlineStr"/>
       <c r="AC255" t="b">
         <v>0</v>
       </c>
@@ -40366,7 +40342,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Identifies enterprise data security needs by reviewing network architecture and organisational requirements.</t>
+          <t>Identifies enterprise data security needs based on network architecture and organisational requirements.</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -40392,7 +40368,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>cybersecurity; risk assessment; network security; data protection; enterprise data security</t>
+          <t>cybersecurity; network security; data protection; compliance governance; enterprise data security</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -40414,12 +40390,12 @@
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>keep:0, "Security Requirements Identification":3</t>
+          <t>keep:0, "Security Requirements Identification":2, "Security Requirements Analysis":1</t>
         </is>
       </c>
       <c r="W256" t="inlineStr">
@@ -40544,7 +40520,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>communication channels; stakeholder management; role‑based messaging; collaboration tools; mode of communication</t>
+          <t>communication channels; role‑based messaging; collaboration tools; information flow; mode of communication</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
@@ -40562,16 +40538,16 @@
         <v>1</v>
       </c>
       <c r="T257" t="n">
-        <v>0.925</v>
+        <v>0.9</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>keep:0, "Communication Coordination/Team Communication Coordination":2, "Communication Determination":1</t>
+          <t>keep:0, "Communication Coordination":3</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
@@ -40670,7 +40646,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Creates workplace documents using specialized, cohesive language to present technical data.</t>
+          <t>Prepares workplace documentation that incorporates an evaluation of technical information using specialised and cohesive language.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -40714,12 +40690,12 @@
         <v>0</v>
       </c>
       <c r="T258" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="U258" t="inlineStr"/>
       <c r="V258" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Technical Documentation Preparation":1</t>
         </is>
       </c>
       <c r="W258" t="inlineStr">
@@ -40817,7 +40793,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Security Issue Troubleshooting</t>
+          <t>Security Issues Troubleshooting</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -40848,7 +40824,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>network security; incident response; connectivity troubleshooting; security protocols; firewall configuration</t>
+          <t>network security; security issues; connectivity troubleshooting; security protocols; firewall configuration</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
@@ -40875,7 +40851,7 @@
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>keep:0, "Security Issues Troubleshooting/Security Issue Troubleshooting":3</t>
+          <t>keep:0, "Security Issue Troubleshooting/Security Issues Troubleshooting":3</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
@@ -40892,7 +40868,7 @@
         </is>
       </c>
       <c r="Z259" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -40969,7 +40945,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>User Impact Analysis</t>
+          <t>User Impact Documentation</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -41000,7 +40976,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>encryption technologies; role-based access control; security policy analysis; user responsibility mapping; impact analysis</t>
+          <t>encryption technologies; impact; security policy analysis; user responsibility mapping; risk and compliance documentation</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
@@ -41015,19 +40991,15 @@
         </is>
       </c>
       <c r="S260" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T260" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="U260" t="inlineStr"/>
       <c r="V260" t="inlineStr">
         <is>
-          <t>keep:0, "User Impact Analysis":2, "User Impact Documentation":1</t>
+          <t>keep:1, "User Impact Analysis":1, "User Role Impact Documentation":1</t>
         </is>
       </c>
       <c r="W260" t="inlineStr">
@@ -41126,7 +41098,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Actively solicit and address feedback on encryption plans from relevant personnel to meet organisational requirements.</t>
+          <t>Seeks feedback on encryption plans from relevant personnel to meet organisational requirements.</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -41152,7 +41124,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>encryption plan feedback; personnel consultation; response handling; feedback integration; proposed encryption plan</t>
+          <t>encryption plan feedback; personnel response; organisational needs; feedback collection; proposed encryption plan</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
@@ -41180,15 +41152,15 @@
       <c r="V261" t="inlineStr"/>
       <c r="W261" t="inlineStr">
         <is>
-          <t>Actively solicit and address feedback on encryption plans from relevant personnel to meet organisational requirements.</t>
+          <t>Collects and addresses feedback on encryption plans from relevant personnel to meet organisational requirements.</t>
         </is>
       </c>
       <c r="X261" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>encryption plan feedback, personnel consultation, organisational needs, response handling, feedback integration</t>
+          <t>encryption plan feedback, personnel response, organisational needs, feedback collection, response handling</t>
         </is>
       </c>
       <c r="Z261" t="b">
@@ -41274,7 +41246,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Records encryption issues and compromises and submits the documentation to the organisational help desk support.</t>
+          <t>Documents encryption problems and compromises and submits them to the organisational help desk for support.</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -41300,7 +41272,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>encryption issues; compromise documentation; help desk submission; incident reporting; reporting</t>
+          <t>encryption issues; compromise documentation; help desk submission; incident reporting; security logging</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
@@ -41328,19 +41300,19 @@
       <c r="V262" t="inlineStr"/>
       <c r="W262" t="inlineStr">
         <is>
-          <t>Records encryption issues and compromises and submits the documentation to the organisational help desk support.</t>
+          <t>Records encryption problems and compromises, prepares documentation, and forwards it to the organisational help desk for support.</t>
         </is>
       </c>
       <c r="X262" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>encryption issues, compromise documentation, help desk submission, incident reporting, security communication</t>
+          <t>encryption issues, compromise documentation, help desk submission, incident reporting, security logging</t>
         </is>
       </c>
       <c r="Z262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
